--- a/chat_bot/1300_вопросов_от_студентов_для_базы_данных.xlsx
+++ b/chat_bot/1300_вопросов_от_студентов_для_базы_данных.xlsx
@@ -12174,10 +12174,19 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12186,11 +12195,17 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -12208,21 +12223,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14356,7 +14356,7 @@
       <c r="F98" s="23"/>
     </row>
     <row r="99" spans="1:6" ht="72" customHeight="1">
-      <c r="A99" s="103" t="s">
+      <c r="A99" s="91" t="s">
         <v>255</v>
       </c>
       <c r="B99" s="5" t="s">
@@ -14372,7 +14372,7 @@
       <c r="F99" s="23"/>
     </row>
     <row r="100" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A100" s="91"/>
+      <c r="A100" s="92"/>
       <c r="B100" s="5" t="s">
         <v>258</v>
       </c>
@@ -14386,7 +14386,7 @@
       <c r="F100" s="23"/>
     </row>
     <row r="101" spans="1:6" ht="31">
-      <c r="A101" s="91"/>
+      <c r="A101" s="92"/>
       <c r="B101" s="5" t="s">
         <v>260</v>
       </c>
@@ -14400,7 +14400,7 @@
       <c r="F101" s="23"/>
     </row>
     <row r="102" spans="1:6" ht="63" customHeight="1">
-      <c r="A102" s="91"/>
+      <c r="A102" s="92"/>
       <c r="B102" s="5" t="s">
         <v>262</v>
       </c>
@@ -14414,7 +14414,7 @@
       <c r="F102" s="23"/>
     </row>
     <row r="103" spans="1:6" ht="155.25" customHeight="1">
-      <c r="A103" s="91"/>
+      <c r="A103" s="92"/>
       <c r="B103" s="5" t="s">
         <v>264</v>
       </c>
@@ -14428,7 +14428,7 @@
       <c r="F103" s="23"/>
     </row>
     <row r="104" spans="1:6" ht="15.5">
-      <c r="A104" s="91"/>
+      <c r="A104" s="92"/>
       <c r="B104" s="5" t="s">
         <v>266</v>
       </c>
@@ -14442,7 +14442,7 @@
       <c r="F104" s="23"/>
     </row>
     <row r="105" spans="1:6" ht="31">
-      <c r="A105" s="91"/>
+      <c r="A105" s="92"/>
       <c r="B105" s="5" t="s">
         <v>268</v>
       </c>
@@ -14456,7 +14456,7 @@
       <c r="F105" s="23"/>
     </row>
     <row r="106" spans="1:6" ht="15.5">
-      <c r="A106" s="91"/>
+      <c r="A106" s="92"/>
       <c r="B106" s="5" t="s">
         <v>270</v>
       </c>
@@ -14470,7 +14470,7 @@
       <c r="F106" s="23"/>
     </row>
     <row r="107" spans="1:6" ht="63" customHeight="1">
-      <c r="A107" s="91"/>
+      <c r="A107" s="92"/>
       <c r="B107" s="5" t="s">
         <v>272</v>
       </c>
@@ -14484,7 +14484,7 @@
       <c r="F107" s="23"/>
     </row>
     <row r="108" spans="1:6" ht="15.5">
-      <c r="A108" s="91"/>
+      <c r="A108" s="92"/>
       <c r="B108" s="5" t="s">
         <v>274</v>
       </c>
@@ -14498,7 +14498,7 @@
       <c r="F108" s="23"/>
     </row>
     <row r="109" spans="1:6" ht="156.75" customHeight="1">
-      <c r="A109" s="91"/>
+      <c r="A109" s="92"/>
       <c r="B109" s="5" t="s">
         <v>276</v>
       </c>
@@ -14512,7 +14512,7 @@
       <c r="F109" s="23"/>
     </row>
     <row r="110" spans="1:6" ht="31">
-      <c r="A110" s="91"/>
+      <c r="A110" s="92"/>
       <c r="B110" s="5" t="s">
         <v>216</v>
       </c>
@@ -14526,7 +14526,7 @@
       <c r="F110" s="23"/>
     </row>
     <row r="111" spans="1:6" ht="31">
-      <c r="A111" s="91"/>
+      <c r="A111" s="92"/>
       <c r="B111" s="5" t="s">
         <v>279</v>
       </c>
@@ -14540,7 +14540,7 @@
       <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="62">
-      <c r="A112" s="91"/>
+      <c r="A112" s="92"/>
       <c r="B112" s="5" t="s">
         <v>281</v>
       </c>
@@ -14556,7 +14556,7 @@
       <c r="F112" s="23"/>
     </row>
     <row r="113" spans="1:6" ht="71.25" customHeight="1">
-      <c r="A113" s="91"/>
+      <c r="A113" s="92"/>
       <c r="B113" s="5" t="s">
         <v>284</v>
       </c>
@@ -14570,7 +14570,7 @@
       <c r="F113" s="23"/>
     </row>
     <row r="114" spans="1:6" ht="46.5">
-      <c r="A114" s="91"/>
+      <c r="A114" s="92"/>
       <c r="B114" s="5" t="s">
         <v>287</v>
       </c>
@@ -14584,7 +14584,7 @@
       <c r="F114" s="23"/>
     </row>
     <row r="115" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A115" s="91"/>
+      <c r="A115" s="92"/>
       <c r="B115" s="5" t="s">
         <v>289</v>
       </c>
@@ -14598,7 +14598,7 @@
       <c r="F115" s="23"/>
     </row>
     <row r="116" spans="1:6" ht="30" customHeight="1">
-      <c r="A116" s="91"/>
+      <c r="A116" s="92"/>
       <c r="B116" s="5" t="s">
         <v>291</v>
       </c>
@@ -14612,7 +14612,7 @@
       <c r="F116" s="23"/>
     </row>
     <row r="117" spans="1:6" ht="31">
-      <c r="A117" s="91"/>
+      <c r="A117" s="92"/>
       <c r="B117" s="5" t="s">
         <v>293</v>
       </c>
@@ -14626,7 +14626,7 @@
       <c r="F117" s="23"/>
     </row>
     <row r="118" spans="1:6" ht="31">
-      <c r="A118" s="91"/>
+      <c r="A118" s="92"/>
       <c r="B118" s="5" t="s">
         <v>295</v>
       </c>
@@ -14640,7 +14640,7 @@
       <c r="F118" s="23"/>
     </row>
     <row r="119" spans="1:6" ht="93">
-      <c r="A119" s="91"/>
+      <c r="A119" s="92"/>
       <c r="B119" s="5" t="s">
         <v>297</v>
       </c>
@@ -14654,7 +14654,7 @@
       <c r="F119" s="23"/>
     </row>
     <row r="120" spans="1:6" ht="31">
-      <c r="A120" s="91"/>
+      <c r="A120" s="92"/>
       <c r="B120" s="5" t="s">
         <v>299</v>
       </c>
@@ -14668,7 +14668,7 @@
       <c r="F120" s="23"/>
     </row>
     <row r="121" spans="1:6" ht="31">
-      <c r="A121" s="91"/>
+      <c r="A121" s="92"/>
       <c r="B121" s="5" t="s">
         <v>302</v>
       </c>
@@ -14682,7 +14682,7 @@
       <c r="F121" s="23"/>
     </row>
     <row r="122" spans="1:6" ht="15.5">
-      <c r="A122" s="91"/>
+      <c r="A122" s="92"/>
       <c r="B122" s="1" t="s">
         <v>304</v>
       </c>
@@ -14696,7 +14696,7 @@
       <c r="F122" s="23"/>
     </row>
     <row r="123" spans="1:6" ht="31">
-      <c r="A123" s="91"/>
+      <c r="A123" s="92"/>
       <c r="B123" s="5" t="s">
         <v>307</v>
       </c>
@@ -14710,7 +14710,7 @@
       <c r="F123" s="23"/>
     </row>
     <row r="124" spans="1:6" ht="31">
-      <c r="A124" s="91"/>
+      <c r="A124" s="92"/>
       <c r="B124" s="5" t="s">
         <v>309</v>
       </c>
@@ -14724,7 +14724,7 @@
       <c r="F124" s="23"/>
     </row>
     <row r="125" spans="1:6" ht="31">
-      <c r="A125" s="91"/>
+      <c r="A125" s="92"/>
       <c r="B125" s="5" t="s">
         <v>312</v>
       </c>
@@ -14738,7 +14738,7 @@
       <c r="F125" s="23"/>
     </row>
     <row r="126" spans="1:6" ht="31">
-      <c r="A126" s="91"/>
+      <c r="A126" s="92"/>
       <c r="B126" s="5" t="s">
         <v>314</v>
       </c>
@@ -14752,7 +14752,7 @@
       <c r="F126" s="23"/>
     </row>
     <row r="127" spans="1:6" ht="77.5">
-      <c r="A127" s="91"/>
+      <c r="A127" s="92"/>
       <c r="B127" s="5" t="s">
         <v>317</v>
       </c>
@@ -14766,7 +14766,7 @@
       <c r="F127" s="23"/>
     </row>
     <row r="128" spans="1:6" ht="31">
-      <c r="A128" s="91"/>
+      <c r="A128" s="92"/>
       <c r="B128" s="5" t="s">
         <v>319</v>
       </c>
@@ -14780,7 +14780,7 @@
       <c r="F128" s="23"/>
     </row>
     <row r="129" spans="1:6" ht="15.5">
-      <c r="A129" s="91"/>
+      <c r="A129" s="92"/>
       <c r="B129" s="5" t="s">
         <v>321</v>
       </c>
@@ -14794,7 +14794,7 @@
       <c r="F129" s="23"/>
     </row>
     <row r="130" spans="1:6" ht="31">
-      <c r="A130" s="91"/>
+      <c r="A130" s="92"/>
       <c r="B130" s="5" t="s">
         <v>323</v>
       </c>
@@ -14808,7 +14808,7 @@
       <c r="F130" s="23"/>
     </row>
     <row r="131" spans="1:6" ht="31">
-      <c r="A131" s="91"/>
+      <c r="A131" s="92"/>
       <c r="B131" s="5" t="s">
         <v>326</v>
       </c>
@@ -14822,7 +14822,7 @@
       <c r="F131" s="23"/>
     </row>
     <row r="132" spans="1:6" ht="31">
-      <c r="A132" s="91"/>
+      <c r="A132" s="92"/>
       <c r="B132" s="5" t="s">
         <v>328</v>
       </c>
@@ -14836,7 +14836,7 @@
       <c r="F132" s="23"/>
     </row>
     <row r="133" spans="1:6" ht="31">
-      <c r="A133" s="91"/>
+      <c r="A133" s="92"/>
       <c r="B133" s="5" t="s">
         <v>330</v>
       </c>
@@ -14850,7 +14850,7 @@
       <c r="F133" s="23"/>
     </row>
     <row r="134" spans="1:6" ht="31">
-      <c r="A134" s="91"/>
+      <c r="A134" s="92"/>
       <c r="B134" s="5" t="s">
         <v>332</v>
       </c>
@@ -14864,7 +14864,7 @@
       <c r="F134" s="23"/>
     </row>
     <row r="135" spans="1:6" ht="31">
-      <c r="A135" s="91"/>
+      <c r="A135" s="92"/>
       <c r="B135" s="5" t="s">
         <v>334</v>
       </c>
@@ -14878,7 +14878,7 @@
       <c r="F135" s="23"/>
     </row>
     <row r="136" spans="1:6" ht="28">
-      <c r="A136" s="91"/>
+      <c r="A136" s="92"/>
       <c r="B136" s="5" t="s">
         <v>337</v>
       </c>
@@ -14892,7 +14892,7 @@
       <c r="F136" s="23"/>
     </row>
     <row r="137" spans="1:6" ht="31">
-      <c r="A137" s="91"/>
+      <c r="A137" s="92"/>
       <c r="B137" s="5" t="s">
         <v>339</v>
       </c>
@@ -14904,7 +14904,7 @@
       <c r="F137" s="23"/>
     </row>
     <row r="138" spans="1:6" ht="42.5">
-      <c r="A138" s="91"/>
+      <c r="A138" s="92"/>
       <c r="B138" s="1" t="s">
         <v>341</v>
       </c>
@@ -14918,7 +14918,7 @@
       <c r="F138" s="23"/>
     </row>
     <row r="139" spans="1:6" ht="236.25" customHeight="1">
-      <c r="A139" s="91"/>
+      <c r="A139" s="92"/>
       <c r="B139" s="5" t="s">
         <v>343</v>
       </c>
@@ -14932,7 +14932,7 @@
       <c r="F139" s="23"/>
     </row>
     <row r="140" spans="1:6" ht="31">
-      <c r="A140" s="91"/>
+      <c r="A140" s="92"/>
       <c r="B140" s="5" t="s">
         <v>345</v>
       </c>
@@ -14946,7 +14946,7 @@
       <c r="F140" s="23"/>
     </row>
     <row r="141" spans="1:6" ht="62">
-      <c r="A141" s="91"/>
+      <c r="A141" s="92"/>
       <c r="B141" s="5" t="s">
         <v>347</v>
       </c>
@@ -14960,7 +14960,7 @@
       <c r="F141" s="23"/>
     </row>
     <row r="142" spans="1:6" ht="31">
-      <c r="A142" s="91"/>
+      <c r="A142" s="92"/>
       <c r="B142" s="5" t="s">
         <v>350</v>
       </c>
@@ -14974,7 +14974,7 @@
       <c r="F142" s="23"/>
     </row>
     <row r="143" spans="1:6" ht="15.5">
-      <c r="A143" s="91"/>
+      <c r="A143" s="92"/>
       <c r="B143" s="5" t="s">
         <v>352</v>
       </c>
@@ -14986,7 +14986,7 @@
       <c r="F143" s="23"/>
     </row>
     <row r="144" spans="1:6" ht="31">
-      <c r="A144" s="91"/>
+      <c r="A144" s="92"/>
       <c r="B144" s="5" t="s">
         <v>354</v>
       </c>
@@ -15000,7 +15000,7 @@
       <c r="F144" s="23"/>
     </row>
     <row r="145" spans="1:6" ht="31">
-      <c r="A145" s="91"/>
+      <c r="A145" s="92"/>
       <c r="B145" s="5" t="s">
         <v>356</v>
       </c>
@@ -15014,7 +15014,7 @@
       <c r="F145" s="23"/>
     </row>
     <row r="146" spans="1:6" ht="62.25" customHeight="1">
-      <c r="A146" s="91"/>
+      <c r="A146" s="92"/>
       <c r="B146" s="5" t="s">
         <v>358</v>
       </c>
@@ -15028,7 +15028,7 @@
       <c r="F146" s="23"/>
     </row>
     <row r="147" spans="1:6" ht="31">
-      <c r="A147" s="91"/>
+      <c r="A147" s="92"/>
       <c r="B147" s="5" t="s">
         <v>360</v>
       </c>
@@ -15042,7 +15042,7 @@
       <c r="F147" s="23"/>
     </row>
     <row r="148" spans="1:6" ht="48" customHeight="1">
-      <c r="A148" s="91"/>
+      <c r="A148" s="92"/>
       <c r="B148" s="66" t="s">
         <v>362</v>
       </c>
@@ -15056,7 +15056,7 @@
       <c r="F148" s="23"/>
     </row>
     <row r="149" spans="1:6" ht="31">
-      <c r="A149" s="91"/>
+      <c r="A149" s="92"/>
       <c r="B149" s="5" t="s">
         <v>364</v>
       </c>
@@ -15070,7 +15070,7 @@
       <c r="F149" s="23"/>
     </row>
     <row r="150" spans="1:6" ht="28">
-      <c r="A150" s="91"/>
+      <c r="A150" s="92"/>
       <c r="B150" s="1" t="s">
         <v>366</v>
       </c>
@@ -15084,7 +15084,7 @@
       <c r="F150" s="23"/>
     </row>
     <row r="151" spans="1:6" ht="73.5" customHeight="1">
-      <c r="A151" s="91"/>
+      <c r="A151" s="92"/>
       <c r="B151" s="5" t="s">
         <v>369</v>
       </c>
@@ -15098,7 +15098,7 @@
       <c r="F151" s="23"/>
     </row>
     <row r="152" spans="1:6" ht="31">
-      <c r="A152" s="91"/>
+      <c r="A152" s="92"/>
       <c r="B152" s="5" t="s">
         <v>371</v>
       </c>
@@ -15112,7 +15112,7 @@
       <c r="F152" s="23"/>
     </row>
     <row r="153" spans="1:6" ht="31">
-      <c r="A153" s="91"/>
+      <c r="A153" s="92"/>
       <c r="B153" s="5" t="s">
         <v>373</v>
       </c>
@@ -15126,7 +15126,7 @@
       <c r="F153" s="23"/>
     </row>
     <row r="154" spans="1:6" ht="28.5">
-      <c r="A154" s="91"/>
+      <c r="A154" s="92"/>
       <c r="B154" s="5" t="s">
         <v>376</v>
       </c>
@@ -15140,7 +15140,7 @@
       <c r="F154" s="23"/>
     </row>
     <row r="155" spans="1:6" ht="31">
-      <c r="A155" s="91"/>
+      <c r="A155" s="92"/>
       <c r="B155" s="5" t="s">
         <v>378</v>
       </c>
@@ -15154,7 +15154,7 @@
       <c r="F155" s="23"/>
     </row>
     <row r="156" spans="1:6" ht="77.5">
-      <c r="A156" s="91"/>
+      <c r="A156" s="92"/>
       <c r="B156" s="5" t="s">
         <v>380</v>
       </c>
@@ -15168,7 +15168,7 @@
       <c r="F156" s="23"/>
     </row>
     <row r="157" spans="1:6" ht="31">
-      <c r="A157" s="91"/>
+      <c r="A157" s="92"/>
       <c r="B157" s="5" t="s">
         <v>382</v>
       </c>
@@ -15182,7 +15182,7 @@
       <c r="F157" s="23"/>
     </row>
     <row r="158" spans="1:6" ht="31">
-      <c r="A158" s="91"/>
+      <c r="A158" s="92"/>
       <c r="B158" s="5" t="s">
         <v>384</v>
       </c>
@@ -15196,7 +15196,7 @@
       <c r="F158" s="23"/>
     </row>
     <row r="159" spans="1:6" ht="31">
-      <c r="A159" s="91"/>
+      <c r="A159" s="92"/>
       <c r="B159" s="5" t="s">
         <v>386</v>
       </c>
@@ -15210,7 +15210,7 @@
       <c r="F159" s="23"/>
     </row>
     <row r="160" spans="1:6" ht="31">
-      <c r="A160" s="91"/>
+      <c r="A160" s="92"/>
       <c r="B160" s="5" t="s">
         <v>388</v>
       </c>
@@ -15224,7 +15224,7 @@
       <c r="F160" s="23"/>
     </row>
     <row r="161" spans="1:6" ht="88.5" customHeight="1">
-      <c r="A161" s="91"/>
+      <c r="A161" s="92"/>
       <c r="B161" s="5" t="s">
         <v>390</v>
       </c>
@@ -15240,7 +15240,7 @@
       <c r="F161" s="23"/>
     </row>
     <row r="162" spans="1:6" ht="31">
-      <c r="A162" s="91"/>
+      <c r="A162" s="92"/>
       <c r="B162" s="5" t="s">
         <v>392</v>
       </c>
@@ -15254,7 +15254,7 @@
       <c r="F162" s="23"/>
     </row>
     <row r="163" spans="1:6" ht="31">
-      <c r="A163" s="91"/>
+      <c r="A163" s="92"/>
       <c r="B163" s="5" t="s">
         <v>394</v>
       </c>
@@ -15268,7 +15268,7 @@
       <c r="F163" s="23"/>
     </row>
     <row r="164" spans="1:6" ht="60.75" customHeight="1">
-      <c r="A164" s="91"/>
+      <c r="A164" s="92"/>
       <c r="B164" s="5" t="s">
         <v>396</v>
       </c>
@@ -15282,7 +15282,7 @@
       <c r="F164" s="23"/>
     </row>
     <row r="165" spans="1:6" ht="62">
-      <c r="A165" s="91"/>
+      <c r="A165" s="92"/>
       <c r="B165" s="5" t="s">
         <v>398</v>
       </c>
@@ -15296,7 +15296,7 @@
       <c r="F165" s="23"/>
     </row>
     <row r="166" spans="1:6" ht="31">
-      <c r="A166" s="91"/>
+      <c r="A166" s="92"/>
       <c r="B166" s="5" t="s">
         <v>400</v>
       </c>
@@ -15310,7 +15310,7 @@
       <c r="F166" s="23"/>
     </row>
     <row r="167" spans="1:6" ht="31">
-      <c r="A167" s="91"/>
+      <c r="A167" s="92"/>
       <c r="B167" s="5" t="s">
         <v>402</v>
       </c>
@@ -15324,7 +15324,7 @@
       <c r="F167" s="23"/>
     </row>
     <row r="168" spans="1:6" ht="62">
-      <c r="A168" s="91"/>
+      <c r="A168" s="92"/>
       <c r="B168" s="1" t="s">
         <v>404</v>
       </c>
@@ -15338,7 +15338,7 @@
       <c r="F168" s="23"/>
     </row>
     <row r="169" spans="1:6" ht="28">
-      <c r="A169" s="91"/>
+      <c r="A169" s="92"/>
       <c r="B169" s="5" t="s">
         <v>406</v>
       </c>
@@ -15352,7 +15352,7 @@
       <c r="F169" s="23"/>
     </row>
     <row r="170" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A170" s="91"/>
+      <c r="A170" s="92"/>
       <c r="B170" s="5" t="s">
         <v>408</v>
       </c>
@@ -15368,7 +15368,7 @@
       <c r="F170" s="23"/>
     </row>
     <row r="171" spans="1:6" ht="56">
-      <c r="A171" s="91"/>
+      <c r="A171" s="92"/>
       <c r="B171" s="5" t="s">
         <v>412</v>
       </c>
@@ -15384,7 +15384,7 @@
       <c r="F171" s="23"/>
     </row>
     <row r="172" spans="1:6" s="26" customFormat="1" ht="120" customHeight="1">
-      <c r="A172" s="91"/>
+      <c r="A172" s="92"/>
       <c r="B172" s="5" t="s">
         <v>414</v>
       </c>
@@ -15396,7 +15396,7 @@
       <c r="F172" s="23"/>
     </row>
     <row r="173" spans="1:6" ht="31">
-      <c r="A173" s="91"/>
+      <c r="A173" s="92"/>
       <c r="B173" s="5" t="s">
         <v>416</v>
       </c>
@@ -15410,7 +15410,7 @@
       <c r="F173" s="23"/>
     </row>
     <row r="174" spans="1:6" ht="31">
-      <c r="A174" s="91"/>
+      <c r="A174" s="92"/>
       <c r="B174" s="1" t="s">
         <v>418</v>
       </c>
@@ -15424,7 +15424,7 @@
       <c r="F174" s="23"/>
     </row>
     <row r="175" spans="1:6" ht="72.75" customHeight="1">
-      <c r="A175" s="91"/>
+      <c r="A175" s="92"/>
       <c r="B175" s="68" t="s">
         <v>420</v>
       </c>
@@ -15438,7 +15438,7 @@
       <c r="F175" s="23"/>
     </row>
     <row r="176" spans="1:6" ht="31">
-      <c r="A176" s="91"/>
+      <c r="A176" s="92"/>
       <c r="B176" s="5" t="s">
         <v>422</v>
       </c>
@@ -15452,7 +15452,7 @@
       <c r="F176" s="23"/>
     </row>
     <row r="177" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A177" s="91"/>
+      <c r="A177" s="92"/>
       <c r="B177" s="1" t="s">
         <v>424</v>
       </c>
@@ -15466,7 +15466,7 @@
       <c r="F177" s="23"/>
     </row>
     <row r="178" spans="1:6" ht="56">
-      <c r="A178" s="91"/>
+      <c r="A178" s="92"/>
       <c r="B178" s="5" t="s">
         <v>426</v>
       </c>
@@ -15482,7 +15482,7 @@
       <c r="F178" s="23"/>
     </row>
     <row r="179" spans="1:6" ht="57.75" customHeight="1">
-      <c r="A179" s="91"/>
+      <c r="A179" s="92"/>
       <c r="B179" s="5" t="s">
         <v>428</v>
       </c>
@@ -15496,7 +15496,7 @@
       <c r="F179" s="23"/>
     </row>
     <row r="180" spans="1:6" ht="46.5">
-      <c r="A180" s="91"/>
+      <c r="A180" s="92"/>
       <c r="B180" s="5" t="s">
         <v>430</v>
       </c>
@@ -15510,7 +15510,7 @@
       <c r="F180" s="23"/>
     </row>
     <row r="181" spans="1:6" ht="46.5">
-      <c r="A181" s="91"/>
+      <c r="A181" s="92"/>
       <c r="B181" s="1" t="s">
         <v>432</v>
       </c>
@@ -15524,7 +15524,7 @@
       <c r="F181" s="23"/>
     </row>
     <row r="182" spans="1:6" ht="60" customHeight="1">
-      <c r="A182" s="91"/>
+      <c r="A182" s="92"/>
       <c r="B182" s="5" t="s">
         <v>434</v>
       </c>
@@ -15538,7 +15538,7 @@
       <c r="F182" s="23"/>
     </row>
     <row r="183" spans="1:6" ht="70.5" customHeight="1">
-      <c r="A183" s="91"/>
+      <c r="A183" s="92"/>
       <c r="B183" s="5" t="s">
         <v>436</v>
       </c>
@@ -15554,7 +15554,7 @@
       <c r="F183" s="23"/>
     </row>
     <row r="184" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A184" s="91"/>
+      <c r="A184" s="92"/>
       <c r="B184" s="5" t="s">
         <v>438</v>
       </c>
@@ -15568,7 +15568,7 @@
       <c r="F184" s="23"/>
     </row>
     <row r="185" spans="1:6" ht="15.5">
-      <c r="A185" s="91"/>
+      <c r="A185" s="92"/>
       <c r="B185" s="5" t="s">
         <v>440</v>
       </c>
@@ -15582,7 +15582,7 @@
       <c r="F185" s="23"/>
     </row>
     <row r="186" spans="1:6" ht="15.5">
-      <c r="A186" s="91"/>
+      <c r="A186" s="92"/>
       <c r="B186" s="5" t="s">
         <v>442</v>
       </c>
@@ -15596,7 +15596,7 @@
       <c r="F186" s="23"/>
     </row>
     <row r="187" spans="1:6" ht="63" customHeight="1">
-      <c r="A187" s="91"/>
+      <c r="A187" s="92"/>
       <c r="B187" s="1" t="s">
         <v>444</v>
       </c>
@@ -15610,7 +15610,7 @@
       <c r="F187" s="23"/>
     </row>
     <row r="188" spans="1:6" ht="46.5">
-      <c r="A188" s="91"/>
+      <c r="A188" s="92"/>
       <c r="B188" s="5" t="s">
         <v>446</v>
       </c>
@@ -15624,7 +15624,7 @@
       <c r="F188" s="23"/>
     </row>
     <row r="189" spans="1:6" ht="31">
-      <c r="A189" s="91"/>
+      <c r="A189" s="92"/>
       <c r="B189" s="5" t="s">
         <v>448</v>
       </c>
@@ -15638,7 +15638,7 @@
       <c r="F189" s="23"/>
     </row>
     <row r="190" spans="1:6" ht="31">
-      <c r="A190" s="91"/>
+      <c r="A190" s="92"/>
       <c r="B190" s="5" t="s">
         <v>450</v>
       </c>
@@ -15652,7 +15652,7 @@
       <c r="F190" s="23"/>
     </row>
     <row r="191" spans="1:6" ht="15.5">
-      <c r="A191" s="91"/>
+      <c r="A191" s="92"/>
       <c r="B191" s="5" t="s">
         <v>452</v>
       </c>
@@ -15666,7 +15666,7 @@
       <c r="F191" s="23"/>
     </row>
     <row r="192" spans="1:6" ht="39" customHeight="1">
-      <c r="A192" s="91"/>
+      <c r="A192" s="92"/>
       <c r="B192" s="5" t="s">
         <v>454</v>
       </c>
@@ -15680,7 +15680,7 @@
       <c r="F192" s="23"/>
     </row>
     <row r="193" spans="1:6" ht="135.75" customHeight="1">
-      <c r="A193" s="91"/>
+      <c r="A193" s="92"/>
       <c r="B193" s="5" t="s">
         <v>456</v>
       </c>
@@ -15694,7 +15694,7 @@
       <c r="F193" s="23"/>
     </row>
     <row r="194" spans="1:6" ht="108.75" customHeight="1">
-      <c r="A194" s="91"/>
+      <c r="A194" s="92"/>
       <c r="B194" s="5" t="s">
         <v>458</v>
       </c>
@@ -15708,7 +15708,7 @@
       <c r="F194" s="23"/>
     </row>
     <row r="195" spans="1:6" ht="31">
-      <c r="A195" s="91"/>
+      <c r="A195" s="92"/>
       <c r="B195" s="5" t="s">
         <v>460</v>
       </c>
@@ -15722,7 +15722,7 @@
       <c r="F195" s="23"/>
     </row>
     <row r="196" spans="1:6" ht="46.5">
-      <c r="A196" s="91"/>
+      <c r="A196" s="92"/>
       <c r="B196" s="5" t="s">
         <v>462</v>
       </c>
@@ -15736,7 +15736,7 @@
       <c r="F196" s="23"/>
     </row>
     <row r="197" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A197" s="91"/>
+      <c r="A197" s="92"/>
       <c r="B197" s="5" t="s">
         <v>464</v>
       </c>
@@ -15750,7 +15750,7 @@
       <c r="F197" s="23"/>
     </row>
     <row r="198" spans="1:6" ht="31">
-      <c r="A198" s="91"/>
+      <c r="A198" s="92"/>
       <c r="B198" s="5" t="s">
         <v>467</v>
       </c>
@@ -15764,7 +15764,7 @@
       <c r="F198" s="23"/>
     </row>
     <row r="199" spans="1:6" ht="28">
-      <c r="A199" s="104" t="s">
+      <c r="A199" s="93" t="s">
         <v>469</v>
       </c>
       <c r="B199" s="5" t="s">
@@ -15780,7 +15780,7 @@
       <c r="F199" s="23"/>
     </row>
     <row r="200" spans="1:6" ht="270.75" customHeight="1">
-      <c r="A200" s="92"/>
+      <c r="A200" s="94"/>
       <c r="B200" s="5" t="s">
         <v>472</v>
       </c>
@@ -15796,7 +15796,7 @@
       <c r="F200" s="23"/>
     </row>
     <row r="201" spans="1:6" ht="31">
-      <c r="A201" s="92"/>
+      <c r="A201" s="94"/>
       <c r="B201" s="5" t="s">
         <v>475</v>
       </c>
@@ -15810,7 +15810,7 @@
       <c r="F201" s="23"/>
     </row>
     <row r="202" spans="1:6" ht="165.75" customHeight="1">
-      <c r="A202" s="92"/>
+      <c r="A202" s="94"/>
       <c r="B202" s="5" t="s">
         <v>478</v>
       </c>
@@ -15824,7 +15824,7 @@
       <c r="F202" s="23"/>
     </row>
     <row r="203" spans="1:6" ht="31">
-      <c r="A203" s="92"/>
+      <c r="A203" s="94"/>
       <c r="B203" s="5" t="s">
         <v>480</v>
       </c>
@@ -15838,7 +15838,7 @@
       <c r="F203" s="23"/>
     </row>
     <row r="204" spans="1:6" ht="68.25" customHeight="1">
-      <c r="A204" s="92"/>
+      <c r="A204" s="94"/>
       <c r="B204" s="5" t="s">
         <v>482</v>
       </c>
@@ -15852,7 +15852,7 @@
       <c r="F204" s="23"/>
     </row>
     <row r="205" spans="1:6" ht="123" customHeight="1">
-      <c r="A205" s="92"/>
+      <c r="A205" s="94"/>
       <c r="B205" s="5" t="s">
         <v>485</v>
       </c>
@@ -15866,7 +15866,7 @@
       <c r="F205" s="23"/>
     </row>
     <row r="206" spans="1:6" ht="42">
-      <c r="A206" s="92"/>
+      <c r="A206" s="94"/>
       <c r="B206" s="5" t="s">
         <v>488</v>
       </c>
@@ -15880,7 +15880,7 @@
       <c r="F206" s="23"/>
     </row>
     <row r="207" spans="1:6" ht="31">
-      <c r="A207" s="92"/>
+      <c r="A207" s="94"/>
       <c r="B207" s="5" t="s">
         <v>491</v>
       </c>
@@ -15894,7 +15894,7 @@
       <c r="F207" s="23"/>
     </row>
     <row r="208" spans="1:6" ht="15.5">
-      <c r="A208" s="92"/>
+      <c r="A208" s="94"/>
       <c r="B208" s="5" t="s">
         <v>494</v>
       </c>
@@ -15908,7 +15908,7 @@
       <c r="F208" s="23"/>
     </row>
     <row r="209" spans="1:6" ht="15.5">
-      <c r="A209" s="92"/>
+      <c r="A209" s="94"/>
       <c r="B209" s="5" t="s">
         <v>496</v>
       </c>
@@ -15922,7 +15922,7 @@
       <c r="F209" s="23"/>
     </row>
     <row r="210" spans="1:6" ht="15.5">
-      <c r="A210" s="92"/>
+      <c r="A210" s="94"/>
       <c r="B210" s="5" t="s">
         <v>498</v>
       </c>
@@ -15936,7 +15936,7 @@
       <c r="F210" s="23"/>
     </row>
     <row r="211" spans="1:6" ht="31">
-      <c r="A211" s="92"/>
+      <c r="A211" s="94"/>
       <c r="B211" s="5" t="s">
         <v>500</v>
       </c>
@@ -15950,7 +15950,7 @@
       <c r="F211" s="23"/>
     </row>
     <row r="212" spans="1:6" ht="52.5" customHeight="1">
-      <c r="A212" s="92"/>
+      <c r="A212" s="94"/>
       <c r="B212" s="5" t="s">
         <v>503</v>
       </c>
@@ -15964,7 +15964,7 @@
       <c r="F212" s="23"/>
     </row>
     <row r="213" spans="1:6" ht="15.5">
-      <c r="A213" s="92"/>
+      <c r="A213" s="94"/>
       <c r="B213" s="5" t="s">
         <v>505</v>
       </c>
@@ -15978,7 +15978,7 @@
       <c r="F213" s="23"/>
     </row>
     <row r="214" spans="1:6" ht="15.5">
-      <c r="A214" s="92"/>
+      <c r="A214" s="94"/>
       <c r="B214" s="5" t="s">
         <v>508</v>
       </c>
@@ -15992,7 +15992,7 @@
       <c r="F214" s="23"/>
     </row>
     <row r="215" spans="1:6" ht="31">
-      <c r="A215" s="92"/>
+      <c r="A215" s="94"/>
       <c r="B215" s="5" t="s">
         <v>511</v>
       </c>
@@ -16006,7 +16006,7 @@
       <c r="F215" s="23"/>
     </row>
     <row r="216" spans="1:6" ht="56">
-      <c r="A216" s="92"/>
+      <c r="A216" s="94"/>
       <c r="B216" s="5" t="s">
         <v>514</v>
       </c>
@@ -16020,7 +16020,7 @@
       <c r="F216" s="23"/>
     </row>
     <row r="217" spans="1:6" ht="15.5">
-      <c r="A217" s="92"/>
+      <c r="A217" s="94"/>
       <c r="B217" s="5" t="s">
         <v>516</v>
       </c>
@@ -16032,7 +16032,7 @@
       <c r="F217" s="23"/>
     </row>
     <row r="218" spans="1:6" ht="31">
-      <c r="A218" s="92"/>
+      <c r="A218" s="94"/>
       <c r="B218" s="5" t="s">
         <v>518</v>
       </c>
@@ -16046,7 +16046,7 @@
       <c r="F218" s="23"/>
     </row>
     <row r="219" spans="1:6" ht="31">
-      <c r="A219" s="92"/>
+      <c r="A219" s="94"/>
       <c r="B219" s="5" t="s">
         <v>521</v>
       </c>
@@ -16062,7 +16062,7 @@
       <c r="F219" s="23"/>
     </row>
     <row r="220" spans="1:6" ht="31">
-      <c r="A220" s="92"/>
+      <c r="A220" s="94"/>
       <c r="B220" s="5" t="s">
         <v>523</v>
       </c>
@@ -16076,7 +16076,7 @@
       <c r="F220" s="23"/>
     </row>
     <row r="221" spans="1:6" ht="60" customHeight="1">
-      <c r="A221" s="92"/>
+      <c r="A221" s="94"/>
       <c r="B221" s="5" t="s">
         <v>525</v>
       </c>
@@ -16092,7 +16092,7 @@
       <c r="F221" s="23"/>
     </row>
     <row r="222" spans="1:6" ht="15.5">
-      <c r="A222" s="92"/>
+      <c r="A222" s="94"/>
       <c r="B222" s="5" t="s">
         <v>529</v>
       </c>
@@ -16106,7 +16106,7 @@
       <c r="F222" s="23"/>
     </row>
     <row r="223" spans="1:6" ht="31">
-      <c r="A223" s="92"/>
+      <c r="A223" s="94"/>
       <c r="B223" s="5" t="s">
         <v>531</v>
       </c>
@@ -16120,7 +16120,7 @@
       <c r="F223" s="23"/>
     </row>
     <row r="224" spans="1:6" ht="77.5">
-      <c r="A224" s="92"/>
+      <c r="A224" s="94"/>
       <c r="B224" s="5" t="s">
         <v>533</v>
       </c>
@@ -16136,7 +16136,7 @@
       <c r="F224" s="23"/>
     </row>
     <row r="225" spans="1:6" ht="15.5">
-      <c r="A225" s="92"/>
+      <c r="A225" s="94"/>
       <c r="B225" s="5" t="s">
         <v>535</v>
       </c>
@@ -16150,7 +16150,7 @@
       <c r="F225" s="23"/>
     </row>
     <row r="226" spans="1:6" ht="15.5">
-      <c r="A226" s="92"/>
+      <c r="A226" s="94"/>
       <c r="B226" s="5" t="s">
         <v>537</v>
       </c>
@@ -16164,7 +16164,7 @@
       <c r="F226" s="23"/>
     </row>
     <row r="227" spans="1:6" ht="31">
-      <c r="A227" s="92"/>
+      <c r="A227" s="94"/>
       <c r="B227" s="5" t="s">
         <v>539</v>
       </c>
@@ -16178,7 +16178,7 @@
       <c r="F227" s="23"/>
     </row>
     <row r="228" spans="1:6" ht="31">
-      <c r="A228" s="92"/>
+      <c r="A228" s="94"/>
       <c r="B228" s="5" t="s">
         <v>541</v>
       </c>
@@ -16192,7 +16192,7 @@
       <c r="F228" s="23"/>
     </row>
     <row r="229" spans="1:6" ht="15.5">
-      <c r="A229" s="92"/>
+      <c r="A229" s="94"/>
       <c r="B229" s="5" t="s">
         <v>543</v>
       </c>
@@ -16206,7 +16206,7 @@
       <c r="F229" s="23"/>
     </row>
     <row r="230" spans="1:6" ht="15.5">
-      <c r="A230" s="92"/>
+      <c r="A230" s="94"/>
       <c r="B230" s="5" t="s">
         <v>545</v>
       </c>
@@ -16220,7 +16220,7 @@
       <c r="F230" s="23"/>
     </row>
     <row r="231" spans="1:6" ht="228.75" customHeight="1">
-      <c r="A231" s="92"/>
+      <c r="A231" s="94"/>
       <c r="B231" s="5" t="s">
         <v>548</v>
       </c>
@@ -16236,7 +16236,7 @@
       <c r="F231" s="23"/>
     </row>
     <row r="232" spans="1:6" ht="77.5">
-      <c r="A232" s="92"/>
+      <c r="A232" s="94"/>
       <c r="B232" s="1" t="s">
         <v>550</v>
       </c>
@@ -16250,7 +16250,7 @@
       <c r="F232" s="23"/>
     </row>
     <row r="233" spans="1:6" ht="15.5">
-      <c r="A233" s="92"/>
+      <c r="A233" s="94"/>
       <c r="B233" s="5" t="s">
         <v>552</v>
       </c>
@@ -16264,7 +16264,7 @@
       <c r="F233" s="23"/>
     </row>
     <row r="234" spans="1:6" ht="15.5">
-      <c r="A234" s="92"/>
+      <c r="A234" s="94"/>
       <c r="B234" s="5" t="s">
         <v>554</v>
       </c>
@@ -16278,7 +16278,7 @@
       <c r="F234" s="23"/>
     </row>
     <row r="235" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A235" s="92"/>
+      <c r="A235" s="94"/>
       <c r="B235" s="5" t="s">
         <v>556</v>
       </c>
@@ -16292,7 +16292,7 @@
       <c r="F235" s="23"/>
     </row>
     <row r="236" spans="1:6" ht="156.75" customHeight="1">
-      <c r="A236" s="92"/>
+      <c r="A236" s="94"/>
       <c r="B236" s="5" t="s">
         <v>558</v>
       </c>
@@ -16308,7 +16308,7 @@
       <c r="F236" s="23"/>
     </row>
     <row r="237" spans="1:6" ht="93">
-      <c r="A237" s="92"/>
+      <c r="A237" s="94"/>
       <c r="B237" s="5" t="s">
         <v>560</v>
       </c>
@@ -16324,7 +16324,7 @@
       <c r="F237" s="23"/>
     </row>
     <row r="238" spans="1:6" ht="31">
-      <c r="A238" s="92"/>
+      <c r="A238" s="94"/>
       <c r="B238" s="5" t="s">
         <v>562</v>
       </c>
@@ -16338,7 +16338,7 @@
       <c r="F238" s="23"/>
     </row>
     <row r="239" spans="1:6" ht="31">
-      <c r="A239" s="92"/>
+      <c r="A239" s="94"/>
       <c r="B239" s="5" t="s">
         <v>565</v>
       </c>
@@ -16352,7 +16352,7 @@
       <c r="F239" s="23"/>
     </row>
     <row r="240" spans="1:6" ht="62">
-      <c r="A240" s="92"/>
+      <c r="A240" s="94"/>
       <c r="B240" s="5" t="s">
         <v>567</v>
       </c>
@@ -16366,7 +16366,7 @@
       <c r="F240" s="23"/>
     </row>
     <row r="241" spans="1:6" ht="56">
-      <c r="A241" s="92"/>
+      <c r="A241" s="94"/>
       <c r="B241" s="5" t="s">
         <v>569</v>
       </c>
@@ -16382,7 +16382,7 @@
       <c r="F241" s="23"/>
     </row>
     <row r="242" spans="1:6" ht="15.5">
-      <c r="A242" s="92"/>
+      <c r="A242" s="94"/>
       <c r="B242" s="5" t="s">
         <v>571</v>
       </c>
@@ -16396,7 +16396,7 @@
       <c r="F242" s="23"/>
     </row>
     <row r="243" spans="1:6" ht="31">
-      <c r="A243" s="92"/>
+      <c r="A243" s="94"/>
       <c r="B243" s="5" t="s">
         <v>574</v>
       </c>
@@ -16410,7 +16410,7 @@
       <c r="F243" s="23"/>
     </row>
     <row r="244" spans="1:6" ht="31">
-      <c r="A244" s="92"/>
+      <c r="A244" s="94"/>
       <c r="B244" s="5" t="s">
         <v>576</v>
       </c>
@@ -16424,7 +16424,7 @@
       <c r="F244" s="23"/>
     </row>
     <row r="245" spans="1:6" ht="31">
-      <c r="A245" s="92"/>
+      <c r="A245" s="94"/>
       <c r="B245" s="5" t="s">
         <v>578</v>
       </c>
@@ -16438,7 +16438,7 @@
       <c r="F245" s="23"/>
     </row>
     <row r="246" spans="1:6" ht="56">
-      <c r="A246" s="92"/>
+      <c r="A246" s="94"/>
       <c r="B246" s="5" t="s">
         <v>580</v>
       </c>
@@ -16454,7 +16454,7 @@
       <c r="F246" s="23"/>
     </row>
     <row r="247" spans="1:6" ht="56">
-      <c r="A247" s="92"/>
+      <c r="A247" s="94"/>
       <c r="B247" s="5" t="s">
         <v>582</v>
       </c>
@@ -16470,7 +16470,7 @@
       <c r="F247" s="23"/>
     </row>
     <row r="248" spans="1:6" ht="28">
-      <c r="A248" s="92"/>
+      <c r="A248" s="94"/>
       <c r="B248" s="5" t="s">
         <v>584</v>
       </c>
@@ -16484,7 +16484,7 @@
       <c r="F248" s="23"/>
     </row>
     <row r="249" spans="1:6" ht="31">
-      <c r="A249" s="92"/>
+      <c r="A249" s="94"/>
       <c r="B249" s="5" t="s">
         <v>586</v>
       </c>
@@ -16498,7 +16498,7 @@
       <c r="F249" s="23"/>
     </row>
     <row r="250" spans="1:6" ht="31">
-      <c r="A250" s="92"/>
+      <c r="A250" s="94"/>
       <c r="B250" s="5" t="s">
         <v>588</v>
       </c>
@@ -16512,7 +16512,7 @@
       <c r="F250" s="23"/>
     </row>
     <row r="251" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A251" s="92"/>
+      <c r="A251" s="94"/>
       <c r="B251" s="5" t="s">
         <v>590</v>
       </c>
@@ -16526,7 +16526,7 @@
       <c r="F251" s="23"/>
     </row>
     <row r="252" spans="1:6" ht="31">
-      <c r="A252" s="92"/>
+      <c r="A252" s="94"/>
       <c r="B252" s="5" t="s">
         <v>592</v>
       </c>
@@ -16540,7 +16540,7 @@
       <c r="F252" s="23"/>
     </row>
     <row r="253" spans="1:6" ht="15.5">
-      <c r="A253" s="92"/>
+      <c r="A253" s="94"/>
       <c r="B253" s="5" t="s">
         <v>594</v>
       </c>
@@ -16554,7 +16554,7 @@
       <c r="F253" s="23"/>
     </row>
     <row r="254" spans="1:6" ht="31">
-      <c r="A254" s="92"/>
+      <c r="A254" s="94"/>
       <c r="B254" s="5" t="s">
         <v>596</v>
       </c>
@@ -16568,7 +16568,7 @@
       <c r="F254" s="23"/>
     </row>
     <row r="255" spans="1:6" ht="31">
-      <c r="A255" s="92"/>
+      <c r="A255" s="94"/>
       <c r="B255" s="5" t="s">
         <v>598</v>
       </c>
@@ -16582,7 +16582,7 @@
       <c r="F255" s="23"/>
     </row>
     <row r="256" spans="1:6" ht="31">
-      <c r="A256" s="92"/>
+      <c r="A256" s="94"/>
       <c r="B256" s="5" t="s">
         <v>600</v>
       </c>
@@ -16596,7 +16596,7 @@
       <c r="F256" s="23"/>
     </row>
     <row r="257" spans="1:6" ht="15.5">
-      <c r="A257" s="92"/>
+      <c r="A257" s="94"/>
       <c r="B257" s="5" t="s">
         <v>602</v>
       </c>
@@ -16610,7 +16610,7 @@
       <c r="F257" s="23"/>
     </row>
     <row r="258" spans="1:6" ht="28">
-      <c r="A258" s="92"/>
+      <c r="A258" s="94"/>
       <c r="B258" s="5" t="s">
         <v>604</v>
       </c>
@@ -16624,7 +16624,7 @@
       <c r="F258" s="23"/>
     </row>
     <row r="259" spans="1:6" ht="87.75" customHeight="1">
-      <c r="A259" s="92"/>
+      <c r="A259" s="94"/>
       <c r="B259" s="5" t="s">
         <v>606</v>
       </c>
@@ -16638,7 +16638,7 @@
       <c r="F259" s="23"/>
     </row>
     <row r="260" spans="1:6" ht="195" customHeight="1">
-      <c r="A260" s="92"/>
+      <c r="A260" s="94"/>
       <c r="B260" s="5" t="s">
         <v>609</v>
       </c>
@@ -16652,7 +16652,7 @@
       <c r="F260" s="23"/>
     </row>
     <row r="261" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A261" s="92"/>
+      <c r="A261" s="94"/>
       <c r="B261" s="5" t="s">
         <v>611</v>
       </c>
@@ -16666,7 +16666,7 @@
       <c r="F261" s="23"/>
     </row>
     <row r="262" spans="1:6" ht="46.5">
-      <c r="A262" s="92"/>
+      <c r="A262" s="94"/>
       <c r="B262" s="5" t="s">
         <v>613</v>
       </c>
@@ -16680,7 +16680,7 @@
       <c r="F262" s="23"/>
     </row>
     <row r="263" spans="1:6" ht="30" customHeight="1">
-      <c r="A263" s="92"/>
+      <c r="A263" s="94"/>
       <c r="B263" s="5" t="s">
         <v>615</v>
       </c>
@@ -16694,7 +16694,7 @@
       <c r="F263" s="23"/>
     </row>
     <row r="264" spans="1:6" ht="15.5">
-      <c r="A264" s="92"/>
+      <c r="A264" s="94"/>
       <c r="B264" s="5" t="s">
         <v>617</v>
       </c>
@@ -16708,7 +16708,7 @@
       <c r="F264" s="23"/>
     </row>
     <row r="265" spans="1:6" ht="31">
-      <c r="A265" s="92"/>
+      <c r="A265" s="94"/>
       <c r="B265" s="5" t="s">
         <v>619</v>
       </c>
@@ -16722,7 +16722,7 @@
       <c r="F265" s="23"/>
     </row>
     <row r="266" spans="1:6" ht="56">
-      <c r="A266" s="92"/>
+      <c r="A266" s="94"/>
       <c r="B266" s="5" t="s">
         <v>621</v>
       </c>
@@ -16738,7 +16738,7 @@
       <c r="F266" s="23"/>
     </row>
     <row r="267" spans="1:6" ht="119.25" customHeight="1">
-      <c r="A267" s="92"/>
+      <c r="A267" s="94"/>
       <c r="B267" s="5" t="s">
         <v>624</v>
       </c>
@@ -16754,7 +16754,7 @@
       <c r="F267" s="23"/>
     </row>
     <row r="268" spans="1:6" ht="31">
-      <c r="A268" s="92"/>
+      <c r="A268" s="94"/>
       <c r="B268" s="5" t="s">
         <v>626</v>
       </c>
@@ -16768,7 +16768,7 @@
       <c r="F268" s="23"/>
     </row>
     <row r="269" spans="1:6" ht="31">
-      <c r="A269" s="92"/>
+      <c r="A269" s="94"/>
       <c r="B269" s="5" t="s">
         <v>628</v>
       </c>
@@ -16782,7 +16782,7 @@
       <c r="F269" s="23"/>
     </row>
     <row r="270" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A270" s="92"/>
+      <c r="A270" s="94"/>
       <c r="B270" s="5" t="s">
         <v>630</v>
       </c>
@@ -16796,7 +16796,7 @@
       <c r="F270" s="23"/>
     </row>
     <row r="271" spans="1:6" ht="42">
-      <c r="A271" s="92"/>
+      <c r="A271" s="94"/>
       <c r="B271" s="5" t="s">
         <v>632</v>
       </c>
@@ -16812,7 +16812,7 @@
       <c r="F271" s="23"/>
     </row>
     <row r="272" spans="1:6" ht="55.5" customHeight="1">
-      <c r="A272" s="92"/>
+      <c r="A272" s="94"/>
       <c r="B272" s="5" t="s">
         <v>634</v>
       </c>
@@ -16826,7 +16826,7 @@
       <c r="F272" s="23"/>
     </row>
     <row r="273" spans="1:6" ht="61.5" customHeight="1">
-      <c r="A273" s="92"/>
+      <c r="A273" s="94"/>
       <c r="B273" s="5" t="s">
         <v>636</v>
       </c>
@@ -16840,7 +16840,7 @@
       <c r="F273" s="23"/>
     </row>
     <row r="274" spans="1:6" ht="62.25" customHeight="1">
-      <c r="A274" s="92"/>
+      <c r="A274" s="94"/>
       <c r="B274" s="5" t="s">
         <v>639</v>
       </c>
@@ -16854,7 +16854,7 @@
       <c r="F274" s="23"/>
     </row>
     <row r="275" spans="1:6" ht="43.5" customHeight="1">
-      <c r="A275" s="92"/>
+      <c r="A275" s="94"/>
       <c r="B275" s="5" t="s">
         <v>641</v>
       </c>
@@ -16870,7 +16870,7 @@
       <c r="F275" s="23"/>
     </row>
     <row r="276" spans="1:6" ht="63" customHeight="1">
-      <c r="A276" s="92"/>
+      <c r="A276" s="94"/>
       <c r="B276" s="5" t="s">
         <v>643</v>
       </c>
@@ -16884,7 +16884,7 @@
       <c r="F276" s="23"/>
     </row>
     <row r="277" spans="1:6" ht="72.75" customHeight="1">
-      <c r="A277" s="92"/>
+      <c r="A277" s="94"/>
       <c r="B277" s="5" t="s">
         <v>645</v>
       </c>
@@ -16898,7 +16898,7 @@
       <c r="F277" s="23"/>
     </row>
     <row r="278" spans="1:6" ht="73.5" customHeight="1">
-      <c r="A278" s="92"/>
+      <c r="A278" s="94"/>
       <c r="B278" s="5" t="s">
         <v>647</v>
       </c>
@@ -16914,7 +16914,7 @@
       <c r="F278" s="23"/>
     </row>
     <row r="279" spans="1:6" ht="56">
-      <c r="A279" s="92"/>
+      <c r="A279" s="94"/>
       <c r="B279" s="5" t="s">
         <v>650</v>
       </c>
@@ -16930,7 +16930,7 @@
       <c r="F279" s="23"/>
     </row>
     <row r="280" spans="1:6" ht="42" customHeight="1">
-      <c r="A280" s="92"/>
+      <c r="A280" s="94"/>
       <c r="B280" s="5" t="s">
         <v>653</v>
       </c>
@@ -16944,7 +16944,7 @@
       <c r="F280" s="23"/>
     </row>
     <row r="281" spans="1:6" ht="31">
-      <c r="A281" s="92"/>
+      <c r="A281" s="94"/>
       <c r="B281" s="5" t="s">
         <v>655</v>
       </c>
@@ -16958,7 +16958,7 @@
       <c r="F281" s="23"/>
     </row>
     <row r="282" spans="1:6" ht="108.75" customHeight="1">
-      <c r="A282" s="92"/>
+      <c r="A282" s="94"/>
       <c r="B282" s="5" t="s">
         <v>657</v>
       </c>
@@ -16974,7 +16974,7 @@
       <c r="F282" s="23"/>
     </row>
     <row r="283" spans="1:6" ht="185.25" customHeight="1">
-      <c r="A283" s="92"/>
+      <c r="A283" s="94"/>
       <c r="B283" s="5" t="s">
         <v>659</v>
       </c>
@@ -16990,7 +16990,7 @@
       <c r="F283" s="23"/>
     </row>
     <row r="284" spans="1:6" ht="77.25" customHeight="1">
-      <c r="A284" s="92"/>
+      <c r="A284" s="94"/>
       <c r="B284" s="5" t="s">
         <v>661</v>
       </c>
@@ -17006,7 +17006,7 @@
       <c r="F284" s="23"/>
     </row>
     <row r="285" spans="1:6" ht="65.25" customHeight="1">
-      <c r="A285" s="92"/>
+      <c r="A285" s="94"/>
       <c r="B285" s="5" t="s">
         <v>663</v>
       </c>
@@ -17022,7 +17022,7 @@
       <c r="F285" s="23"/>
     </row>
     <row r="286" spans="1:6" ht="76.5" customHeight="1">
-      <c r="A286" s="92"/>
+      <c r="A286" s="94"/>
       <c r="B286" s="5" t="s">
         <v>665</v>
       </c>
@@ -17036,7 +17036,7 @@
       <c r="F286" s="23"/>
     </row>
     <row r="287" spans="1:6" ht="108.5">
-      <c r="A287" s="92"/>
+      <c r="A287" s="94"/>
       <c r="B287" s="5" t="s">
         <v>667</v>
       </c>
@@ -17050,7 +17050,7 @@
       <c r="F287" s="23"/>
     </row>
     <row r="288" spans="1:6" ht="42">
-      <c r="A288" s="92"/>
+      <c r="A288" s="94"/>
       <c r="B288" s="5" t="s">
         <v>669</v>
       </c>
@@ -17064,7 +17064,7 @@
       <c r="F288" s="23"/>
     </row>
     <row r="289" spans="1:6" ht="93">
-      <c r="A289" s="92"/>
+      <c r="A289" s="94"/>
       <c r="B289" s="5" t="s">
         <v>671</v>
       </c>
@@ -17080,7 +17080,7 @@
       <c r="F289" s="23"/>
     </row>
     <row r="290" spans="1:6" ht="89.25" customHeight="1">
-      <c r="A290" s="92"/>
+      <c r="A290" s="94"/>
       <c r="B290" s="5" t="s">
         <v>673</v>
       </c>
@@ -17096,7 +17096,7 @@
       <c r="F290" s="23"/>
     </row>
     <row r="291" spans="1:6" ht="62">
-      <c r="A291" s="92"/>
+      <c r="A291" s="94"/>
       <c r="B291" s="5" t="s">
         <v>675</v>
       </c>
@@ -17110,7 +17110,7 @@
       <c r="F291" s="23"/>
     </row>
     <row r="292" spans="1:6" ht="31">
-      <c r="A292" s="92"/>
+      <c r="A292" s="94"/>
       <c r="B292" s="5" t="s">
         <v>677</v>
       </c>
@@ -17124,7 +17124,7 @@
       <c r="F292" s="23"/>
     </row>
     <row r="293" spans="1:6" ht="28">
-      <c r="A293" s="92"/>
+      <c r="A293" s="94"/>
       <c r="B293" s="5" t="s">
         <v>680</v>
       </c>
@@ -17138,7 +17138,7 @@
       <c r="F293" s="23"/>
     </row>
     <row r="294" spans="1:6" ht="114.75" customHeight="1">
-      <c r="A294" s="92"/>
+      <c r="A294" s="94"/>
       <c r="B294" s="5" t="s">
         <v>681</v>
       </c>
@@ -17152,7 +17152,7 @@
       <c r="F294" s="23"/>
     </row>
     <row r="295" spans="1:6" ht="121.5" customHeight="1">
-      <c r="A295" s="92"/>
+      <c r="A295" s="94"/>
       <c r="B295" s="5" t="s">
         <v>684</v>
       </c>
@@ -17166,7 +17166,7 @@
       <c r="F295" s="23"/>
     </row>
     <row r="296" spans="1:6" ht="183" customHeight="1">
-      <c r="A296" s="92"/>
+      <c r="A296" s="94"/>
       <c r="B296" s="5" t="s">
         <v>686</v>
       </c>
@@ -17182,7 +17182,7 @@
       <c r="F296" s="23"/>
     </row>
     <row r="297" spans="1:6" ht="130.5" customHeight="1">
-      <c r="A297" s="92"/>
+      <c r="A297" s="94"/>
       <c r="B297" s="5" t="s">
         <v>688</v>
       </c>
@@ -17196,7 +17196,7 @@
       <c r="F297" s="23"/>
     </row>
     <row r="298" spans="1:6" ht="42.75" customHeight="1">
-      <c r="A298" s="105" t="s">
+      <c r="A298" s="95" t="s">
         <v>690</v>
       </c>
       <c r="B298" s="1" t="s">
@@ -17212,7 +17212,7 @@
       <c r="F298" s="23"/>
     </row>
     <row r="299" spans="1:6" ht="93.75" customHeight="1">
-      <c r="A299" s="91"/>
+      <c r="A299" s="92"/>
       <c r="B299" s="5" t="s">
         <v>694</v>
       </c>
@@ -17228,7 +17228,7 @@
       <c r="F299" s="23"/>
     </row>
     <row r="300" spans="1:6" ht="108" customHeight="1">
-      <c r="A300" s="91"/>
+      <c r="A300" s="92"/>
       <c r="B300" s="5" t="s">
         <v>696</v>
       </c>
@@ -17244,7 +17244,7 @@
       <c r="F300" s="23"/>
     </row>
     <row r="301" spans="1:6" ht="31">
-      <c r="A301" s="91"/>
+      <c r="A301" s="92"/>
       <c r="B301" s="5" t="s">
         <v>699</v>
       </c>
@@ -17260,7 +17260,7 @@
       <c r="F301" s="23"/>
     </row>
     <row r="302" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A302" s="91"/>
+      <c r="A302" s="92"/>
       <c r="B302" s="5" t="s">
         <v>701</v>
       </c>
@@ -17274,7 +17274,7 @@
       <c r="F302" s="23"/>
     </row>
     <row r="303" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A303" s="91"/>
+      <c r="A303" s="92"/>
       <c r="B303" s="5" t="s">
         <v>703</v>
       </c>
@@ -17290,7 +17290,7 @@
       <c r="F303" s="23"/>
     </row>
     <row r="304" spans="1:6" ht="91.5" customHeight="1">
-      <c r="A304" s="91"/>
+      <c r="A304" s="92"/>
       <c r="B304" s="5" t="s">
         <v>707</v>
       </c>
@@ -17306,7 +17306,7 @@
       <c r="F304" s="23"/>
     </row>
     <row r="305" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A305" s="91"/>
+      <c r="A305" s="92"/>
       <c r="B305" s="5" t="s">
         <v>709</v>
       </c>
@@ -17320,7 +17320,7 @@
       <c r="F305" s="23"/>
     </row>
     <row r="306" spans="1:6" ht="76.5" customHeight="1">
-      <c r="A306" s="91"/>
+      <c r="A306" s="92"/>
       <c r="B306" s="5" t="s">
         <v>711</v>
       </c>
@@ -17336,7 +17336,7 @@
       <c r="F306" s="23"/>
     </row>
     <row r="307" spans="1:6" ht="42">
-      <c r="A307" s="91"/>
+      <c r="A307" s="92"/>
       <c r="B307" s="5" t="s">
         <v>713</v>
       </c>
@@ -17352,7 +17352,7 @@
       <c r="F307" s="23"/>
     </row>
     <row r="308" spans="1:6" ht="46.5">
-      <c r="A308" s="91"/>
+      <c r="A308" s="92"/>
       <c r="B308" s="5" t="s">
         <v>715</v>
       </c>
@@ -17368,7 +17368,7 @@
       <c r="F308" s="23"/>
     </row>
     <row r="309" spans="1:6" ht="46.5">
-      <c r="A309" s="91"/>
+      <c r="A309" s="92"/>
       <c r="B309" s="5" t="s">
         <v>718</v>
       </c>
@@ -17384,7 +17384,7 @@
       <c r="F309" s="23"/>
     </row>
     <row r="310" spans="1:6" ht="105.75" customHeight="1">
-      <c r="A310" s="91"/>
+      <c r="A310" s="92"/>
       <c r="B310" s="5" t="s">
         <v>719</v>
       </c>
@@ -17398,7 +17398,7 @@
       <c r="F310" s="23"/>
     </row>
     <row r="311" spans="1:6" ht="93">
-      <c r="A311" s="91"/>
+      <c r="A311" s="92"/>
       <c r="B311" s="5" t="s">
         <v>721</v>
       </c>
@@ -17414,7 +17414,7 @@
       <c r="F311" s="23"/>
     </row>
     <row r="312" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A312" s="91"/>
+      <c r="A312" s="92"/>
       <c r="B312" s="5" t="s">
         <v>723</v>
       </c>
@@ -17428,7 +17428,7 @@
       <c r="F312" s="23"/>
     </row>
     <row r="313" spans="1:6" ht="15.5">
-      <c r="A313" s="91"/>
+      <c r="A313" s="92"/>
       <c r="B313" s="5" t="s">
         <v>725</v>
       </c>
@@ -17442,7 +17442,7 @@
       <c r="F313" s="23"/>
     </row>
     <row r="314" spans="1:6" ht="31">
-      <c r="A314" s="91"/>
+      <c r="A314" s="92"/>
       <c r="B314" s="5" t="s">
         <v>727</v>
       </c>
@@ -17456,7 +17456,7 @@
       <c r="F314" s="23"/>
     </row>
     <row r="315" spans="1:6" ht="62">
-      <c r="A315" s="91"/>
+      <c r="A315" s="92"/>
       <c r="B315" s="5" t="s">
         <v>729</v>
       </c>
@@ -17472,7 +17472,7 @@
       <c r="F315" s="23"/>
     </row>
     <row r="316" spans="1:6" ht="36" customHeight="1">
-      <c r="A316" s="91"/>
+      <c r="A316" s="92"/>
       <c r="B316" s="5" t="s">
         <v>731</v>
       </c>
@@ -17486,7 +17486,7 @@
       <c r="F316" s="23"/>
     </row>
     <row r="317" spans="1:6" ht="30" customHeight="1">
-      <c r="A317" s="91"/>
+      <c r="A317" s="92"/>
       <c r="B317" s="5" t="s">
         <v>733</v>
       </c>
@@ -17500,7 +17500,7 @@
       <c r="F317" s="23"/>
     </row>
     <row r="318" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A318" s="91"/>
+      <c r="A318" s="92"/>
       <c r="B318" s="5" t="s">
         <v>736</v>
       </c>
@@ -17514,7 +17514,7 @@
       <c r="F318" s="23"/>
     </row>
     <row r="319" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A319" s="91"/>
+      <c r="A319" s="92"/>
       <c r="B319" s="5" t="s">
         <v>739</v>
       </c>
@@ -17530,7 +17530,7 @@
       <c r="F319" s="23"/>
     </row>
     <row r="320" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A320" s="91"/>
+      <c r="A320" s="92"/>
       <c r="B320" s="5" t="s">
         <v>741</v>
       </c>
@@ -17544,7 +17544,7 @@
       <c r="F320" s="23"/>
     </row>
     <row r="321" spans="1:6" ht="31">
-      <c r="A321" s="91"/>
+      <c r="A321" s="92"/>
       <c r="B321" s="5" t="s">
         <v>743</v>
       </c>
@@ -17558,7 +17558,7 @@
       <c r="F321" s="23"/>
     </row>
     <row r="322" spans="1:6" ht="57" customHeight="1">
-      <c r="A322" s="91"/>
+      <c r="A322" s="92"/>
       <c r="B322" s="5" t="s">
         <v>745</v>
       </c>
@@ -17574,7 +17574,7 @@
       <c r="F322" s="23"/>
     </row>
     <row r="323" spans="1:6" ht="45" customHeight="1">
-      <c r="A323" s="91"/>
+      <c r="A323" s="92"/>
       <c r="B323" s="5" t="s">
         <v>747</v>
       </c>
@@ -17590,7 +17590,7 @@
       <c r="F323" s="23"/>
     </row>
     <row r="324" spans="1:6" ht="31">
-      <c r="A324" s="91"/>
+      <c r="A324" s="92"/>
       <c r="B324" s="5" t="s">
         <v>749</v>
       </c>
@@ -17604,7 +17604,7 @@
       <c r="F324" s="23"/>
     </row>
     <row r="325" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A325" s="91"/>
+      <c r="A325" s="92"/>
       <c r="B325" s="5" t="s">
         <v>751</v>
       </c>
@@ -17618,7 +17618,7 @@
       <c r="F325" s="23"/>
     </row>
     <row r="326" spans="1:6" ht="27" customHeight="1">
-      <c r="A326" s="91"/>
+      <c r="A326" s="92"/>
       <c r="B326" s="5" t="s">
         <v>753</v>
       </c>
@@ -17632,7 +17632,7 @@
       <c r="F326" s="23"/>
     </row>
     <row r="327" spans="1:6" ht="64.5" customHeight="1">
-      <c r="A327" s="91"/>
+      <c r="A327" s="92"/>
       <c r="B327" s="5" t="s">
         <v>755</v>
       </c>
@@ -17648,7 +17648,7 @@
       <c r="F327" s="23"/>
     </row>
     <row r="328" spans="1:6" ht="124.5" customHeight="1">
-      <c r="A328" s="91"/>
+      <c r="A328" s="92"/>
       <c r="B328" s="5" t="s">
         <v>757</v>
       </c>
@@ -17664,7 +17664,7 @@
       <c r="F328" s="23"/>
     </row>
     <row r="329" spans="1:6" ht="50.25" customHeight="1">
-      <c r="A329" s="91"/>
+      <c r="A329" s="92"/>
       <c r="B329" s="1" t="s">
         <v>760</v>
       </c>
@@ -17680,7 +17680,7 @@
       <c r="F329" s="23"/>
     </row>
     <row r="330" spans="1:6" ht="42">
-      <c r="A330" s="91"/>
+      <c r="A330" s="92"/>
       <c r="B330" s="5" t="s">
         <v>762</v>
       </c>
@@ -17696,7 +17696,7 @@
       <c r="F330" s="23"/>
     </row>
     <row r="331" spans="1:6" ht="43.5" customHeight="1">
-      <c r="A331" s="91"/>
+      <c r="A331" s="92"/>
       <c r="B331" s="5" t="s">
         <v>764</v>
       </c>
@@ -17710,7 +17710,7 @@
       <c r="F331" s="23"/>
     </row>
     <row r="332" spans="1:6" ht="46.5">
-      <c r="A332" s="91"/>
+      <c r="A332" s="92"/>
       <c r="B332" s="5" t="s">
         <v>766</v>
       </c>
@@ -17722,7 +17722,7 @@
       <c r="F332" s="23"/>
     </row>
     <row r="333" spans="1:6" ht="56">
-      <c r="A333" s="91"/>
+      <c r="A333" s="92"/>
       <c r="B333" s="1" t="s">
         <v>768</v>
       </c>
@@ -17738,7 +17738,7 @@
       <c r="F333" s="23"/>
     </row>
     <row r="334" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A334" s="91"/>
+      <c r="A334" s="92"/>
       <c r="B334" s="5" t="s">
         <v>770</v>
       </c>
@@ -17750,7 +17750,7 @@
       <c r="F334" s="23"/>
     </row>
     <row r="335" spans="1:6" ht="62">
-      <c r="A335" s="91"/>
+      <c r="A335" s="92"/>
       <c r="B335" s="5" t="s">
         <v>772</v>
       </c>
@@ -17764,7 +17764,7 @@
       <c r="F335" s="23"/>
     </row>
     <row r="336" spans="1:6" ht="115.5" customHeight="1">
-      <c r="A336" s="91"/>
+      <c r="A336" s="92"/>
       <c r="B336" s="5" t="s">
         <v>775</v>
       </c>
@@ -17780,7 +17780,7 @@
       <c r="F336" s="23"/>
     </row>
     <row r="337" spans="1:6" ht="31">
-      <c r="A337" s="91"/>
+      <c r="A337" s="92"/>
       <c r="B337" s="5" t="s">
         <v>777</v>
       </c>
@@ -17794,7 +17794,7 @@
       <c r="F337" s="23"/>
     </row>
     <row r="338" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A338" s="91"/>
+      <c r="A338" s="92"/>
       <c r="B338" s="5" t="s">
         <v>779</v>
       </c>
@@ -17808,7 +17808,7 @@
       <c r="F338" s="23"/>
     </row>
     <row r="339" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A339" s="91"/>
+      <c r="A339" s="92"/>
       <c r="B339" s="5" t="s">
         <v>782</v>
       </c>
@@ -17824,7 +17824,7 @@
       <c r="F339" s="23"/>
     </row>
     <row r="340" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A340" s="91"/>
+      <c r="A340" s="92"/>
       <c r="B340" s="5" t="s">
         <v>785</v>
       </c>
@@ -17838,7 +17838,7 @@
       <c r="F340" s="23"/>
     </row>
     <row r="341" spans="1:6" ht="15.5">
-      <c r="A341" s="91"/>
+      <c r="A341" s="92"/>
       <c r="B341" s="5" t="s">
         <v>787</v>
       </c>
@@ -17852,7 +17852,7 @@
       <c r="F341" s="23"/>
     </row>
     <row r="342" spans="1:6" ht="31">
-      <c r="A342" s="91"/>
+      <c r="A342" s="92"/>
       <c r="B342" s="5" t="s">
         <v>789</v>
       </c>
@@ -17866,7 +17866,7 @@
       <c r="F342" s="23"/>
     </row>
     <row r="343" spans="1:6" ht="15.5">
-      <c r="A343" s="91"/>
+      <c r="A343" s="92"/>
       <c r="B343" s="5" t="s">
         <v>791</v>
       </c>
@@ -17880,7 +17880,7 @@
       <c r="F343" s="23"/>
     </row>
     <row r="344" spans="1:6" ht="31">
-      <c r="A344" s="91"/>
+      <c r="A344" s="92"/>
       <c r="B344" s="5" t="s">
         <v>793</v>
       </c>
@@ -17894,7 +17894,7 @@
       <c r="F344" s="23"/>
     </row>
     <row r="345" spans="1:6" ht="195" customHeight="1">
-      <c r="A345" s="91"/>
+      <c r="A345" s="92"/>
       <c r="B345" s="5" t="s">
         <v>795</v>
       </c>
@@ -17908,7 +17908,7 @@
       <c r="F345" s="23"/>
     </row>
     <row r="346" spans="1:6" ht="56">
-      <c r="A346" s="91"/>
+      <c r="A346" s="92"/>
       <c r="B346" s="5" t="s">
         <v>798</v>
       </c>
@@ -17924,7 +17924,7 @@
       <c r="F346" s="23"/>
     </row>
     <row r="347" spans="1:6" ht="75.75" customHeight="1">
-      <c r="A347" s="91"/>
+      <c r="A347" s="92"/>
       <c r="B347" s="5" t="s">
         <v>800</v>
       </c>
@@ -17940,7 +17940,7 @@
       <c r="F347" s="23"/>
     </row>
     <row r="348" spans="1:6" ht="77.5">
-      <c r="A348" s="91"/>
+      <c r="A348" s="92"/>
       <c r="B348" s="5" t="s">
         <v>802</v>
       </c>
@@ -17956,7 +17956,7 @@
       <c r="F348" s="23"/>
     </row>
     <row r="349" spans="1:6" ht="42">
-      <c r="A349" s="91"/>
+      <c r="A349" s="92"/>
       <c r="B349" s="5" t="s">
         <v>804</v>
       </c>
@@ -17972,7 +17972,7 @@
       <c r="F349" s="23"/>
     </row>
     <row r="350" spans="1:6" ht="93">
-      <c r="A350" s="91"/>
+      <c r="A350" s="92"/>
       <c r="B350" s="5" t="s">
         <v>806</v>
       </c>
@@ -17986,7 +17986,7 @@
       <c r="F350" s="23"/>
     </row>
     <row r="351" spans="1:6" ht="46.5">
-      <c r="A351" s="91"/>
+      <c r="A351" s="92"/>
       <c r="B351" s="5" t="s">
         <v>809</v>
       </c>
@@ -18000,7 +18000,7 @@
       <c r="F351" s="23"/>
     </row>
     <row r="352" spans="1:6" ht="31">
-      <c r="A352" s="91"/>
+      <c r="A352" s="92"/>
       <c r="B352" s="5" t="s">
         <v>811</v>
       </c>
@@ -18014,7 +18014,7 @@
       <c r="F352" s="23"/>
     </row>
     <row r="353" spans="1:6" ht="82.5" customHeight="1">
-      <c r="A353" s="91"/>
+      <c r="A353" s="92"/>
       <c r="B353" s="1" t="s">
         <v>814</v>
       </c>
@@ -18028,7 +18028,7 @@
       <c r="F353" s="23"/>
     </row>
     <row r="354" spans="1:6" ht="48.75" customHeight="1">
-      <c r="A354" s="91"/>
+      <c r="A354" s="92"/>
       <c r="B354" s="5" t="s">
         <v>816</v>
       </c>
@@ -18042,7 +18042,7 @@
       <c r="F354" s="23"/>
     </row>
     <row r="355" spans="1:6" ht="31">
-      <c r="A355" s="91"/>
+      <c r="A355" s="92"/>
       <c r="B355" s="5" t="s">
         <v>819</v>
       </c>
@@ -18056,7 +18056,7 @@
       <c r="F355" s="23"/>
     </row>
     <row r="356" spans="1:6" ht="31">
-      <c r="A356" s="91"/>
+      <c r="A356" s="92"/>
       <c r="B356" s="5" t="s">
         <v>821</v>
       </c>
@@ -18070,7 +18070,7 @@
       <c r="F356" s="23"/>
     </row>
     <row r="357" spans="1:6" ht="106.5" customHeight="1">
-      <c r="A357" s="91"/>
+      <c r="A357" s="92"/>
       <c r="B357" s="5" t="s">
         <v>823</v>
       </c>
@@ -18086,7 +18086,7 @@
       <c r="F357" s="23"/>
     </row>
     <row r="358" spans="1:6" ht="56">
-      <c r="A358" s="91"/>
+      <c r="A358" s="92"/>
       <c r="B358" s="5" t="s">
         <v>825</v>
       </c>
@@ -18102,7 +18102,7 @@
       <c r="F358" s="23"/>
     </row>
     <row r="359" spans="1:6" ht="152.25" customHeight="1">
-      <c r="A359" s="91"/>
+      <c r="A359" s="92"/>
       <c r="B359" s="5" t="s">
         <v>827</v>
       </c>
@@ -18116,7 +18116,7 @@
       <c r="F359" s="23"/>
     </row>
     <row r="360" spans="1:6" ht="15.5">
-      <c r="A360" s="91"/>
+      <c r="A360" s="92"/>
       <c r="B360" s="5" t="s">
         <v>829</v>
       </c>
@@ -18130,7 +18130,7 @@
       <c r="F360" s="23"/>
     </row>
     <row r="361" spans="1:6" ht="42" customHeight="1">
-      <c r="A361" s="91"/>
+      <c r="A361" s="92"/>
       <c r="B361" s="5" t="s">
         <v>831</v>
       </c>
@@ -18144,7 +18144,7 @@
       <c r="F361" s="23"/>
     </row>
     <row r="362" spans="1:6" ht="108.5">
-      <c r="A362" s="91"/>
+      <c r="A362" s="92"/>
       <c r="B362" s="5" t="s">
         <v>833</v>
       </c>
@@ -18158,7 +18158,7 @@
       <c r="F362" s="23"/>
     </row>
     <row r="363" spans="1:6" ht="42">
-      <c r="A363" s="91"/>
+      <c r="A363" s="92"/>
       <c r="B363" s="5" t="s">
         <v>835</v>
       </c>
@@ -18174,7 +18174,7 @@
       <c r="F363" s="23"/>
     </row>
     <row r="364" spans="1:6" ht="42">
-      <c r="A364" s="91"/>
+      <c r="A364" s="92"/>
       <c r="B364" s="5" t="s">
         <v>837</v>
       </c>
@@ -18190,7 +18190,7 @@
       <c r="F364" s="23"/>
     </row>
     <row r="365" spans="1:6" ht="165" customHeight="1">
-      <c r="A365" s="91"/>
+      <c r="A365" s="92"/>
       <c r="B365" s="5" t="s">
         <v>839</v>
       </c>
@@ -18204,7 +18204,7 @@
       <c r="F365" s="23"/>
     </row>
     <row r="366" spans="1:6" ht="31">
-      <c r="A366" s="91"/>
+      <c r="A366" s="92"/>
       <c r="B366" s="5" t="s">
         <v>841</v>
       </c>
@@ -18218,7 +18218,7 @@
       <c r="F366" s="23"/>
     </row>
     <row r="367" spans="1:6" ht="63.75" customHeight="1">
-      <c r="A367" s="91"/>
+      <c r="A367" s="92"/>
       <c r="B367" s="5" t="s">
         <v>843</v>
       </c>
@@ -18234,7 +18234,7 @@
       <c r="F367" s="23"/>
     </row>
     <row r="368" spans="1:6" ht="31">
-      <c r="A368" s="91"/>
+      <c r="A368" s="92"/>
       <c r="B368" s="5" t="s">
         <v>845</v>
       </c>
@@ -18250,7 +18250,7 @@
       <c r="F368" s="23"/>
     </row>
     <row r="369" spans="1:6" ht="56">
-      <c r="A369" s="91"/>
+      <c r="A369" s="92"/>
       <c r="B369" s="5" t="s">
         <v>847</v>
       </c>
@@ -18266,7 +18266,7 @@
       <c r="F369" s="23"/>
     </row>
     <row r="370" spans="1:6" ht="93.75" customHeight="1">
-      <c r="A370" s="91"/>
+      <c r="A370" s="92"/>
       <c r="B370" s="5" t="s">
         <v>849</v>
       </c>
@@ -18282,7 +18282,7 @@
       <c r="F370" s="23"/>
     </row>
     <row r="371" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A371" s="91"/>
+      <c r="A371" s="92"/>
       <c r="B371" s="5" t="s">
         <v>852</v>
       </c>
@@ -18298,7 +18298,7 @@
       <c r="F371" s="23"/>
     </row>
     <row r="372" spans="1:6" ht="15.5">
-      <c r="A372" s="91"/>
+      <c r="A372" s="92"/>
       <c r="B372" s="5" t="s">
         <v>854</v>
       </c>
@@ -18312,7 +18312,7 @@
       <c r="F372" s="23"/>
     </row>
     <row r="373" spans="1:6" ht="47.25" customHeight="1">
-      <c r="A373" s="91"/>
+      <c r="A373" s="92"/>
       <c r="B373" s="5" t="s">
         <v>856</v>
       </c>
@@ -18326,7 +18326,7 @@
       <c r="F373" s="23"/>
     </row>
     <row r="374" spans="1:6" ht="31">
-      <c r="A374" s="91"/>
+      <c r="A374" s="92"/>
       <c r="B374" s="5" t="s">
         <v>858</v>
       </c>
@@ -18340,7 +18340,7 @@
       <c r="F374" s="23"/>
     </row>
     <row r="375" spans="1:6" ht="134.25" customHeight="1">
-      <c r="A375" s="91"/>
+      <c r="A375" s="92"/>
       <c r="B375" s="5" t="s">
         <v>860</v>
       </c>
@@ -18354,7 +18354,7 @@
       <c r="F375" s="23"/>
     </row>
     <row r="376" spans="1:6" ht="31">
-      <c r="A376" s="91"/>
+      <c r="A376" s="92"/>
       <c r="B376" s="5" t="s">
         <v>862</v>
       </c>
@@ -18368,7 +18368,7 @@
       <c r="F376" s="23"/>
     </row>
     <row r="377" spans="1:6" ht="77.5">
-      <c r="A377" s="91"/>
+      <c r="A377" s="92"/>
       <c r="B377" s="5" t="s">
         <v>864</v>
       </c>
@@ -18382,7 +18382,7 @@
       <c r="F377" s="23"/>
     </row>
     <row r="378" spans="1:6" ht="90" customHeight="1">
-      <c r="A378" s="91"/>
+      <c r="A378" s="92"/>
       <c r="B378" s="5" t="s">
         <v>866</v>
       </c>
@@ -18396,7 +18396,7 @@
       <c r="F378" s="23"/>
     </row>
     <row r="379" spans="1:6" ht="15.5">
-      <c r="A379" s="91"/>
+      <c r="A379" s="92"/>
       <c r="B379" s="5" t="s">
         <v>869</v>
       </c>
@@ -18410,7 +18410,7 @@
       <c r="F379" s="23"/>
     </row>
     <row r="380" spans="1:6" ht="108.75" customHeight="1">
-      <c r="A380" s="91"/>
+      <c r="A380" s="92"/>
       <c r="B380" s="5" t="s">
         <v>871</v>
       </c>
@@ -18426,7 +18426,7 @@
       <c r="F380" s="23"/>
     </row>
     <row r="381" spans="1:6" ht="77.5">
-      <c r="A381" s="91"/>
+      <c r="A381" s="92"/>
       <c r="B381" s="5" t="s">
         <v>873</v>
       </c>
@@ -18440,7 +18440,7 @@
       <c r="F381" s="23"/>
     </row>
     <row r="382" spans="1:6" ht="56">
-      <c r="A382" s="91"/>
+      <c r="A382" s="92"/>
       <c r="B382" s="5" t="s">
         <v>874</v>
       </c>
@@ -18456,7 +18456,7 @@
       <c r="F382" s="23"/>
     </row>
     <row r="383" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A383" s="91"/>
+      <c r="A383" s="92"/>
       <c r="B383" s="5" t="s">
         <v>876</v>
       </c>
@@ -18470,7 +18470,7 @@
       <c r="F383" s="23"/>
     </row>
     <row r="384" spans="1:6" ht="46.5">
-      <c r="A384" s="91"/>
+      <c r="A384" s="92"/>
       <c r="B384" s="5" t="s">
         <v>878</v>
       </c>
@@ -18484,7 +18484,7 @@
       <c r="F384" s="23"/>
     </row>
     <row r="385" spans="1:6" ht="46.5">
-      <c r="A385" s="91"/>
+      <c r="A385" s="92"/>
       <c r="B385" s="5" t="s">
         <v>880</v>
       </c>
@@ -18498,7 +18498,7 @@
       <c r="F385" s="23"/>
     </row>
     <row r="386" spans="1:6" ht="42">
-      <c r="A386" s="91"/>
+      <c r="A386" s="92"/>
       <c r="B386" s="5" t="s">
         <v>882</v>
       </c>
@@ -18514,7 +18514,7 @@
       <c r="F386" s="23"/>
     </row>
     <row r="387" spans="1:6" ht="168.75" customHeight="1">
-      <c r="A387" s="91"/>
+      <c r="A387" s="92"/>
       <c r="B387" s="1" t="s">
         <v>884</v>
       </c>
@@ -18530,7 +18530,7 @@
       <c r="F387" s="23"/>
     </row>
     <row r="388" spans="1:6" ht="161.25" customHeight="1">
-      <c r="A388" s="91"/>
+      <c r="A388" s="92"/>
       <c r="B388" s="5" t="s">
         <v>887</v>
       </c>
@@ -18544,7 +18544,7 @@
       <c r="F388" s="23"/>
     </row>
     <row r="389" spans="1:6" ht="31">
-      <c r="A389" s="91"/>
+      <c r="A389" s="92"/>
       <c r="B389" s="5" t="s">
         <v>889</v>
       </c>
@@ -18560,7 +18560,7 @@
       <c r="F389" s="23"/>
     </row>
     <row r="390" spans="1:6" ht="72" customHeight="1">
-      <c r="A390" s="91"/>
+      <c r="A390" s="92"/>
       <c r="B390" s="5" t="s">
         <v>891</v>
       </c>
@@ -18576,7 +18576,7 @@
       <c r="F390" s="23"/>
     </row>
     <row r="391" spans="1:6" ht="71.25" customHeight="1">
-      <c r="A391" s="91"/>
+      <c r="A391" s="92"/>
       <c r="B391" s="5" t="s">
         <v>893</v>
       </c>
@@ -18592,7 +18592,7 @@
       <c r="F391" s="23"/>
     </row>
     <row r="392" spans="1:6" ht="105" customHeight="1">
-      <c r="A392" s="91"/>
+      <c r="A392" s="92"/>
       <c r="B392" s="5" t="s">
         <v>895</v>
       </c>
@@ -18606,7 +18606,7 @@
       <c r="F392" s="23"/>
     </row>
     <row r="393" spans="1:6" ht="78" customHeight="1">
-      <c r="A393" s="91"/>
+      <c r="A393" s="92"/>
       <c r="B393" s="5" t="s">
         <v>897</v>
       </c>
@@ -18620,7 +18620,7 @@
       <c r="F393" s="23"/>
     </row>
     <row r="394" spans="1:6" ht="109.5" customHeight="1">
-      <c r="A394" s="91"/>
+      <c r="A394" s="92"/>
       <c r="B394" s="5" t="s">
         <v>899</v>
       </c>
@@ -18634,7 +18634,7 @@
       <c r="F394" s="23"/>
     </row>
     <row r="395" spans="1:6" ht="31">
-      <c r="A395" s="91"/>
+      <c r="A395" s="92"/>
       <c r="B395" s="5" t="s">
         <v>901</v>
       </c>
@@ -18648,7 +18648,7 @@
       <c r="F395" s="23"/>
     </row>
     <row r="396" spans="1:6" ht="46.5">
-      <c r="A396" s="91"/>
+      <c r="A396" s="92"/>
       <c r="B396" s="5" t="s">
         <v>904</v>
       </c>
@@ -18662,7 +18662,7 @@
       <c r="F396" s="23"/>
     </row>
     <row r="397" spans="1:6" ht="85.5" customHeight="1">
-      <c r="A397" s="93" t="s">
+      <c r="A397" s="96" t="s">
         <v>907</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -18680,7 +18680,7 @@
       <c r="F397" s="23"/>
     </row>
     <row r="398" spans="1:6" ht="42">
-      <c r="A398" s="94"/>
+      <c r="A398" s="97"/>
       <c r="B398" s="5" t="s">
         <v>912</v>
       </c>
@@ -18696,7 +18696,7 @@
       <c r="F398" s="23"/>
     </row>
     <row r="399" spans="1:6" ht="15.5">
-      <c r="A399" s="94"/>
+      <c r="A399" s="97"/>
       <c r="B399" s="5" t="s">
         <v>915</v>
       </c>
@@ -18710,7 +18710,7 @@
       <c r="F399" s="23"/>
     </row>
     <row r="400" spans="1:6" ht="31">
-      <c r="A400" s="94"/>
+      <c r="A400" s="97"/>
       <c r="B400" s="5" t="s">
         <v>917</v>
       </c>
@@ -18724,7 +18724,7 @@
       <c r="F400" s="23"/>
     </row>
     <row r="401" spans="1:6" ht="62">
-      <c r="A401" s="94"/>
+      <c r="A401" s="97"/>
       <c r="B401" s="5" t="s">
         <v>920</v>
       </c>
@@ -18738,7 +18738,7 @@
       <c r="F401" s="23"/>
     </row>
     <row r="402" spans="1:6" ht="15.5">
-      <c r="A402" s="94"/>
+      <c r="A402" s="97"/>
       <c r="B402" s="5" t="s">
         <v>922</v>
       </c>
@@ -18752,7 +18752,7 @@
       <c r="F402" s="23"/>
     </row>
     <row r="403" spans="1:6" ht="243.75" customHeight="1">
-      <c r="A403" s="94"/>
+      <c r="A403" s="97"/>
       <c r="B403" s="5" t="s">
         <v>924</v>
       </c>
@@ -18766,7 +18766,7 @@
       <c r="F403" s="23"/>
     </row>
     <row r="404" spans="1:6" s="24" customFormat="1" ht="31">
-      <c r="A404" s="94"/>
+      <c r="A404" s="97"/>
       <c r="B404" s="1" t="s">
         <v>926</v>
       </c>
@@ -18780,7 +18780,7 @@
       <c r="F404" s="23"/>
     </row>
     <row r="405" spans="1:6" ht="15.5">
-      <c r="A405" s="94"/>
+      <c r="A405" s="97"/>
       <c r="B405" s="5" t="s">
         <v>929</v>
       </c>
@@ -18794,7 +18794,7 @@
       <c r="F405" s="23"/>
     </row>
     <row r="406" spans="1:6" ht="94.5" customHeight="1">
-      <c r="A406" s="94"/>
+      <c r="A406" s="97"/>
       <c r="B406" s="5" t="s">
         <v>932</v>
       </c>
@@ -18810,7 +18810,7 @@
       <c r="F406" s="23"/>
     </row>
     <row r="407" spans="1:6" ht="31">
-      <c r="A407" s="94"/>
+      <c r="A407" s="97"/>
       <c r="B407" s="5" t="s">
         <v>934</v>
       </c>
@@ -18824,7 +18824,7 @@
       <c r="F407" s="23"/>
     </row>
     <row r="408" spans="1:6" ht="70">
-      <c r="A408" s="94"/>
+      <c r="A408" s="97"/>
       <c r="B408" s="5" t="s">
         <v>936</v>
       </c>
@@ -18840,7 +18840,7 @@
       <c r="F408" s="23"/>
     </row>
     <row r="409" spans="1:6" ht="70">
-      <c r="A409" s="94"/>
+      <c r="A409" s="97"/>
       <c r="B409" s="5" t="s">
         <v>938</v>
       </c>
@@ -18856,7 +18856,7 @@
       <c r="F409" s="23"/>
     </row>
     <row r="410" spans="1:6" ht="137.25" customHeight="1">
-      <c r="A410" s="94"/>
+      <c r="A410" s="97"/>
       <c r="B410" s="5" t="s">
         <v>940</v>
       </c>
@@ -18872,7 +18872,7 @@
       <c r="F410" s="23"/>
     </row>
     <row r="411" spans="1:6" ht="70">
-      <c r="A411" s="94"/>
+      <c r="A411" s="97"/>
       <c r="B411" s="5" t="s">
         <v>942</v>
       </c>
@@ -18888,7 +18888,7 @@
       <c r="F411" s="23"/>
     </row>
     <row r="412" spans="1:6" ht="31">
-      <c r="A412" s="94"/>
+      <c r="A412" s="97"/>
       <c r="B412" s="5" t="s">
         <v>944</v>
       </c>
@@ -18902,7 +18902,7 @@
       <c r="F412" s="23"/>
     </row>
     <row r="413" spans="1:6" ht="93">
-      <c r="A413" s="94"/>
+      <c r="A413" s="97"/>
       <c r="B413" s="5" t="s">
         <v>947</v>
       </c>
@@ -18918,7 +18918,7 @@
       <c r="F413" s="23"/>
     </row>
     <row r="414" spans="1:6" ht="77.5">
-      <c r="A414" s="94"/>
+      <c r="A414" s="97"/>
       <c r="B414" s="5" t="s">
         <v>949</v>
       </c>
@@ -18934,7 +18934,7 @@
       <c r="F414" s="23"/>
     </row>
     <row r="415" spans="1:6" ht="70">
-      <c r="A415" s="94"/>
+      <c r="A415" s="97"/>
       <c r="B415" s="5" t="s">
         <v>951</v>
       </c>
@@ -18950,7 +18950,7 @@
       <c r="F415" s="23"/>
     </row>
     <row r="416" spans="1:6" ht="42">
-      <c r="A416" s="94"/>
+      <c r="A416" s="97"/>
       <c r="B416" s="1" t="s">
         <v>953</v>
       </c>
@@ -18966,7 +18966,7 @@
       <c r="F416" s="23"/>
     </row>
     <row r="417" spans="1:6" ht="132.75" customHeight="1">
-      <c r="A417" s="94"/>
+      <c r="A417" s="97"/>
       <c r="B417" s="5" t="s">
         <v>954</v>
       </c>
@@ -18982,7 +18982,7 @@
       <c r="F417" s="23"/>
     </row>
     <row r="418" spans="1:6" ht="130.5" customHeight="1">
-      <c r="A418" s="94"/>
+      <c r="A418" s="97"/>
       <c r="B418" s="5" t="s">
         <v>956</v>
       </c>
@@ -18998,7 +18998,7 @@
       <c r="F418" s="23"/>
     </row>
     <row r="419" spans="1:6" ht="57" customHeight="1">
-      <c r="A419" s="94"/>
+      <c r="A419" s="97"/>
       <c r="B419" s="1" t="s">
         <v>957</v>
       </c>
@@ -19012,7 +19012,7 @@
       <c r="F419" s="23"/>
     </row>
     <row r="420" spans="1:6" ht="102.75" customHeight="1">
-      <c r="A420" s="94"/>
+      <c r="A420" s="97"/>
       <c r="B420" s="5" t="s">
         <v>959</v>
       </c>
@@ -19028,7 +19028,7 @@
       <c r="F420" s="23"/>
     </row>
     <row r="421" spans="1:6" ht="234.75" customHeight="1">
-      <c r="A421" s="94"/>
+      <c r="A421" s="97"/>
       <c r="B421" s="5" t="s">
         <v>961</v>
       </c>
@@ -19042,7 +19042,7 @@
       <c r="F421" s="23"/>
     </row>
     <row r="422" spans="1:6" ht="31">
-      <c r="A422" s="94"/>
+      <c r="A422" s="97"/>
       <c r="B422" s="5" t="s">
         <v>963</v>
       </c>
@@ -19056,7 +19056,7 @@
       <c r="F422" s="23"/>
     </row>
     <row r="423" spans="1:6" ht="15.5">
-      <c r="A423" s="94"/>
+      <c r="A423" s="97"/>
       <c r="B423" s="5" t="s">
         <v>965</v>
       </c>
@@ -19070,7 +19070,7 @@
       <c r="F423" s="23"/>
     </row>
     <row r="424" spans="1:6" ht="15.5">
-      <c r="A424" s="94"/>
+      <c r="A424" s="97"/>
       <c r="B424" s="5" t="s">
         <v>967</v>
       </c>
@@ -19084,7 +19084,7 @@
       <c r="F424" s="23"/>
     </row>
     <row r="425" spans="1:6" ht="42">
-      <c r="A425" s="94"/>
+      <c r="A425" s="97"/>
       <c r="B425" s="1" t="s">
         <v>969</v>
       </c>
@@ -19100,7 +19100,7 @@
       <c r="F425" s="23"/>
     </row>
     <row r="426" spans="1:6" ht="42">
-      <c r="A426" s="94"/>
+      <c r="A426" s="97"/>
       <c r="B426" s="5" t="s">
         <v>971</v>
       </c>
@@ -19116,7 +19116,7 @@
       <c r="F426" s="23"/>
     </row>
     <row r="427" spans="1:6" ht="46.5">
-      <c r="A427" s="94"/>
+      <c r="A427" s="97"/>
       <c r="B427" s="1" t="s">
         <v>972</v>
       </c>
@@ -19130,7 +19130,7 @@
       <c r="F427" s="23"/>
     </row>
     <row r="428" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A428" s="94"/>
+      <c r="A428" s="97"/>
       <c r="B428" s="1" t="s">
         <v>974</v>
       </c>
@@ -19144,7 +19144,7 @@
       <c r="F428" s="23"/>
     </row>
     <row r="429" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A429" s="94"/>
+      <c r="A429" s="97"/>
       <c r="B429" s="5" t="s">
         <v>976</v>
       </c>
@@ -19160,7 +19160,7 @@
       <c r="F429" s="23"/>
     </row>
     <row r="430" spans="1:6" ht="15.5">
-      <c r="A430" s="94"/>
+      <c r="A430" s="97"/>
       <c r="B430" s="5" t="s">
         <v>978</v>
       </c>
@@ -19174,7 +19174,7 @@
       <c r="F430" s="23"/>
     </row>
     <row r="431" spans="1:6" ht="42">
-      <c r="A431" s="94"/>
+      <c r="A431" s="97"/>
       <c r="B431" s="5" t="s">
         <v>980</v>
       </c>
@@ -19190,7 +19190,7 @@
       <c r="F431" s="23"/>
     </row>
     <row r="432" spans="1:6" s="37" customFormat="1" ht="15.5">
-      <c r="A432" s="94"/>
+      <c r="A432" s="97"/>
       <c r="B432" s="1" t="s">
         <v>982</v>
       </c>
@@ -19204,7 +19204,7 @@
       <c r="F432" s="36"/>
     </row>
     <row r="433" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A433" s="94"/>
+      <c r="A433" s="97"/>
       <c r="B433" s="5" t="s">
         <v>984</v>
       </c>
@@ -19220,7 +19220,7 @@
       <c r="F433" s="23"/>
     </row>
     <row r="434" spans="1:6" ht="42">
-      <c r="A434" s="94"/>
+      <c r="A434" s="97"/>
       <c r="B434" s="5" t="s">
         <v>986</v>
       </c>
@@ -19236,7 +19236,7 @@
       <c r="F434" s="23"/>
     </row>
     <row r="435" spans="1:6" ht="46.5">
-      <c r="A435" s="94"/>
+      <c r="A435" s="97"/>
       <c r="B435" s="1" t="s">
         <v>988</v>
       </c>
@@ -19250,7 +19250,7 @@
       <c r="F435" s="23"/>
     </row>
     <row r="436" spans="1:6" ht="15.5">
-      <c r="A436" s="94"/>
+      <c r="A436" s="97"/>
       <c r="B436" s="5" t="s">
         <v>991</v>
       </c>
@@ -19264,7 +19264,7 @@
       <c r="F436" s="23"/>
     </row>
     <row r="437" spans="1:6" ht="15.5">
-      <c r="A437" s="94"/>
+      <c r="A437" s="97"/>
       <c r="B437" s="1" t="s">
         <v>993</v>
       </c>
@@ -19276,7 +19276,7 @@
       <c r="F437" s="23"/>
     </row>
     <row r="438" spans="1:6" ht="155.25" customHeight="1">
-      <c r="A438" s="94"/>
+      <c r="A438" s="97"/>
       <c r="B438" s="5" t="s">
         <v>995</v>
       </c>
@@ -19292,7 +19292,7 @@
       <c r="F438" s="23"/>
     </row>
     <row r="439" spans="1:6" ht="31">
-      <c r="A439" s="94"/>
+      <c r="A439" s="97"/>
       <c r="B439" s="5" t="s">
         <v>997</v>
       </c>
@@ -19306,7 +19306,7 @@
       <c r="F439" s="23"/>
     </row>
     <row r="440" spans="1:6" ht="31">
-      <c r="A440" s="94"/>
+      <c r="A440" s="97"/>
       <c r="B440" s="5" t="s">
         <v>999</v>
       </c>
@@ -19320,7 +19320,7 @@
       <c r="F440" s="23"/>
     </row>
     <row r="441" spans="1:6" ht="90.75" customHeight="1">
-      <c r="A441" s="94"/>
+      <c r="A441" s="97"/>
       <c r="B441" s="1" t="s">
         <v>1001</v>
       </c>
@@ -19334,7 +19334,7 @@
       <c r="F441" s="23"/>
     </row>
     <row r="442" spans="1:6" ht="103.5" customHeight="1">
-      <c r="A442" s="94"/>
+      <c r="A442" s="97"/>
       <c r="B442" s="1" t="s">
         <v>1003</v>
       </c>
@@ -19350,7 +19350,7 @@
       <c r="F442" s="23"/>
     </row>
     <row r="443" spans="1:6" ht="31">
-      <c r="A443" s="94"/>
+      <c r="A443" s="97"/>
       <c r="B443" s="5" t="s">
         <v>1005</v>
       </c>
@@ -19364,7 +19364,7 @@
       <c r="F443" s="23"/>
     </row>
     <row r="444" spans="1:6" ht="15.5">
-      <c r="A444" s="94"/>
+      <c r="A444" s="97"/>
       <c r="B444" s="5" t="s">
         <v>1007</v>
       </c>
@@ -19378,7 +19378,7 @@
       <c r="F444" s="23"/>
     </row>
     <row r="445" spans="1:6" ht="15.5">
-      <c r="A445" s="94"/>
+      <c r="A445" s="97"/>
       <c r="B445" s="5" t="s">
         <v>1009</v>
       </c>
@@ -19390,7 +19390,7 @@
       <c r="F445" s="23"/>
     </row>
     <row r="446" spans="1:6" ht="31">
-      <c r="A446" s="94"/>
+      <c r="A446" s="97"/>
       <c r="B446" s="5" t="s">
         <v>1011</v>
       </c>
@@ -19402,7 +19402,7 @@
       <c r="F446" s="23"/>
     </row>
     <row r="447" spans="1:6" ht="31">
-      <c r="A447" s="94"/>
+      <c r="A447" s="97"/>
       <c r="B447" s="5" t="s">
         <v>1013</v>
       </c>
@@ -19416,7 +19416,7 @@
       <c r="F447" s="23"/>
     </row>
     <row r="448" spans="1:6" ht="70">
-      <c r="A448" s="94"/>
+      <c r="A448" s="97"/>
       <c r="B448" s="5" t="s">
         <v>1016</v>
       </c>
@@ -19432,7 +19432,7 @@
       <c r="F448" s="23"/>
     </row>
     <row r="449" spans="1:6" ht="15.5">
-      <c r="A449" s="94"/>
+      <c r="A449" s="97"/>
       <c r="B449" s="5" t="s">
         <v>1019</v>
       </c>
@@ -19446,7 +19446,7 @@
       <c r="F449" s="23"/>
     </row>
     <row r="450" spans="1:6" ht="31">
-      <c r="A450" s="94"/>
+      <c r="A450" s="97"/>
       <c r="B450" s="1" t="s">
         <v>1021</v>
       </c>
@@ -19460,7 +19460,7 @@
       <c r="F450" s="23"/>
     </row>
     <row r="451" spans="1:6" ht="31">
-      <c r="A451" s="94"/>
+      <c r="A451" s="97"/>
       <c r="B451" s="5" t="s">
         <v>1023</v>
       </c>
@@ -19474,7 +19474,7 @@
       <c r="F451" s="23"/>
     </row>
     <row r="452" spans="1:6" ht="15.5">
-      <c r="A452" s="94"/>
+      <c r="A452" s="97"/>
       <c r="B452" s="1" t="s">
         <v>1025</v>
       </c>
@@ -19488,7 +19488,7 @@
       <c r="F452" s="23"/>
     </row>
     <row r="453" spans="1:6" ht="31">
-      <c r="A453" s="94"/>
+      <c r="A453" s="97"/>
       <c r="B453" s="5" t="s">
         <v>1028</v>
       </c>
@@ -19502,7 +19502,7 @@
       <c r="F453" s="23"/>
     </row>
     <row r="454" spans="1:6" ht="46.5">
-      <c r="A454" s="94"/>
+      <c r="A454" s="97"/>
       <c r="B454" s="5" t="s">
         <v>1030</v>
       </c>
@@ -19518,7 +19518,7 @@
       <c r="F454" s="23"/>
     </row>
     <row r="455" spans="1:6" ht="42">
-      <c r="A455" s="94"/>
+      <c r="A455" s="97"/>
       <c r="B455" s="5" t="s">
         <v>1032</v>
       </c>
@@ -19534,7 +19534,7 @@
       <c r="F455" s="23"/>
     </row>
     <row r="456" spans="1:6" ht="42">
-      <c r="A456" s="94"/>
+      <c r="A456" s="97"/>
       <c r="B456" s="5" t="s">
         <v>1034</v>
       </c>
@@ -19550,7 +19550,7 @@
       <c r="F456" s="23"/>
     </row>
     <row r="457" spans="1:6" ht="15.5">
-      <c r="A457" s="94"/>
+      <c r="A457" s="97"/>
       <c r="B457" s="5" t="s">
         <v>1036</v>
       </c>
@@ -19562,7 +19562,7 @@
       <c r="F457" s="23"/>
     </row>
     <row r="458" spans="1:6" ht="58.5" customHeight="1">
-      <c r="A458" s="94"/>
+      <c r="A458" s="97"/>
       <c r="B458" s="5" t="s">
         <v>1038</v>
       </c>
@@ -19578,7 +19578,7 @@
       <c r="F458" s="23"/>
     </row>
     <row r="459" spans="1:6" ht="15.5">
-      <c r="A459" s="94"/>
+      <c r="A459" s="97"/>
       <c r="B459" s="5" t="s">
         <v>1040</v>
       </c>
@@ -19592,7 +19592,7 @@
       <c r="F459" s="23"/>
     </row>
     <row r="460" spans="1:6" ht="51" customHeight="1">
-      <c r="A460" s="94"/>
+      <c r="A460" s="97"/>
       <c r="B460" s="1" t="s">
         <v>1042</v>
       </c>
@@ -19606,7 +19606,7 @@
       <c r="F460" s="23"/>
     </row>
     <row r="461" spans="1:6" ht="77.5">
-      <c r="A461" s="94"/>
+      <c r="A461" s="97"/>
       <c r="B461" s="5" t="s">
         <v>1044</v>
       </c>
@@ -19622,7 +19622,7 @@
       <c r="F461" s="23"/>
     </row>
     <row r="462" spans="1:6" ht="62">
-      <c r="A462" s="94"/>
+      <c r="A462" s="97"/>
       <c r="B462" s="1" t="s">
         <v>1046</v>
       </c>
@@ -19638,7 +19638,7 @@
       <c r="F462" s="23"/>
     </row>
     <row r="463" spans="1:6" ht="42">
-      <c r="A463" s="94"/>
+      <c r="A463" s="97"/>
       <c r="B463" s="5" t="s">
         <v>1048</v>
       </c>
@@ -19654,7 +19654,7 @@
       <c r="F463" s="23"/>
     </row>
     <row r="464" spans="1:6" ht="42">
-      <c r="A464" s="94"/>
+      <c r="A464" s="97"/>
       <c r="B464" s="5" t="s">
         <v>1050</v>
       </c>
@@ -19670,7 +19670,7 @@
       <c r="F464" s="23"/>
     </row>
     <row r="465" spans="1:6" ht="201.75" customHeight="1">
-      <c r="A465" s="94"/>
+      <c r="A465" s="97"/>
       <c r="B465" s="1" t="s">
         <v>1052</v>
       </c>
@@ -19686,7 +19686,7 @@
       <c r="F465" s="23"/>
     </row>
     <row r="466" spans="1:6" ht="31">
-      <c r="A466" s="94"/>
+      <c r="A466" s="97"/>
       <c r="B466" s="5" t="s">
         <v>1055</v>
       </c>
@@ -19700,7 +19700,7 @@
       <c r="F466" s="23"/>
     </row>
     <row r="467" spans="1:6" ht="63.75" customHeight="1">
-      <c r="A467" s="94"/>
+      <c r="A467" s="97"/>
       <c r="B467" s="5" t="s">
         <v>1057</v>
       </c>
@@ -19716,7 +19716,7 @@
       <c r="F467" s="23"/>
     </row>
     <row r="468" spans="1:6" ht="104.25" customHeight="1">
-      <c r="A468" s="94"/>
+      <c r="A468" s="97"/>
       <c r="B468" s="5" t="s">
         <v>1059</v>
       </c>
@@ -19732,7 +19732,7 @@
       <c r="F468" s="23"/>
     </row>
     <row r="469" spans="1:6" ht="62">
-      <c r="A469" s="94"/>
+      <c r="A469" s="97"/>
       <c r="B469" s="5" t="s">
         <v>1061</v>
       </c>
@@ -19748,7 +19748,7 @@
       <c r="F469" s="23"/>
     </row>
     <row r="470" spans="1:6" ht="93">
-      <c r="A470" s="94"/>
+      <c r="A470" s="97"/>
       <c r="B470" s="5" t="s">
         <v>1063</v>
       </c>
@@ -19764,7 +19764,7 @@
       <c r="F470" s="23"/>
     </row>
     <row r="471" spans="1:6" ht="107.25" customHeight="1">
-      <c r="A471" s="94"/>
+      <c r="A471" s="97"/>
       <c r="B471" s="5" t="s">
         <v>1065</v>
       </c>
@@ -19780,7 +19780,7 @@
       <c r="F471" s="23"/>
     </row>
     <row r="472" spans="1:6" ht="83.25" customHeight="1">
-      <c r="A472" s="94"/>
+      <c r="A472" s="97"/>
       <c r="B472" s="1" t="s">
         <v>1067</v>
       </c>
@@ -19796,7 +19796,7 @@
       <c r="F472" s="23"/>
     </row>
     <row r="473" spans="1:6" ht="90" customHeight="1">
-      <c r="A473" s="94"/>
+      <c r="A473" s="97"/>
       <c r="B473" s="5" t="s">
         <v>1068</v>
       </c>
@@ -19812,7 +19812,7 @@
       <c r="F473" s="23"/>
     </row>
     <row r="474" spans="1:6" ht="42">
-      <c r="A474" s="94"/>
+      <c r="A474" s="97"/>
       <c r="B474" s="5" t="s">
         <v>1070</v>
       </c>
@@ -19828,7 +19828,7 @@
       <c r="F474" s="23"/>
     </row>
     <row r="475" spans="1:6" ht="15.5">
-      <c r="A475" s="94"/>
+      <c r="A475" s="97"/>
       <c r="B475" s="5" t="s">
         <v>1072</v>
       </c>
@@ -19842,7 +19842,7 @@
       <c r="F475" s="23"/>
     </row>
     <row r="476" spans="1:6" ht="75" customHeight="1">
-      <c r="A476" s="94"/>
+      <c r="A476" s="97"/>
       <c r="B476" s="5" t="s">
         <v>1074</v>
       </c>
@@ -19858,7 +19858,7 @@
       <c r="F476" s="23"/>
     </row>
     <row r="477" spans="1:6" ht="42">
-      <c r="A477" s="94"/>
+      <c r="A477" s="97"/>
       <c r="B477" s="5" t="s">
         <v>1077</v>
       </c>
@@ -19874,7 +19874,7 @@
       <c r="F477" s="23"/>
     </row>
     <row r="478" spans="1:6" ht="15.5">
-      <c r="A478" s="94"/>
+      <c r="A478" s="97"/>
       <c r="B478" s="5" t="s">
         <v>1079</v>
       </c>
@@ -19888,7 +19888,7 @@
       <c r="F478" s="23"/>
     </row>
     <row r="479" spans="1:6" ht="42">
-      <c r="A479" s="94"/>
+      <c r="A479" s="97"/>
       <c r="B479" s="5" t="s">
         <v>1081</v>
       </c>
@@ -19904,7 +19904,7 @@
       <c r="F479" s="23"/>
     </row>
     <row r="480" spans="1:6" ht="62">
-      <c r="A480" s="94"/>
+      <c r="A480" s="97"/>
       <c r="B480" s="5" t="s">
         <v>1084</v>
       </c>
@@ -19918,7 +19918,7 @@
       <c r="F480" s="23"/>
     </row>
     <row r="481" spans="1:6" ht="139.5">
-      <c r="A481" s="94"/>
+      <c r="A481" s="97"/>
       <c r="B481" s="5" t="s">
         <v>1086</v>
       </c>
@@ -19934,7 +19934,7 @@
       <c r="F481" s="23"/>
     </row>
     <row r="482" spans="1:6" ht="46.5">
-      <c r="A482" s="94"/>
+      <c r="A482" s="97"/>
       <c r="B482" s="5" t="s">
         <v>1088</v>
       </c>
@@ -19948,7 +19948,7 @@
       <c r="F482" s="23"/>
     </row>
     <row r="483" spans="1:6" ht="31">
-      <c r="A483" s="94"/>
+      <c r="A483" s="97"/>
       <c r="B483" s="5" t="s">
         <v>1091</v>
       </c>
@@ -19960,7 +19960,7 @@
       <c r="F483" s="23"/>
     </row>
     <row r="484" spans="1:6" ht="15.5">
-      <c r="A484" s="94"/>
+      <c r="A484" s="97"/>
       <c r="B484" s="5" t="s">
         <v>1093</v>
       </c>
@@ -19974,7 +19974,7 @@
       <c r="F484" s="23"/>
     </row>
     <row r="485" spans="1:6" ht="31">
-      <c r="A485" s="94"/>
+      <c r="A485" s="97"/>
       <c r="B485" s="5" t="s">
         <v>1095</v>
       </c>
@@ -19988,7 +19988,7 @@
       <c r="F485" s="23"/>
     </row>
     <row r="486" spans="1:6" ht="15.5">
-      <c r="A486" s="94"/>
+      <c r="A486" s="97"/>
       <c r="B486" s="5" t="s">
         <v>1097</v>
       </c>
@@ -20000,7 +20000,7 @@
       <c r="F486" s="23"/>
     </row>
     <row r="487" spans="1:6" ht="15.5">
-      <c r="A487" s="94"/>
+      <c r="A487" s="97"/>
       <c r="B487" s="5" t="s">
         <v>1098</v>
       </c>
@@ -20012,7 +20012,7 @@
       <c r="F487" s="23"/>
     </row>
     <row r="488" spans="1:6" ht="31">
-      <c r="A488" s="94"/>
+      <c r="A488" s="97"/>
       <c r="B488" s="5" t="s">
         <v>1099</v>
       </c>
@@ -20026,7 +20026,7 @@
       <c r="F488" s="23"/>
     </row>
     <row r="489" spans="1:6" ht="51" customHeight="1">
-      <c r="A489" s="106" t="s">
+      <c r="A489" s="98" t="s">
         <v>1102</v>
       </c>
       <c r="B489" s="1" t="s">
@@ -20044,7 +20044,7 @@
       <c r="F489" s="23"/>
     </row>
     <row r="490" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A490" s="95"/>
+      <c r="A490" s="99"/>
       <c r="B490" s="5" t="s">
         <v>1106</v>
       </c>
@@ -20060,7 +20060,7 @@
       <c r="F490" s="23"/>
     </row>
     <row r="491" spans="1:6" ht="42">
-      <c r="A491" s="95"/>
+      <c r="A491" s="99"/>
       <c r="B491" s="5" t="s">
         <v>1109</v>
       </c>
@@ -20076,7 +20076,7 @@
       <c r="F491" s="23"/>
     </row>
     <row r="492" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A492" s="95"/>
+      <c r="A492" s="99"/>
       <c r="B492" s="5" t="s">
         <v>1111</v>
       </c>
@@ -20092,7 +20092,7 @@
       <c r="F492" s="23"/>
     </row>
     <row r="493" spans="1:6" ht="57" customHeight="1">
-      <c r="A493" s="95"/>
+      <c r="A493" s="99"/>
       <c r="B493" s="5" t="s">
         <v>1113</v>
       </c>
@@ -20106,7 +20106,7 @@
       <c r="F493" s="23"/>
     </row>
     <row r="494" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A494" s="95"/>
+      <c r="A494" s="99"/>
       <c r="B494" s="5" t="s">
         <v>1116</v>
       </c>
@@ -20120,7 +20120,7 @@
       <c r="F494" s="23"/>
     </row>
     <row r="495" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A495" s="95"/>
+      <c r="A495" s="99"/>
       <c r="B495" s="5" t="s">
         <v>1118</v>
       </c>
@@ -20134,7 +20134,7 @@
       <c r="F495" s="23"/>
     </row>
     <row r="496" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A496" s="95"/>
+      <c r="A496" s="99"/>
       <c r="B496" s="5" t="s">
         <v>1120</v>
       </c>
@@ -20148,7 +20148,7 @@
       <c r="F496" s="23"/>
     </row>
     <row r="497" spans="1:6" ht="36" customHeight="1">
-      <c r="A497" s="95"/>
+      <c r="A497" s="99"/>
       <c r="B497" s="5" t="s">
         <v>1122</v>
       </c>
@@ -20162,7 +20162,7 @@
       <c r="F497" s="23"/>
     </row>
     <row r="498" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A498" s="95"/>
+      <c r="A498" s="99"/>
       <c r="B498" s="5" t="s">
         <v>1124</v>
       </c>
@@ -20178,7 +20178,7 @@
       <c r="F498" s="23"/>
     </row>
     <row r="499" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A499" s="95"/>
+      <c r="A499" s="99"/>
       <c r="B499" s="5" t="s">
         <v>1127</v>
       </c>
@@ -20194,7 +20194,7 @@
       <c r="F499" s="23"/>
     </row>
     <row r="500" spans="1:6" ht="30" customHeight="1">
-      <c r="A500" s="95"/>
+      <c r="A500" s="99"/>
       <c r="B500" s="5" t="s">
         <v>1128</v>
       </c>
@@ -20210,7 +20210,7 @@
       <c r="F500" s="23"/>
     </row>
     <row r="501" spans="1:6" ht="33" customHeight="1">
-      <c r="A501" s="95"/>
+      <c r="A501" s="99"/>
       <c r="B501" s="5" t="s">
         <v>1130</v>
       </c>
@@ -20226,7 +20226,7 @@
       <c r="F501" s="23"/>
     </row>
     <row r="502" spans="1:6" ht="15.5">
-      <c r="A502" s="95"/>
+      <c r="A502" s="99"/>
       <c r="B502" s="5" t="s">
         <v>1133</v>
       </c>
@@ -20240,7 +20240,7 @@
       <c r="F502" s="23"/>
     </row>
     <row r="503" spans="1:6" ht="42">
-      <c r="A503" s="95"/>
+      <c r="A503" s="99"/>
       <c r="B503" s="5" t="s">
         <v>1136</v>
       </c>
@@ -20256,7 +20256,7 @@
       <c r="F503" s="23"/>
     </row>
     <row r="504" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A504" s="95"/>
+      <c r="A504" s="99"/>
       <c r="B504" s="5" t="s">
         <v>1138</v>
       </c>
@@ -20272,7 +20272,7 @@
       <c r="F504" s="23"/>
     </row>
     <row r="505" spans="1:6" ht="42">
-      <c r="A505" s="95"/>
+      <c r="A505" s="99"/>
       <c r="B505" s="5" t="s">
         <v>1141</v>
       </c>
@@ -20288,7 +20288,7 @@
       <c r="F505" s="23"/>
     </row>
     <row r="506" spans="1:6" ht="58.5" customHeight="1">
-      <c r="A506" s="95"/>
+      <c r="A506" s="99"/>
       <c r="B506" s="5" t="s">
         <v>1142</v>
       </c>
@@ -20302,7 +20302,7 @@
       <c r="F506" s="23"/>
     </row>
     <row r="507" spans="1:6" ht="55.5" customHeight="1">
-      <c r="A507" s="95"/>
+      <c r="A507" s="99"/>
       <c r="B507" s="5" t="s">
         <v>1145</v>
       </c>
@@ -20316,7 +20316,7 @@
       <c r="F507" s="23"/>
     </row>
     <row r="508" spans="1:6" ht="42" customHeight="1">
-      <c r="A508" s="95"/>
+      <c r="A508" s="99"/>
       <c r="B508" s="5" t="s">
         <v>1148</v>
       </c>
@@ -20330,7 +20330,7 @@
       <c r="F508" s="23"/>
     </row>
     <row r="509" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A509" s="95"/>
+      <c r="A509" s="99"/>
       <c r="B509" s="5" t="s">
         <v>1150</v>
       </c>
@@ -20344,7 +20344,7 @@
       <c r="F509" s="23"/>
     </row>
     <row r="510" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A510" s="95"/>
+      <c r="A510" s="99"/>
       <c r="B510" s="5" t="s">
         <v>1152</v>
       </c>
@@ -20358,7 +20358,7 @@
       <c r="F510" s="23"/>
     </row>
     <row r="511" spans="1:6" ht="41.25" customHeight="1">
-      <c r="A511" s="95"/>
+      <c r="A511" s="99"/>
       <c r="B511" s="5" t="s">
         <v>1154</v>
       </c>
@@ -20374,7 +20374,7 @@
       <c r="F511" s="23"/>
     </row>
     <row r="512" spans="1:6" ht="55.5" customHeight="1">
-      <c r="A512" s="95"/>
+      <c r="A512" s="99"/>
       <c r="B512" s="5" t="s">
         <v>1156</v>
       </c>
@@ -20390,7 +20390,7 @@
       <c r="F512" s="23"/>
     </row>
     <row r="513" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A513" s="95"/>
+      <c r="A513" s="99"/>
       <c r="B513" s="5" t="s">
         <v>1158</v>
       </c>
@@ -20406,7 +20406,7 @@
       <c r="F513" s="23"/>
     </row>
     <row r="514" spans="1:6" ht="46.5">
-      <c r="A514" s="95"/>
+      <c r="A514" s="99"/>
       <c r="B514" s="5" t="s">
         <v>1160</v>
       </c>
@@ -20422,7 +20422,7 @@
       <c r="F514" s="23"/>
     </row>
     <row r="515" spans="1:6" ht="42">
-      <c r="A515" s="95"/>
+      <c r="A515" s="99"/>
       <c r="B515" s="5" t="s">
         <v>1162</v>
       </c>
@@ -20438,7 +20438,7 @@
       <c r="F515" s="23"/>
     </row>
     <row r="516" spans="1:6" ht="42">
-      <c r="A516" s="95"/>
+      <c r="A516" s="99"/>
       <c r="B516" s="5" t="s">
         <v>1164</v>
       </c>
@@ -20454,7 +20454,7 @@
       <c r="F516" s="23"/>
     </row>
     <row r="517" spans="1:6" ht="31">
-      <c r="A517" s="95"/>
+      <c r="A517" s="99"/>
       <c r="B517" s="1" t="s">
         <v>1166</v>
       </c>
@@ -20468,7 +20468,7 @@
       <c r="F517" s="23"/>
     </row>
     <row r="518" spans="1:6" ht="31">
-      <c r="A518" s="95"/>
+      <c r="A518" s="99"/>
       <c r="B518" s="5" t="s">
         <v>1168</v>
       </c>
@@ -20482,7 +20482,7 @@
       <c r="F518" s="23"/>
     </row>
     <row r="519" spans="1:6" ht="42">
-      <c r="A519" s="95"/>
+      <c r="A519" s="99"/>
       <c r="B519" s="5" t="s">
         <v>1170</v>
       </c>
@@ -20498,7 +20498,7 @@
       <c r="F519" s="23"/>
     </row>
     <row r="520" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A520" s="95"/>
+      <c r="A520" s="99"/>
       <c r="B520" s="5" t="s">
         <v>1172</v>
       </c>
@@ -20512,7 +20512,7 @@
       <c r="F520" s="23"/>
     </row>
     <row r="521" spans="1:6" ht="31">
-      <c r="A521" s="95"/>
+      <c r="A521" s="99"/>
       <c r="B521" s="5" t="s">
         <v>1174</v>
       </c>
@@ -20526,7 +20526,7 @@
       <c r="F521" s="23"/>
     </row>
     <row r="522" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A522" s="95"/>
+      <c r="A522" s="99"/>
       <c r="B522" s="5" t="s">
         <v>1176</v>
       </c>
@@ -20542,7 +20542,7 @@
       <c r="F522" s="23"/>
     </row>
     <row r="523" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A523" s="95"/>
+      <c r="A523" s="99"/>
       <c r="B523" s="5" t="s">
         <v>1178</v>
       </c>
@@ -20558,7 +20558,7 @@
       <c r="F523" s="23"/>
     </row>
     <row r="524" spans="1:6" ht="42">
-      <c r="A524" s="95"/>
+      <c r="A524" s="99"/>
       <c r="B524" s="5" t="s">
         <v>1180</v>
       </c>
@@ -20574,7 +20574,7 @@
       <c r="F524" s="23"/>
     </row>
     <row r="525" spans="1:6" ht="42">
-      <c r="A525" s="95"/>
+      <c r="A525" s="99"/>
       <c r="B525" s="5" t="s">
         <v>1182</v>
       </c>
@@ -20590,7 +20590,7 @@
       <c r="F525" s="23"/>
     </row>
     <row r="526" spans="1:6" ht="42">
-      <c r="A526" s="95"/>
+      <c r="A526" s="99"/>
       <c r="B526" s="5" t="s">
         <v>1184</v>
       </c>
@@ -20606,7 +20606,7 @@
       <c r="F526" s="23"/>
     </row>
     <row r="527" spans="1:6" ht="42">
-      <c r="A527" s="95"/>
+      <c r="A527" s="99"/>
       <c r="B527" s="5" t="s">
         <v>1185</v>
       </c>
@@ -20622,7 +20622,7 @@
       <c r="F527" s="23"/>
     </row>
     <row r="528" spans="1:6" ht="42">
-      <c r="A528" s="95"/>
+      <c r="A528" s="99"/>
       <c r="B528" s="5" t="s">
         <v>1187</v>
       </c>
@@ -20638,7 +20638,7 @@
       <c r="F528" s="23"/>
     </row>
     <row r="529" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A529" s="95"/>
+      <c r="A529" s="99"/>
       <c r="B529" s="5" t="s">
         <v>920</v>
       </c>
@@ -20654,7 +20654,7 @@
       <c r="F529" s="23"/>
     </row>
     <row r="530" spans="1:6" ht="51.75" customHeight="1">
-      <c r="A530" s="95"/>
+      <c r="A530" s="99"/>
       <c r="B530" s="5" t="s">
         <v>1189</v>
       </c>
@@ -20668,7 +20668,7 @@
       <c r="F530" s="23"/>
     </row>
     <row r="531" spans="1:6" ht="15.5">
-      <c r="A531" s="95"/>
+      <c r="A531" s="99"/>
       <c r="B531" s="5" t="s">
         <v>1191</v>
       </c>
@@ -20682,7 +20682,7 @@
       <c r="F531" s="23"/>
     </row>
     <row r="532" spans="1:6" ht="15.5">
-      <c r="A532" s="95"/>
+      <c r="A532" s="99"/>
       <c r="B532" s="5" t="s">
         <v>1193</v>
       </c>
@@ -20696,7 +20696,7 @@
       <c r="F532" s="23"/>
     </row>
     <row r="533" spans="1:6" ht="46.5">
-      <c r="A533" s="95"/>
+      <c r="A533" s="99"/>
       <c r="B533" s="5" t="s">
         <v>1195</v>
       </c>
@@ -20712,7 +20712,7 @@
       <c r="F533" s="23"/>
     </row>
     <row r="534" spans="1:6" ht="15.5">
-      <c r="A534" s="95"/>
+      <c r="A534" s="99"/>
       <c r="B534" s="5" t="s">
         <v>1197</v>
       </c>
@@ -20726,7 +20726,7 @@
       <c r="F534" s="23"/>
     </row>
     <row r="535" spans="1:6" ht="81.75" customHeight="1">
-      <c r="A535" s="95"/>
+      <c r="A535" s="99"/>
       <c r="B535" s="5" t="s">
         <v>1199</v>
       </c>
@@ -20740,7 +20740,7 @@
       <c r="F535" s="23"/>
     </row>
     <row r="536" spans="1:6" ht="31">
-      <c r="A536" s="95"/>
+      <c r="A536" s="99"/>
       <c r="B536" s="5" t="s">
         <v>1202</v>
       </c>
@@ -20754,7 +20754,7 @@
       <c r="F536" s="23"/>
     </row>
     <row r="537" spans="1:6" ht="31">
-      <c r="A537" s="95"/>
+      <c r="A537" s="99"/>
       <c r="B537" s="5" t="s">
         <v>1204</v>
       </c>
@@ -20770,7 +20770,7 @@
       <c r="F537" s="23"/>
     </row>
     <row r="538" spans="1:6" ht="92.25" customHeight="1">
-      <c r="A538" s="95"/>
+      <c r="A538" s="99"/>
       <c r="B538" s="5" t="s">
         <v>1206</v>
       </c>
@@ -20786,7 +20786,7 @@
       <c r="F538" s="23"/>
     </row>
     <row r="539" spans="1:6" ht="28">
-      <c r="A539" s="95"/>
+      <c r="A539" s="99"/>
       <c r="B539" s="5" t="s">
         <v>1208</v>
       </c>
@@ -20802,7 +20802,7 @@
       <c r="F539" s="23"/>
     </row>
     <row r="540" spans="1:6" ht="15.5">
-      <c r="A540" s="95"/>
+      <c r="A540" s="99"/>
       <c r="B540" s="5" t="s">
         <v>1210</v>
       </c>
@@ -20816,7 +20816,7 @@
       <c r="F540" s="23"/>
     </row>
     <row r="541" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A541" s="95"/>
+      <c r="A541" s="99"/>
       <c r="B541" s="5" t="s">
         <v>1212</v>
       </c>
@@ -20830,7 +20830,7 @@
       <c r="F541" s="23"/>
     </row>
     <row r="542" spans="1:6" ht="15.5">
-      <c r="A542" s="95"/>
+      <c r="A542" s="99"/>
       <c r="B542" s="5" t="s">
         <v>1214</v>
       </c>
@@ -20844,7 +20844,7 @@
       <c r="F542" s="23"/>
     </row>
     <row r="543" spans="1:6" ht="31">
-      <c r="A543" s="95"/>
+      <c r="A543" s="99"/>
       <c r="B543" s="5" t="s">
         <v>1216</v>
       </c>
@@ -20860,7 +20860,7 @@
       <c r="F543" s="23"/>
     </row>
     <row r="544" spans="1:6" ht="28">
-      <c r="A544" s="95"/>
+      <c r="A544" s="99"/>
       <c r="B544" s="5" t="s">
         <v>1218</v>
       </c>
@@ -20876,7 +20876,7 @@
       <c r="F544" s="23"/>
     </row>
     <row r="545" spans="1:6" ht="42">
-      <c r="A545" s="95"/>
+      <c r="A545" s="99"/>
       <c r="B545" s="5" t="s">
         <v>1220</v>
       </c>
@@ -20892,7 +20892,7 @@
       <c r="F545" s="23"/>
     </row>
     <row r="546" spans="1:6" ht="46.5">
-      <c r="A546" s="95"/>
+      <c r="A546" s="99"/>
       <c r="B546" s="5" t="s">
         <v>1222</v>
       </c>
@@ -20908,7 +20908,7 @@
       <c r="F546" s="23"/>
     </row>
     <row r="547" spans="1:6" ht="96.75" customHeight="1">
-      <c r="A547" s="95"/>
+      <c r="A547" s="99"/>
       <c r="B547" s="5" t="s">
         <v>1225</v>
       </c>
@@ -20922,7 +20922,7 @@
       <c r="F547" s="23"/>
     </row>
     <row r="548" spans="1:6" ht="31">
-      <c r="A548" s="95"/>
+      <c r="A548" s="99"/>
       <c r="B548" s="5" t="s">
         <v>1228</v>
       </c>
@@ -20938,7 +20938,7 @@
       <c r="F548" s="23"/>
     </row>
     <row r="549" spans="1:6" ht="31">
-      <c r="A549" s="95"/>
+      <c r="A549" s="99"/>
       <c r="B549" s="5" t="s">
         <v>1230</v>
       </c>
@@ -20954,7 +20954,7 @@
       <c r="F549" s="23"/>
     </row>
     <row r="550" spans="1:6" ht="31">
-      <c r="A550" s="95"/>
+      <c r="A550" s="99"/>
       <c r="B550" s="5" t="s">
         <v>1232</v>
       </c>
@@ -20970,7 +20970,7 @@
       <c r="F550" s="23"/>
     </row>
     <row r="551" spans="1:6" ht="28">
-      <c r="A551" s="95"/>
+      <c r="A551" s="99"/>
       <c r="B551" s="5" t="s">
         <v>1234</v>
       </c>
@@ -20986,7 +20986,7 @@
       <c r="F551" s="23"/>
     </row>
     <row r="552" spans="1:6" ht="31">
-      <c r="A552" s="95"/>
+      <c r="A552" s="99"/>
       <c r="B552" s="5" t="s">
         <v>1236</v>
       </c>
@@ -21002,7 +21002,7 @@
       <c r="F552" s="23"/>
     </row>
     <row r="553" spans="1:6" ht="28">
-      <c r="A553" s="95"/>
+      <c r="A553" s="99"/>
       <c r="B553" s="5" t="s">
         <v>1238</v>
       </c>
@@ -21018,7 +21018,7 @@
       <c r="F553" s="23"/>
     </row>
     <row r="554" spans="1:6" ht="31">
-      <c r="A554" s="95"/>
+      <c r="A554" s="99"/>
       <c r="B554" s="5" t="s">
         <v>1240</v>
       </c>
@@ -21032,7 +21032,7 @@
       <c r="F554" s="23"/>
     </row>
     <row r="555" spans="1:6" ht="31">
-      <c r="A555" s="95"/>
+      <c r="A555" s="99"/>
       <c r="B555" s="5" t="s">
         <v>1241</v>
       </c>
@@ -21048,7 +21048,7 @@
       <c r="F555" s="23"/>
     </row>
     <row r="556" spans="1:6" ht="31">
-      <c r="A556" s="95"/>
+      <c r="A556" s="99"/>
       <c r="B556" s="5" t="s">
         <v>1243</v>
       </c>
@@ -21062,7 +21062,7 @@
       <c r="F556" s="23"/>
     </row>
     <row r="557" spans="1:6" ht="15.5">
-      <c r="A557" s="95"/>
+      <c r="A557" s="99"/>
       <c r="B557" s="5" t="s">
         <v>1245</v>
       </c>
@@ -21076,7 +21076,7 @@
       <c r="F557" s="23"/>
     </row>
     <row r="558" spans="1:6" ht="31">
-      <c r="A558" s="95"/>
+      <c r="A558" s="99"/>
       <c r="B558" s="5" t="s">
         <v>1247</v>
       </c>
@@ -21090,7 +21090,7 @@
       <c r="F558" s="23"/>
     </row>
     <row r="559" spans="1:6" ht="31">
-      <c r="A559" s="95"/>
+      <c r="A559" s="99"/>
       <c r="B559" s="5" t="s">
         <v>1248</v>
       </c>
@@ -21104,7 +21104,7 @@
       <c r="F559" s="23"/>
     </row>
     <row r="560" spans="1:6" ht="15.5">
-      <c r="A560" s="95"/>
+      <c r="A560" s="99"/>
       <c r="B560" s="5" t="s">
         <v>1250</v>
       </c>
@@ -21118,7 +21118,7 @@
       <c r="F560" s="23"/>
     </row>
     <row r="561" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A561" s="95"/>
+      <c r="A561" s="99"/>
       <c r="B561" s="5" t="s">
         <v>1252</v>
       </c>
@@ -21132,7 +21132,7 @@
       <c r="F561" s="23"/>
     </row>
     <row r="562" spans="1:6" ht="31">
-      <c r="A562" s="95"/>
+      <c r="A562" s="99"/>
       <c r="B562" s="5" t="s">
         <v>1254</v>
       </c>
@@ -21146,7 +21146,7 @@
       <c r="F562" s="23"/>
     </row>
     <row r="563" spans="1:6" ht="31">
-      <c r="A563" s="95"/>
+      <c r="A563" s="99"/>
       <c r="B563" s="5" t="s">
         <v>1255</v>
       </c>
@@ -21160,7 +21160,7 @@
       <c r="F563" s="23"/>
     </row>
     <row r="564" spans="1:6" ht="31">
-      <c r="A564" s="95"/>
+      <c r="A564" s="99"/>
       <c r="B564" s="5" t="s">
         <v>1257</v>
       </c>
@@ -21174,7 +21174,7 @@
       <c r="F564" s="23"/>
     </row>
     <row r="565" spans="1:6" ht="31">
-      <c r="A565" s="95"/>
+      <c r="A565" s="99"/>
       <c r="B565" s="5" t="s">
         <v>1258</v>
       </c>
@@ -21188,7 +21188,7 @@
       <c r="F565" s="23"/>
     </row>
     <row r="566" spans="1:6" ht="62">
-      <c r="A566" s="95"/>
+      <c r="A566" s="99"/>
       <c r="B566" s="5" t="s">
         <v>1259</v>
       </c>
@@ -21202,7 +21202,7 @@
       <c r="F566" s="23"/>
     </row>
     <row r="567" spans="1:6" ht="46.5">
-      <c r="A567" s="95"/>
+      <c r="A567" s="99"/>
       <c r="B567" s="5" t="s">
         <v>1261</v>
       </c>
@@ -21216,7 +21216,7 @@
       <c r="F567" s="23"/>
     </row>
     <row r="568" spans="1:6" ht="31">
-      <c r="A568" s="95"/>
+      <c r="A568" s="99"/>
       <c r="B568" s="5" t="s">
         <v>1263</v>
       </c>
@@ -21230,7 +21230,7 @@
       <c r="F568" s="23"/>
     </row>
     <row r="569" spans="1:6" ht="46.5">
-      <c r="A569" s="95"/>
+      <c r="A569" s="99"/>
       <c r="B569" s="5" t="s">
         <v>1265</v>
       </c>
@@ -21244,7 +21244,7 @@
       <c r="F569" s="23"/>
     </row>
     <row r="570" spans="1:6" ht="15.5">
-      <c r="A570" s="95"/>
+      <c r="A570" s="99"/>
       <c r="B570" s="5" t="s">
         <v>1266</v>
       </c>
@@ -21258,7 +21258,7 @@
       <c r="F570" s="23"/>
     </row>
     <row r="571" spans="1:6" ht="46.5">
-      <c r="A571" s="95"/>
+      <c r="A571" s="99"/>
       <c r="B571" s="5" t="s">
         <v>1268</v>
       </c>
@@ -21272,7 +21272,7 @@
       <c r="F571" s="23"/>
     </row>
     <row r="572" spans="1:6" ht="31">
-      <c r="A572" s="95"/>
+      <c r="A572" s="99"/>
       <c r="B572" s="5" t="s">
         <v>1269</v>
       </c>
@@ -21286,7 +21286,7 @@
       <c r="F572" s="23"/>
     </row>
     <row r="573" spans="1:6" ht="31">
-      <c r="A573" s="95"/>
+      <c r="A573" s="99"/>
       <c r="B573" s="5" t="s">
         <v>1271</v>
       </c>
@@ -21300,7 +21300,7 @@
       <c r="F573" s="23"/>
     </row>
     <row r="574" spans="1:6" ht="31">
-      <c r="A574" s="95"/>
+      <c r="A574" s="99"/>
       <c r="B574" s="5" t="s">
         <v>1273</v>
       </c>
@@ -21314,7 +21314,7 @@
       <c r="F574" s="23"/>
     </row>
     <row r="575" spans="1:6" ht="15.5">
-      <c r="A575" s="95"/>
+      <c r="A575" s="99"/>
       <c r="B575" s="5" t="s">
         <v>1275</v>
       </c>
@@ -21328,7 +21328,7 @@
       <c r="F575" s="23"/>
     </row>
     <row r="576" spans="1:6" ht="46.5">
-      <c r="A576" s="95"/>
+      <c r="A576" s="99"/>
       <c r="B576" s="5" t="s">
         <v>1277</v>
       </c>
@@ -21342,7 +21342,7 @@
       <c r="F576" s="23"/>
     </row>
     <row r="577" spans="1:6" ht="60" customHeight="1">
-      <c r="A577" s="95"/>
+      <c r="A577" s="99"/>
       <c r="B577" s="5" t="s">
         <v>1279</v>
       </c>
@@ -21358,7 +21358,7 @@
       <c r="F577" s="23"/>
     </row>
     <row r="578" spans="1:6" ht="15.5">
-      <c r="A578" s="95"/>
+      <c r="A578" s="99"/>
       <c r="B578" s="5" t="s">
         <v>1281</v>
       </c>
@@ -21372,7 +21372,7 @@
       <c r="F578" s="23"/>
     </row>
     <row r="579" spans="1:6" ht="31">
-      <c r="A579" s="95"/>
+      <c r="A579" s="99"/>
       <c r="B579" s="5" t="s">
         <v>1283</v>
       </c>
@@ -21388,7 +21388,7 @@
       <c r="F579" s="23"/>
     </row>
     <row r="580" spans="1:6" ht="31">
-      <c r="A580" s="95"/>
+      <c r="A580" s="99"/>
       <c r="B580" s="5" t="s">
         <v>1285</v>
       </c>
@@ -21402,7 +21402,7 @@
       <c r="F580" s="23"/>
     </row>
     <row r="581" spans="1:6" ht="28">
-      <c r="A581" s="95"/>
+      <c r="A581" s="99"/>
       <c r="B581" s="5" t="s">
         <v>1287</v>
       </c>
@@ -21418,7 +21418,7 @@
       <c r="F581" s="23"/>
     </row>
     <row r="582" spans="1:6" ht="28">
-      <c r="A582" s="95"/>
+      <c r="A582" s="99"/>
       <c r="B582" s="5" t="s">
         <v>1289</v>
       </c>
@@ -21434,7 +21434,7 @@
       <c r="F582" s="23"/>
     </row>
     <row r="583" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A583" s="95"/>
+      <c r="A583" s="99"/>
       <c r="B583" s="5" t="s">
         <v>1290</v>
       </c>
@@ -21450,7 +21450,7 @@
       <c r="F583" s="23"/>
     </row>
     <row r="584" spans="1:6" ht="42">
-      <c r="A584" s="95"/>
+      <c r="A584" s="99"/>
       <c r="B584" s="5" t="s">
         <v>1292</v>
       </c>
@@ -21466,7 +21466,7 @@
       <c r="F584" s="23"/>
     </row>
     <row r="585" spans="1:6" ht="78.75" customHeight="1">
-      <c r="A585" s="95"/>
+      <c r="A585" s="99"/>
       <c r="B585" s="5" t="s">
         <v>1293</v>
       </c>
@@ -21482,7 +21482,7 @@
       <c r="F585" s="23"/>
     </row>
     <row r="586" spans="1:6" ht="83.25" customHeight="1">
-      <c r="A586" s="95"/>
+      <c r="A586" s="99"/>
       <c r="B586" s="5" t="s">
         <v>1295</v>
       </c>
@@ -21498,7 +21498,7 @@
       <c r="F586" s="23"/>
     </row>
     <row r="587" spans="1:6" ht="42">
-      <c r="A587" s="96"/>
+      <c r="A587" s="100"/>
       <c r="B587" s="5" t="s">
         <v>1297</v>
       </c>
@@ -21514,7 +21514,7 @@
       <c r="F587" s="23"/>
     </row>
     <row r="588" spans="1:6" ht="51" customHeight="1">
-      <c r="A588" s="107" t="s">
+      <c r="A588" s="101" t="s">
         <v>1299</v>
       </c>
       <c r="B588" s="38" t="s">
@@ -21530,7 +21530,7 @@
       <c r="F588" s="23"/>
     </row>
     <row r="589" spans="1:6" ht="31">
-      <c r="A589" s="97"/>
+      <c r="A589" s="102"/>
       <c r="B589" s="39" t="s">
         <v>1303</v>
       </c>
@@ -21544,7 +21544,7 @@
       <c r="F589" s="23"/>
     </row>
     <row r="590" spans="1:6" ht="120" customHeight="1">
-      <c r="A590" s="97"/>
+      <c r="A590" s="102"/>
       <c r="B590" s="39" t="s">
         <v>1306</v>
       </c>
@@ -21558,7 +21558,7 @@
       <c r="F590" s="23"/>
     </row>
     <row r="591" spans="1:6" ht="92.25" customHeight="1">
-      <c r="A591" s="97"/>
+      <c r="A591" s="102"/>
       <c r="B591" s="39" t="s">
         <v>1308</v>
       </c>
@@ -21572,7 +21572,7 @@
       <c r="F591" s="23"/>
     </row>
     <row r="592" spans="1:6" ht="74.25" customHeight="1">
-      <c r="A592" s="97"/>
+      <c r="A592" s="102"/>
       <c r="B592" s="39" t="s">
         <v>1311</v>
       </c>
@@ -21588,7 +21588,7 @@
       <c r="F592" s="23"/>
     </row>
     <row r="593" spans="1:6" ht="294.75" customHeight="1">
-      <c r="A593" s="97"/>
+      <c r="A593" s="102"/>
       <c r="B593" s="39" t="s">
         <v>1314</v>
       </c>
@@ -21604,7 +21604,7 @@
       <c r="F593" s="23"/>
     </row>
     <row r="594" spans="1:6" ht="31">
-      <c r="A594" s="97"/>
+      <c r="A594" s="102"/>
       <c r="B594" s="39" t="s">
         <v>1317</v>
       </c>
@@ -21618,7 +21618,7 @@
       <c r="F594" s="23"/>
     </row>
     <row r="595" spans="1:6" ht="108.5">
-      <c r="A595" s="97"/>
+      <c r="A595" s="102"/>
       <c r="B595" s="39" t="s">
         <v>1319</v>
       </c>
@@ -21632,7 +21632,7 @@
       <c r="F595" s="23"/>
     </row>
     <row r="596" spans="1:6" ht="28">
-      <c r="A596" s="97"/>
+      <c r="A596" s="102"/>
       <c r="B596" s="39" t="s">
         <v>1320</v>
       </c>
@@ -21646,7 +21646,7 @@
       <c r="F596" s="23"/>
     </row>
     <row r="597" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A597" s="97"/>
+      <c r="A597" s="102"/>
       <c r="B597" s="39" t="s">
         <v>1322</v>
       </c>
@@ -21660,7 +21660,7 @@
       <c r="F597" s="23"/>
     </row>
     <row r="598" spans="1:6" ht="101.25" customHeight="1">
-      <c r="A598" s="97"/>
+      <c r="A598" s="102"/>
       <c r="B598" s="39" t="s">
         <v>1324</v>
       </c>
@@ -21676,7 +21676,7 @@
       <c r="F598" s="23"/>
     </row>
     <row r="599" spans="1:6" ht="56">
-      <c r="A599" s="97"/>
+      <c r="A599" s="102"/>
       <c r="B599" s="39" t="s">
         <v>1326</v>
       </c>
@@ -21692,7 +21692,7 @@
       <c r="F599" s="23"/>
     </row>
     <row r="600" spans="1:6" ht="87.75" customHeight="1">
-      <c r="A600" s="97"/>
+      <c r="A600" s="102"/>
       <c r="B600" s="39" t="s">
         <v>1328</v>
       </c>
@@ -21708,7 +21708,7 @@
       <c r="F600" s="23"/>
     </row>
     <row r="601" spans="1:6" ht="283.5" customHeight="1">
-      <c r="A601" s="97"/>
+      <c r="A601" s="102"/>
       <c r="B601" s="39" t="s">
         <v>1330</v>
       </c>
@@ -21724,7 +21724,7 @@
       <c r="F601" s="23"/>
     </row>
     <row r="602" spans="1:6" ht="56">
-      <c r="A602" s="97"/>
+      <c r="A602" s="102"/>
       <c r="B602" s="39" t="s">
         <v>1332</v>
       </c>
@@ -21740,7 +21740,7 @@
       <c r="F602" s="23"/>
     </row>
     <row r="603" spans="1:6" ht="31">
-      <c r="A603" s="97"/>
+      <c r="A603" s="102"/>
       <c r="B603" s="39" t="s">
         <v>1335</v>
       </c>
@@ -21754,7 +21754,7 @@
       <c r="F603" s="23"/>
     </row>
     <row r="604" spans="1:6" ht="31">
-      <c r="A604" s="97"/>
+      <c r="A604" s="102"/>
       <c r="B604" s="39" t="s">
         <v>1337</v>
       </c>
@@ -21768,7 +21768,7 @@
       <c r="F604" s="23"/>
     </row>
     <row r="605" spans="1:6" ht="56">
-      <c r="A605" s="97"/>
+      <c r="A605" s="102"/>
       <c r="B605" s="39" t="s">
         <v>1339</v>
       </c>
@@ -21784,7 +21784,7 @@
       <c r="F605" s="23"/>
     </row>
     <row r="606" spans="1:6" ht="56">
-      <c r="A606" s="97"/>
+      <c r="A606" s="102"/>
       <c r="B606" s="39" t="s">
         <v>1341</v>
       </c>
@@ -21800,7 +21800,7 @@
       <c r="F606" s="23"/>
     </row>
     <row r="607" spans="1:6" ht="94.5" customHeight="1">
-      <c r="A607" s="97"/>
+      <c r="A607" s="102"/>
       <c r="B607" s="39" t="s">
         <v>1343</v>
       </c>
@@ -21816,7 +21816,7 @@
       <c r="F607" s="23"/>
     </row>
     <row r="608" spans="1:6" ht="31">
-      <c r="A608" s="97"/>
+      <c r="A608" s="102"/>
       <c r="B608" s="39" t="s">
         <v>1303</v>
       </c>
@@ -21830,7 +21830,7 @@
       <c r="F608" s="23"/>
     </row>
     <row r="609" spans="1:6" ht="108.5">
-      <c r="A609" s="97"/>
+      <c r="A609" s="102"/>
       <c r="B609" s="39" t="s">
         <v>1306</v>
       </c>
@@ -21844,7 +21844,7 @@
       <c r="F609" s="23"/>
     </row>
     <row r="610" spans="1:6" ht="108.5">
-      <c r="A610" s="97"/>
+      <c r="A610" s="102"/>
       <c r="B610" s="39" t="s">
         <v>1319</v>
       </c>
@@ -21858,7 +21858,7 @@
       <c r="F610" s="23"/>
     </row>
     <row r="611" spans="1:6" ht="84" customHeight="1">
-      <c r="A611" s="97"/>
+      <c r="A611" s="102"/>
       <c r="B611" s="39" t="s">
         <v>1346</v>
       </c>
@@ -21872,7 +21872,7 @@
       <c r="F611" s="23"/>
     </row>
     <row r="612" spans="1:6" ht="57" customHeight="1">
-      <c r="A612" s="97"/>
+      <c r="A612" s="102"/>
       <c r="B612" s="39" t="s">
         <v>1348</v>
       </c>
@@ -21888,7 +21888,7 @@
       <c r="F612" s="23"/>
     </row>
     <row r="613" spans="1:6" ht="108.5">
-      <c r="A613" s="97"/>
+      <c r="A613" s="102"/>
       <c r="B613" s="39" t="s">
         <v>1350</v>
       </c>
@@ -21902,7 +21902,7 @@
       <c r="F613" s="23"/>
     </row>
     <row r="614" spans="1:6" ht="108.5">
-      <c r="A614" s="97"/>
+      <c r="A614" s="102"/>
       <c r="B614" s="39" t="s">
         <v>1352</v>
       </c>
@@ -21916,7 +21916,7 @@
       <c r="F614" s="23"/>
     </row>
     <row r="615" spans="1:6" ht="30" customHeight="1">
-      <c r="A615" s="97"/>
+      <c r="A615" s="102"/>
       <c r="B615" s="39" t="s">
         <v>1354</v>
       </c>
@@ -21930,7 +21930,7 @@
       <c r="F615" s="23"/>
     </row>
     <row r="616" spans="1:6" ht="28">
-      <c r="A616" s="97"/>
+      <c r="A616" s="102"/>
       <c r="B616" s="39" t="s">
         <v>1356</v>
       </c>
@@ -21944,7 +21944,7 @@
       <c r="F616" s="23"/>
     </row>
     <row r="617" spans="1:6" ht="108.5">
-      <c r="A617" s="97"/>
+      <c r="A617" s="102"/>
       <c r="B617" s="39" t="s">
         <v>1358</v>
       </c>
@@ -21958,7 +21958,7 @@
       <c r="F617" s="23"/>
     </row>
     <row r="618" spans="1:6" ht="31">
-      <c r="A618" s="97"/>
+      <c r="A618" s="102"/>
       <c r="B618" s="39" t="s">
         <v>1359</v>
       </c>
@@ -21972,7 +21972,7 @@
       <c r="F618" s="23"/>
     </row>
     <row r="619" spans="1:6" ht="28">
-      <c r="A619" s="97"/>
+      <c r="A619" s="102"/>
       <c r="B619" s="39" t="s">
         <v>1360</v>
       </c>
@@ -21986,7 +21986,7 @@
       <c r="F619" s="23"/>
     </row>
     <row r="620" spans="1:6" ht="31">
-      <c r="A620" s="97"/>
+      <c r="A620" s="102"/>
       <c r="B620" s="39" t="s">
         <v>1362</v>
       </c>
@@ -22000,7 +22000,7 @@
       <c r="F620" s="23"/>
     </row>
     <row r="621" spans="1:6" ht="28">
-      <c r="A621" s="97"/>
+      <c r="A621" s="102"/>
       <c r="B621" s="39" t="s">
         <v>1364</v>
       </c>
@@ -22014,7 +22014,7 @@
       <c r="F621" s="23"/>
     </row>
     <row r="622" spans="1:6" ht="28">
-      <c r="A622" s="97"/>
+      <c r="A622" s="102"/>
       <c r="B622" s="39" t="s">
         <v>1366</v>
       </c>
@@ -22028,7 +22028,7 @@
       <c r="F622" s="23"/>
     </row>
     <row r="623" spans="1:6" ht="31">
-      <c r="A623" s="97"/>
+      <c r="A623" s="102"/>
       <c r="B623" s="38" t="s">
         <v>1368</v>
       </c>
@@ -22042,7 +22042,7 @@
       <c r="F623" s="23"/>
     </row>
     <row r="624" spans="1:6" ht="15.5">
-      <c r="A624" s="97"/>
+      <c r="A624" s="102"/>
       <c r="B624" s="39" t="s">
         <v>1370</v>
       </c>
@@ -22056,7 +22056,7 @@
       <c r="F624" s="23"/>
     </row>
     <row r="625" spans="1:6" ht="15.5">
-      <c r="A625" s="97"/>
+      <c r="A625" s="102"/>
       <c r="B625" s="39" t="s">
         <v>1372</v>
       </c>
@@ -22070,7 +22070,7 @@
       <c r="F625" s="23"/>
     </row>
     <row r="626" spans="1:6" ht="68.25" customHeight="1">
-      <c r="A626" s="97"/>
+      <c r="A626" s="102"/>
       <c r="B626" s="39" t="s">
         <v>1314</v>
       </c>
@@ -22086,7 +22086,7 @@
       <c r="F626" s="23"/>
     </row>
     <row r="627" spans="1:6" ht="56">
-      <c r="A627" s="97"/>
+      <c r="A627" s="102"/>
       <c r="B627" s="39" t="s">
         <v>1375</v>
       </c>
@@ -22102,7 +22102,7 @@
       <c r="F627" s="23"/>
     </row>
     <row r="628" spans="1:6" ht="56">
-      <c r="A628" s="97"/>
+      <c r="A628" s="102"/>
       <c r="B628" s="39" t="s">
         <v>1377</v>
       </c>
@@ -22118,7 +22118,7 @@
       <c r="F628" s="23"/>
     </row>
     <row r="629" spans="1:6" ht="57" customHeight="1">
-      <c r="A629" s="97"/>
+      <c r="A629" s="102"/>
       <c r="B629" s="39" t="s">
         <v>1379</v>
       </c>
@@ -22134,7 +22134,7 @@
       <c r="F629" s="23"/>
     </row>
     <row r="630" spans="1:6" ht="56">
-      <c r="A630" s="97"/>
+      <c r="A630" s="102"/>
       <c r="B630" s="39" t="s">
         <v>1381</v>
       </c>
@@ -22150,7 +22150,7 @@
       <c r="F630" s="23"/>
     </row>
     <row r="631" spans="1:6" ht="56">
-      <c r="A631" s="97"/>
+      <c r="A631" s="102"/>
       <c r="B631" s="39" t="s">
         <v>1382</v>
       </c>
@@ -22166,7 +22166,7 @@
       <c r="F631" s="23"/>
     </row>
     <row r="632" spans="1:6" ht="42" customHeight="1">
-      <c r="A632" s="97"/>
+      <c r="A632" s="102"/>
       <c r="B632" s="39" t="s">
         <v>1384</v>
       </c>
@@ -22182,7 +22182,7 @@
       <c r="F632" s="23"/>
     </row>
     <row r="633" spans="1:6" ht="56">
-      <c r="A633" s="97"/>
+      <c r="A633" s="102"/>
       <c r="B633" s="39" t="s">
         <v>1386</v>
       </c>
@@ -22198,7 +22198,7 @@
       <c r="F633" s="23"/>
     </row>
     <row r="634" spans="1:6" ht="56">
-      <c r="A634" s="97"/>
+      <c r="A634" s="102"/>
       <c r="B634" s="39" t="s">
         <v>1388</v>
       </c>
@@ -22214,7 +22214,7 @@
       <c r="F634" s="23"/>
     </row>
     <row r="635" spans="1:6" ht="28">
-      <c r="A635" s="97"/>
+      <c r="A635" s="102"/>
       <c r="B635" s="39" t="s">
         <v>1390</v>
       </c>
@@ -22228,7 +22228,7 @@
       <c r="F635" s="23"/>
     </row>
     <row r="636" spans="1:6" ht="46.5">
-      <c r="A636" s="97"/>
+      <c r="A636" s="102"/>
       <c r="B636" s="39" t="s">
         <v>1392</v>
       </c>
@@ -22242,7 +22242,7 @@
       <c r="F636" s="23"/>
     </row>
     <row r="637" spans="1:6" ht="31">
-      <c r="A637" s="97"/>
+      <c r="A637" s="102"/>
       <c r="B637" s="39" t="s">
         <v>1308</v>
       </c>
@@ -22256,7 +22256,7 @@
       <c r="F637" s="23"/>
     </row>
     <row r="638" spans="1:6" ht="31">
-      <c r="A638" s="97"/>
+      <c r="A638" s="102"/>
       <c r="B638" s="39" t="s">
         <v>1395</v>
       </c>
@@ -22270,7 +22270,7 @@
       <c r="F638" s="23"/>
     </row>
     <row r="639" spans="1:6" ht="31">
-      <c r="A639" s="97"/>
+      <c r="A639" s="102"/>
       <c r="B639" s="39" t="s">
         <v>1397</v>
       </c>
@@ -22284,7 +22284,7 @@
       <c r="F639" s="23"/>
     </row>
     <row r="640" spans="1:6" ht="31">
-      <c r="A640" s="97"/>
+      <c r="A640" s="102"/>
       <c r="B640" s="39" t="s">
         <v>1398</v>
       </c>
@@ -22298,7 +22298,7 @@
       <c r="F640" s="23"/>
     </row>
     <row r="641" spans="1:6" ht="28">
-      <c r="A641" s="97"/>
+      <c r="A641" s="102"/>
       <c r="B641" s="39" t="s">
         <v>1400</v>
       </c>
@@ -22312,7 +22312,7 @@
       <c r="F641" s="23"/>
     </row>
     <row r="642" spans="1:6" ht="31">
-      <c r="A642" s="97"/>
+      <c r="A642" s="102"/>
       <c r="B642" s="39" t="s">
         <v>1402</v>
       </c>
@@ -22326,7 +22326,7 @@
       <c r="F642" s="23"/>
     </row>
     <row r="643" spans="1:6" ht="15.5">
-      <c r="A643" s="97"/>
+      <c r="A643" s="102"/>
       <c r="B643" s="39" t="s">
         <v>1404</v>
       </c>
@@ -22340,7 +22340,7 @@
       <c r="F643" s="23"/>
     </row>
     <row r="644" spans="1:6" ht="24" customHeight="1">
-      <c r="A644" s="97"/>
+      <c r="A644" s="102"/>
       <c r="B644" s="39" t="s">
         <v>1406</v>
       </c>
@@ -22354,7 +22354,7 @@
       <c r="F644" s="23"/>
     </row>
     <row r="645" spans="1:6" ht="46.5">
-      <c r="A645" s="97"/>
+      <c r="A645" s="102"/>
       <c r="B645" s="39" t="s">
         <v>1408</v>
       </c>
@@ -22368,7 +22368,7 @@
       <c r="F645" s="23"/>
     </row>
     <row r="646" spans="1:6" ht="31">
-      <c r="A646" s="97"/>
+      <c r="A646" s="102"/>
       <c r="B646" s="39" t="s">
         <v>1410</v>
       </c>
@@ -22382,7 +22382,7 @@
       <c r="F646" s="23"/>
     </row>
     <row r="647" spans="1:6" ht="138.75" customHeight="1">
-      <c r="A647" s="97"/>
+      <c r="A647" s="102"/>
       <c r="B647" s="39" t="s">
         <v>1412</v>
       </c>
@@ -22396,7 +22396,7 @@
       <c r="F647" s="23"/>
     </row>
     <row r="648" spans="1:6" ht="15.5">
-      <c r="A648" s="97"/>
+      <c r="A648" s="102"/>
       <c r="B648" s="39" t="s">
         <v>1414</v>
       </c>
@@ -22410,7 +22410,7 @@
       <c r="F648" s="23"/>
     </row>
     <row r="649" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A649" s="97"/>
+      <c r="A649" s="102"/>
       <c r="B649" s="39" t="s">
         <v>1416</v>
       </c>
@@ -22424,7 +22424,7 @@
       <c r="F649" s="23"/>
     </row>
     <row r="650" spans="1:6" ht="51" customHeight="1">
-      <c r="A650" s="97"/>
+      <c r="A650" s="102"/>
       <c r="B650" s="39" t="s">
         <v>1418</v>
       </c>
@@ -22438,7 +22438,7 @@
       <c r="F650" s="23"/>
     </row>
     <row r="651" spans="1:6" ht="15.5">
-      <c r="A651" s="97"/>
+      <c r="A651" s="102"/>
       <c r="B651" s="39" t="s">
         <v>1420</v>
       </c>
@@ -22452,7 +22452,7 @@
       <c r="F651" s="23"/>
     </row>
     <row r="652" spans="1:6" ht="15.5">
-      <c r="A652" s="97"/>
+      <c r="A652" s="102"/>
       <c r="B652" s="39" t="s">
         <v>1422</v>
       </c>
@@ -22466,7 +22466,7 @@
       <c r="F652" s="23"/>
     </row>
     <row r="653" spans="1:6" ht="31">
-      <c r="A653" s="97"/>
+      <c r="A653" s="102"/>
       <c r="B653" s="39" t="s">
         <v>1424</v>
       </c>
@@ -22480,7 +22480,7 @@
       <c r="F653" s="23"/>
     </row>
     <row r="654" spans="1:6" ht="31">
-      <c r="A654" s="97"/>
+      <c r="A654" s="102"/>
       <c r="B654" s="39" t="s">
         <v>1322</v>
       </c>
@@ -22496,7 +22496,7 @@
       <c r="F654" s="23"/>
     </row>
     <row r="655" spans="1:6" ht="15.5">
-      <c r="A655" s="97"/>
+      <c r="A655" s="102"/>
       <c r="B655" s="39" t="s">
         <v>1428</v>
       </c>
@@ -22510,7 +22510,7 @@
       <c r="F655" s="23"/>
     </row>
     <row r="656" spans="1:6" ht="31">
-      <c r="A656" s="97"/>
+      <c r="A656" s="102"/>
       <c r="B656" s="39" t="s">
         <v>1431</v>
       </c>
@@ -22526,7 +22526,7 @@
       <c r="F656" s="23"/>
     </row>
     <row r="657" spans="1:6" ht="31">
-      <c r="A657" s="97"/>
+      <c r="A657" s="102"/>
       <c r="B657" s="39" t="s">
         <v>1432</v>
       </c>
@@ -22542,7 +22542,7 @@
       <c r="F657" s="23"/>
     </row>
     <row r="658" spans="1:6" ht="31">
-      <c r="A658" s="97"/>
+      <c r="A658" s="102"/>
       <c r="B658" s="39" t="s">
         <v>1434</v>
       </c>
@@ -22558,7 +22558,7 @@
       <c r="F658" s="23"/>
     </row>
     <row r="659" spans="1:6" ht="31">
-      <c r="A659" s="97"/>
+      <c r="A659" s="102"/>
       <c r="B659" s="39" t="s">
         <v>1436</v>
       </c>
@@ -22574,7 +22574,7 @@
       <c r="F659" s="23"/>
     </row>
     <row r="660" spans="1:6" ht="31">
-      <c r="A660" s="97"/>
+      <c r="A660" s="102"/>
       <c r="B660" s="39" t="s">
         <v>1438</v>
       </c>
@@ -22590,7 +22590,7 @@
       <c r="F660" s="23"/>
     </row>
     <row r="661" spans="1:6" ht="28">
-      <c r="A661" s="97"/>
+      <c r="A661" s="102"/>
       <c r="B661" s="39" t="s">
         <v>1439</v>
       </c>
@@ -22604,7 +22604,7 @@
       <c r="F661" s="23"/>
     </row>
     <row r="662" spans="1:6" ht="31">
-      <c r="A662" s="97"/>
+      <c r="A662" s="102"/>
       <c r="B662" s="39" t="s">
         <v>1441</v>
       </c>
@@ -22618,7 +22618,7 @@
       <c r="F662" s="23"/>
     </row>
     <row r="663" spans="1:6" ht="15.5">
-      <c r="A663" s="97"/>
+      <c r="A663" s="102"/>
       <c r="B663" s="39" t="s">
         <v>1443</v>
       </c>
@@ -22632,7 +22632,7 @@
       <c r="F663" s="23"/>
     </row>
     <row r="664" spans="1:6" ht="56">
-      <c r="A664" s="97"/>
+      <c r="A664" s="102"/>
       <c r="B664" s="39" t="s">
         <v>1445</v>
       </c>
@@ -22648,7 +22648,7 @@
       <c r="F664" s="23"/>
     </row>
     <row r="665" spans="1:6" ht="56">
-      <c r="A665" s="97"/>
+      <c r="A665" s="102"/>
       <c r="B665" s="39" t="s">
         <v>1447</v>
       </c>
@@ -22664,7 +22664,7 @@
       <c r="F665" s="23"/>
     </row>
     <row r="666" spans="1:6" ht="31">
-      <c r="A666" s="97"/>
+      <c r="A666" s="102"/>
       <c r="B666" s="39" t="s">
         <v>1449</v>
       </c>
@@ -22678,7 +22678,7 @@
       <c r="F666" s="23"/>
     </row>
     <row r="667" spans="1:6" ht="46.5">
-      <c r="A667" s="97"/>
+      <c r="A667" s="102"/>
       <c r="B667" s="39" t="s">
         <v>1451</v>
       </c>
@@ -22692,7 +22692,7 @@
       <c r="F667" s="23"/>
     </row>
     <row r="668" spans="1:6" ht="46.5">
-      <c r="A668" s="97"/>
+      <c r="A668" s="102"/>
       <c r="B668" s="39" t="s">
         <v>1453</v>
       </c>
@@ -22706,7 +22706,7 @@
       <c r="F668" s="23"/>
     </row>
     <row r="669" spans="1:6" ht="31">
-      <c r="A669" s="97"/>
+      <c r="A669" s="102"/>
       <c r="B669" s="39" t="s">
         <v>1455</v>
       </c>
@@ -22720,7 +22720,7 @@
       <c r="F669" s="23"/>
     </row>
     <row r="670" spans="1:6" ht="56">
-      <c r="A670" s="97"/>
+      <c r="A670" s="102"/>
       <c r="B670" s="39" t="s">
         <v>1457</v>
       </c>
@@ -22736,7 +22736,7 @@
       <c r="F670" s="23"/>
     </row>
     <row r="671" spans="1:6" ht="69" customHeight="1">
-      <c r="A671" s="97"/>
+      <c r="A671" s="102"/>
       <c r="B671" s="39" t="s">
         <v>1459</v>
       </c>
@@ -22750,7 +22750,7 @@
       <c r="F671" s="23"/>
     </row>
     <row r="672" spans="1:6" ht="31">
-      <c r="A672" s="97"/>
+      <c r="A672" s="102"/>
       <c r="B672" s="39" t="s">
         <v>1461</v>
       </c>
@@ -22764,7 +22764,7 @@
       <c r="F672" s="23"/>
     </row>
     <row r="673" spans="1:6" ht="56">
-      <c r="A673" s="97"/>
+      <c r="A673" s="102"/>
       <c r="B673" s="39" t="s">
         <v>1314</v>
       </c>
@@ -22780,7 +22780,7 @@
       <c r="F673" s="23"/>
     </row>
     <row r="674" spans="1:6" ht="56">
-      <c r="A674" s="97"/>
+      <c r="A674" s="102"/>
       <c r="B674" s="39" t="s">
         <v>1375</v>
       </c>
@@ -22796,7 +22796,7 @@
       <c r="F674" s="23"/>
     </row>
     <row r="675" spans="1:6" ht="56">
-      <c r="A675" s="97"/>
+      <c r="A675" s="102"/>
       <c r="B675" s="39" t="s">
         <v>1377</v>
       </c>
@@ -22812,7 +22812,7 @@
       <c r="F675" s="23"/>
     </row>
     <row r="676" spans="1:6" ht="56">
-      <c r="A676" s="97"/>
+      <c r="A676" s="102"/>
       <c r="B676" s="39" t="s">
         <v>1384</v>
       </c>
@@ -22828,7 +22828,7 @@
       <c r="F676" s="23"/>
     </row>
     <row r="677" spans="1:6" ht="56">
-      <c r="A677" s="97"/>
+      <c r="A677" s="102"/>
       <c r="B677" s="39" t="s">
         <v>1463</v>
       </c>
@@ -22844,7 +22844,7 @@
       <c r="F677" s="23"/>
     </row>
     <row r="678" spans="1:6" ht="95.25" customHeight="1">
-      <c r="A678" s="98" t="s">
+      <c r="A678" s="103" t="s">
         <v>1464</v>
       </c>
       <c r="B678" s="13" t="s">
@@ -22862,7 +22862,7 @@
       <c r="F678" s="23"/>
     </row>
     <row r="679" spans="1:6" ht="39.75" customHeight="1">
-      <c r="A679" s="94"/>
+      <c r="A679" s="97"/>
       <c r="B679" s="5" t="s">
         <v>1469</v>
       </c>
@@ -22876,7 +22876,7 @@
       <c r="F679" s="23"/>
     </row>
     <row r="680" spans="1:6" ht="264.75" customHeight="1">
-      <c r="A680" s="94"/>
+      <c r="A680" s="97"/>
       <c r="B680" s="5" t="s">
         <v>1471</v>
       </c>
@@ -22892,7 +22892,7 @@
       <c r="F680" s="23"/>
     </row>
     <row r="681" spans="1:6" ht="27" customHeight="1">
-      <c r="A681" s="94"/>
+      <c r="A681" s="97"/>
       <c r="B681" s="5" t="s">
         <v>1474</v>
       </c>
@@ -22906,7 +22906,7 @@
       <c r="F681" s="23"/>
     </row>
     <row r="682" spans="1:6" ht="28">
-      <c r="A682" s="94"/>
+      <c r="A682" s="97"/>
       <c r="B682" s="5" t="s">
         <v>1476</v>
       </c>
@@ -22920,7 +22920,7 @@
       <c r="F682" s="23"/>
     </row>
     <row r="683" spans="1:6" ht="31">
-      <c r="A683" s="94"/>
+      <c r="A683" s="97"/>
       <c r="B683" s="5" t="s">
         <v>1478</v>
       </c>
@@ -22934,7 +22934,7 @@
       <c r="F683" s="23"/>
     </row>
     <row r="684" spans="1:6" s="24" customFormat="1" ht="31">
-      <c r="A684" s="94"/>
+      <c r="A684" s="97"/>
       <c r="B684" s="5" t="s">
         <v>1480</v>
       </c>
@@ -22948,7 +22948,7 @@
       <c r="F684" s="23"/>
     </row>
     <row r="685" spans="1:6" ht="31">
-      <c r="A685" s="94"/>
+      <c r="A685" s="97"/>
       <c r="B685" s="5" t="s">
         <v>1483</v>
       </c>
@@ -22962,7 +22962,7 @@
       <c r="F685" s="23"/>
     </row>
     <row r="686" spans="1:6" ht="180" customHeight="1">
-      <c r="A686" s="94"/>
+      <c r="A686" s="97"/>
       <c r="B686" s="5" t="s">
         <v>1485</v>
       </c>
@@ -22978,7 +22978,7 @@
       <c r="F686" s="23"/>
     </row>
     <row r="687" spans="1:6" ht="102.75" customHeight="1">
-      <c r="A687" s="94"/>
+      <c r="A687" s="97"/>
       <c r="B687" s="5" t="s">
         <v>1488</v>
       </c>
@@ -22994,7 +22994,7 @@
       <c r="F687" s="23"/>
     </row>
     <row r="688" spans="1:6" ht="173.25" customHeight="1">
-      <c r="A688" s="94"/>
+      <c r="A688" s="97"/>
       <c r="B688" s="5" t="s">
         <v>1490</v>
       </c>
@@ -23008,7 +23008,7 @@
       <c r="F688" s="23"/>
     </row>
     <row r="689" spans="1:6" ht="253.5" customHeight="1">
-      <c r="A689" s="94"/>
+      <c r="A689" s="97"/>
       <c r="B689" s="5" t="s">
         <v>1492</v>
       </c>
@@ -23024,7 +23024,7 @@
       <c r="F689" s="23"/>
     </row>
     <row r="690" spans="1:6" ht="250.5" customHeight="1">
-      <c r="A690" s="94"/>
+      <c r="A690" s="97"/>
       <c r="B690" s="5" t="s">
         <v>1495</v>
       </c>
@@ -23040,7 +23040,7 @@
       <c r="F690" s="23"/>
     </row>
     <row r="691" spans="1:6" ht="109.5" customHeight="1">
-      <c r="A691" s="94"/>
+      <c r="A691" s="97"/>
       <c r="B691" s="5" t="s">
         <v>1497</v>
       </c>
@@ -23054,7 +23054,7 @@
       <c r="F691" s="23"/>
     </row>
     <row r="692" spans="1:6" ht="114.75" customHeight="1">
-      <c r="A692" s="94"/>
+      <c r="A692" s="97"/>
       <c r="B692" s="5" t="s">
         <v>1499</v>
       </c>
@@ -23070,7 +23070,7 @@
       <c r="F692" s="23"/>
     </row>
     <row r="693" spans="1:6" ht="70">
-      <c r="A693" s="94"/>
+      <c r="A693" s="97"/>
       <c r="B693" s="5" t="s">
         <v>1501</v>
       </c>
@@ -23086,7 +23086,7 @@
       <c r="F693" s="23"/>
     </row>
     <row r="694" spans="1:6" ht="120.75" customHeight="1">
-      <c r="A694" s="94"/>
+      <c r="A694" s="97"/>
       <c r="B694" s="5" t="s">
         <v>1504</v>
       </c>
@@ -23102,7 +23102,7 @@
       <c r="F694" s="23"/>
     </row>
     <row r="695" spans="1:6" ht="31">
-      <c r="A695" s="94"/>
+      <c r="A695" s="97"/>
       <c r="B695" s="5" t="s">
         <v>1506</v>
       </c>
@@ -23116,7 +23116,7 @@
       <c r="F695" s="23"/>
     </row>
     <row r="696" spans="1:6" ht="77.5">
-      <c r="A696" s="94"/>
+      <c r="A696" s="97"/>
       <c r="B696" s="5" t="s">
         <v>1465</v>
       </c>
@@ -23130,7 +23130,7 @@
       <c r="F696" s="23"/>
     </row>
     <row r="697" spans="1:6" ht="74.25" customHeight="1">
-      <c r="A697" s="94"/>
+      <c r="A697" s="97"/>
       <c r="B697" s="5" t="s">
         <v>1510</v>
       </c>
@@ -23144,7 +23144,7 @@
       <c r="F697" s="23"/>
     </row>
     <row r="698" spans="1:6" ht="62">
-      <c r="A698" s="94"/>
+      <c r="A698" s="97"/>
       <c r="B698" s="5" t="s">
         <v>1512</v>
       </c>
@@ -23158,7 +23158,7 @@
       <c r="F698" s="23"/>
     </row>
     <row r="699" spans="1:6" ht="31">
-      <c r="A699" s="94"/>
+      <c r="A699" s="97"/>
       <c r="B699" s="5" t="s">
         <v>1514</v>
       </c>
@@ -23172,7 +23172,7 @@
       <c r="F699" s="23"/>
     </row>
     <row r="700" spans="1:6" ht="62">
-      <c r="A700" s="94"/>
+      <c r="A700" s="97"/>
       <c r="B700" s="5" t="s">
         <v>1516</v>
       </c>
@@ -23186,7 +23186,7 @@
       <c r="F700" s="23"/>
     </row>
     <row r="701" spans="1:6" ht="31">
-      <c r="A701" s="94"/>
+      <c r="A701" s="97"/>
       <c r="B701" s="5" t="s">
         <v>1518</v>
       </c>
@@ -23200,7 +23200,7 @@
       <c r="F701" s="23"/>
     </row>
     <row r="702" spans="1:6" ht="77.5">
-      <c r="A702" s="94"/>
+      <c r="A702" s="97"/>
       <c r="B702" s="5" t="s">
         <v>1519</v>
       </c>
@@ -23214,7 +23214,7 @@
       <c r="F702" s="23"/>
     </row>
     <row r="703" spans="1:6" ht="15.5">
-      <c r="A703" s="94"/>
+      <c r="A703" s="97"/>
       <c r="B703" s="5" t="s">
         <v>1521</v>
       </c>
@@ -23228,7 +23228,7 @@
       <c r="F703" s="23"/>
     </row>
     <row r="704" spans="1:6" ht="170.5">
-      <c r="A704" s="94"/>
+      <c r="A704" s="97"/>
       <c r="B704" s="5" t="s">
         <v>1523</v>
       </c>
@@ -23242,7 +23242,7 @@
       <c r="F704" s="23"/>
     </row>
     <row r="705" spans="1:6" ht="61.5" customHeight="1">
-      <c r="A705" s="94"/>
+      <c r="A705" s="97"/>
       <c r="B705" s="5" t="s">
         <v>1525</v>
       </c>
@@ -23256,7 +23256,7 @@
       <c r="F705" s="23"/>
     </row>
     <row r="706" spans="1:6" ht="15.5">
-      <c r="A706" s="94"/>
+      <c r="A706" s="97"/>
       <c r="B706" s="5" t="s">
         <v>1527</v>
       </c>
@@ -23270,7 +23270,7 @@
       <c r="F706" s="23"/>
     </row>
     <row r="707" spans="1:6" ht="46.5">
-      <c r="A707" s="94"/>
+      <c r="A707" s="97"/>
       <c r="B707" s="5" t="s">
         <v>1529</v>
       </c>
@@ -23284,7 +23284,7 @@
       <c r="F707" s="23"/>
     </row>
     <row r="708" spans="1:6" ht="188.25" customHeight="1">
-      <c r="A708" s="94"/>
+      <c r="A708" s="97"/>
       <c r="B708" s="5" t="s">
         <v>1531</v>
       </c>
@@ -23298,7 +23298,7 @@
       <c r="F708" s="23"/>
     </row>
     <row r="709" spans="1:6" ht="77.5">
-      <c r="A709" s="94"/>
+      <c r="A709" s="97"/>
       <c r="B709" s="5" t="s">
         <v>1534</v>
       </c>
@@ -23312,7 +23312,7 @@
       <c r="F709" s="23"/>
     </row>
     <row r="710" spans="1:6" ht="31">
-      <c r="A710" s="94"/>
+      <c r="A710" s="97"/>
       <c r="B710" s="5" t="s">
         <v>1536</v>
       </c>
@@ -23326,7 +23326,7 @@
       <c r="F710" s="23"/>
     </row>
     <row r="711" spans="1:6" ht="31">
-      <c r="A711" s="94"/>
+      <c r="A711" s="97"/>
       <c r="B711" s="5" t="s">
         <v>1538</v>
       </c>
@@ -23340,7 +23340,7 @@
       <c r="F711" s="23"/>
     </row>
     <row r="712" spans="1:6" ht="128.25" customHeight="1">
-      <c r="A712" s="94"/>
+      <c r="A712" s="97"/>
       <c r="B712" s="5" t="s">
         <v>1540</v>
       </c>
@@ -23354,7 +23354,7 @@
       <c r="F712" s="23"/>
     </row>
     <row r="713" spans="1:6" ht="194.25" customHeight="1">
-      <c r="A713" s="94"/>
+      <c r="A713" s="97"/>
       <c r="B713" s="5" t="s">
         <v>1542</v>
       </c>
@@ -23368,7 +23368,7 @@
       <c r="F713" s="23"/>
     </row>
     <row r="714" spans="1:6" ht="93">
-      <c r="A714" s="94"/>
+      <c r="A714" s="97"/>
       <c r="B714" s="5" t="s">
         <v>1544</v>
       </c>
@@ -23382,7 +23382,7 @@
       <c r="F714" s="23"/>
     </row>
     <row r="715" spans="1:6" ht="77.5">
-      <c r="A715" s="94"/>
+      <c r="A715" s="97"/>
       <c r="B715" s="5" t="s">
         <v>1546</v>
       </c>
@@ -23396,7 +23396,7 @@
       <c r="F715" s="23"/>
     </row>
     <row r="716" spans="1:6" ht="31">
-      <c r="A716" s="94"/>
+      <c r="A716" s="97"/>
       <c r="B716" s="5" t="s">
         <v>1469</v>
       </c>
@@ -23410,7 +23410,7 @@
       <c r="F716" s="23"/>
     </row>
     <row r="717" spans="1:6" ht="31">
-      <c r="A717" s="94"/>
+      <c r="A717" s="97"/>
       <c r="B717" s="5" t="s">
         <v>1548</v>
       </c>
@@ -23424,7 +23424,7 @@
       <c r="F717" s="23"/>
     </row>
     <row r="718" spans="1:6" ht="46.5">
-      <c r="A718" s="94"/>
+      <c r="A718" s="97"/>
       <c r="B718" s="5" t="s">
         <v>1549</v>
       </c>
@@ -23438,7 +23438,7 @@
       <c r="F718" s="23"/>
     </row>
     <row r="719" spans="1:6" ht="15.5">
-      <c r="A719" s="94"/>
+      <c r="A719" s="97"/>
       <c r="B719" s="5" t="s">
         <v>1551</v>
       </c>
@@ -23452,7 +23452,7 @@
       <c r="F719" s="23"/>
     </row>
     <row r="720" spans="1:6" ht="139.5">
-      <c r="A720" s="94"/>
+      <c r="A720" s="97"/>
       <c r="B720" s="5" t="s">
         <v>1553</v>
       </c>
@@ -23466,7 +23466,7 @@
       <c r="F720" s="23"/>
     </row>
     <row r="721" spans="1:6" ht="15.5">
-      <c r="A721" s="94"/>
+      <c r="A721" s="97"/>
       <c r="B721" s="5" t="s">
         <v>1555</v>
       </c>
@@ -23480,7 +23480,7 @@
       <c r="F721" s="23"/>
     </row>
     <row r="722" spans="1:6" ht="15.5">
-      <c r="A722" s="94"/>
+      <c r="A722" s="97"/>
       <c r="B722" s="5" t="s">
         <v>1557</v>
       </c>
@@ -23494,7 +23494,7 @@
       <c r="F722" s="23"/>
     </row>
     <row r="723" spans="1:6" ht="15.5">
-      <c r="A723" s="94"/>
+      <c r="A723" s="97"/>
       <c r="B723" s="5" t="s">
         <v>1559</v>
       </c>
@@ -23508,7 +23508,7 @@
       <c r="F723" s="23"/>
     </row>
     <row r="724" spans="1:6" ht="15.5">
-      <c r="A724" s="94"/>
+      <c r="A724" s="97"/>
       <c r="B724" s="5" t="s">
         <v>1561</v>
       </c>
@@ -23522,7 +23522,7 @@
       <c r="F724" s="23"/>
     </row>
     <row r="725" spans="1:6" ht="88.5" customHeight="1">
-      <c r="A725" s="94"/>
+      <c r="A725" s="97"/>
       <c r="B725" s="5" t="s">
         <v>1563</v>
       </c>
@@ -23536,7 +23536,7 @@
       <c r="F725" s="23"/>
     </row>
     <row r="726" spans="1:6" ht="140.25" customHeight="1">
-      <c r="A726" s="94"/>
+      <c r="A726" s="97"/>
       <c r="B726" s="5" t="s">
         <v>1565</v>
       </c>
@@ -23550,7 +23550,7 @@
       <c r="F726" s="23"/>
     </row>
     <row r="727" spans="1:6" ht="31">
-      <c r="A727" s="94"/>
+      <c r="A727" s="97"/>
       <c r="B727" s="5" t="s">
         <v>1567</v>
       </c>
@@ -23564,7 +23564,7 @@
       <c r="F727" s="23"/>
     </row>
     <row r="728" spans="1:6" ht="31">
-      <c r="A728" s="94"/>
+      <c r="A728" s="97"/>
       <c r="B728" s="5" t="s">
         <v>1569</v>
       </c>
@@ -23578,7 +23578,7 @@
       <c r="F728" s="23"/>
     </row>
     <row r="729" spans="1:6" ht="31">
-      <c r="A729" s="94"/>
+      <c r="A729" s="97"/>
       <c r="B729" s="5" t="s">
         <v>1571</v>
       </c>
@@ -23592,7 +23592,7 @@
       <c r="F729" s="23"/>
     </row>
     <row r="730" spans="1:6" ht="46.5">
-      <c r="A730" s="94"/>
+      <c r="A730" s="97"/>
       <c r="B730" s="5" t="s">
         <v>1573</v>
       </c>
@@ -23606,7 +23606,7 @@
       <c r="F730" s="23"/>
     </row>
     <row r="731" spans="1:6" ht="31">
-      <c r="A731" s="94"/>
+      <c r="A731" s="97"/>
       <c r="B731" s="5" t="s">
         <v>1575</v>
       </c>
@@ -23620,7 +23620,7 @@
       <c r="F731" s="23"/>
     </row>
     <row r="732" spans="1:6" ht="120" customHeight="1">
-      <c r="A732" s="94"/>
+      <c r="A732" s="97"/>
       <c r="B732" s="5" t="s">
         <v>1577</v>
       </c>
@@ -23636,7 +23636,7 @@
       <c r="F732" s="23"/>
     </row>
     <row r="733" spans="1:6" ht="15.5">
-      <c r="A733" s="94"/>
+      <c r="A733" s="97"/>
       <c r="B733" s="5" t="s">
         <v>1579</v>
       </c>
@@ -23652,7 +23652,7 @@
       <c r="F733" s="23"/>
     </row>
     <row r="734" spans="1:6" ht="99" customHeight="1">
-      <c r="A734" s="94"/>
+      <c r="A734" s="97"/>
       <c r="B734" s="5" t="s">
         <v>1581</v>
       </c>
@@ -23668,7 +23668,7 @@
       <c r="F734" s="23"/>
     </row>
     <row r="735" spans="1:6" ht="31">
-      <c r="A735" s="94"/>
+      <c r="A735" s="97"/>
       <c r="B735" s="5" t="s">
         <v>1583</v>
       </c>
@@ -23682,7 +23682,7 @@
       <c r="F735" s="23"/>
     </row>
     <row r="736" spans="1:6" ht="77.5">
-      <c r="A736" s="94"/>
+      <c r="A736" s="97"/>
       <c r="B736" s="5" t="s">
         <v>1478</v>
       </c>
@@ -23696,7 +23696,7 @@
       <c r="F736" s="23"/>
     </row>
     <row r="737" spans="1:6" ht="77.5">
-      <c r="A737" s="94"/>
+      <c r="A737" s="97"/>
       <c r="B737" s="5" t="s">
         <v>1586</v>
       </c>
@@ -23712,7 +23712,7 @@
       <c r="F737" s="23"/>
     </row>
     <row r="738" spans="1:6" ht="75.75" customHeight="1">
-      <c r="A738" s="94"/>
+      <c r="A738" s="97"/>
       <c r="B738" s="5" t="s">
         <v>1588</v>
       </c>
@@ -23726,7 +23726,7 @@
       <c r="F738" s="23"/>
     </row>
     <row r="739" spans="1:6" ht="31">
-      <c r="A739" s="94"/>
+      <c r="A739" s="97"/>
       <c r="B739" s="5" t="s">
         <v>1590</v>
       </c>
@@ -23740,7 +23740,7 @@
       <c r="F739" s="23"/>
     </row>
     <row r="740" spans="1:6" ht="93">
-      <c r="A740" s="94"/>
+      <c r="A740" s="97"/>
       <c r="B740" s="5" t="s">
         <v>1474</v>
       </c>
@@ -23754,7 +23754,7 @@
       <c r="F740" s="23"/>
     </row>
     <row r="741" spans="1:6" ht="15.5">
-      <c r="A741" s="94"/>
+      <c r="A741" s="97"/>
       <c r="B741" s="1" t="s">
         <v>1593</v>
       </c>
@@ -23768,7 +23768,7 @@
       <c r="F741" s="23"/>
     </row>
     <row r="742" spans="1:6" ht="15.5">
-      <c r="A742" s="94"/>
+      <c r="A742" s="97"/>
       <c r="B742" s="1" t="s">
         <v>1595</v>
       </c>
@@ -23782,7 +23782,7 @@
       <c r="F742" s="23"/>
     </row>
     <row r="743" spans="1:6" ht="93">
-      <c r="A743" s="94"/>
+      <c r="A743" s="97"/>
       <c r="B743" s="5" t="s">
         <v>1597</v>
       </c>
@@ -23796,7 +23796,7 @@
       <c r="F743" s="23"/>
     </row>
     <row r="744" spans="1:6" ht="93">
-      <c r="A744" s="94"/>
+      <c r="A744" s="97"/>
       <c r="B744" s="5" t="s">
         <v>1599</v>
       </c>
@@ -23810,7 +23810,7 @@
       <c r="F744" s="23"/>
     </row>
     <row r="745" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A745" s="94"/>
+      <c r="A745" s="97"/>
       <c r="B745" s="5" t="s">
         <v>1601</v>
       </c>
@@ -23824,7 +23824,7 @@
       <c r="F745" s="23"/>
     </row>
     <row r="746" spans="1:6" ht="75.75" customHeight="1">
-      <c r="A746" s="94"/>
+      <c r="A746" s="97"/>
       <c r="B746" s="5" t="s">
         <v>1480</v>
       </c>
@@ -23838,7 +23838,7 @@
       <c r="F746" s="23"/>
     </row>
     <row r="747" spans="1:6" ht="15.5">
-      <c r="A747" s="94"/>
+      <c r="A747" s="97"/>
       <c r="B747" s="5" t="s">
         <v>1604</v>
       </c>
@@ -23852,7 +23852,7 @@
       <c r="F747" s="23"/>
     </row>
     <row r="748" spans="1:6" ht="77.5">
-      <c r="A748" s="94"/>
+      <c r="A748" s="97"/>
       <c r="B748" s="5" t="s">
         <v>1606</v>
       </c>
@@ -23866,7 +23866,7 @@
       <c r="F748" s="23"/>
     </row>
     <row r="749" spans="1:6" ht="124">
-      <c r="A749" s="94"/>
+      <c r="A749" s="97"/>
       <c r="B749" s="5" t="s">
         <v>1608</v>
       </c>
@@ -23880,7 +23880,7 @@
       <c r="F749" s="23"/>
     </row>
     <row r="750" spans="1:6" ht="62">
-      <c r="A750" s="94"/>
+      <c r="A750" s="97"/>
       <c r="B750" s="5" t="s">
         <v>1610</v>
       </c>
@@ -23894,7 +23894,7 @@
       <c r="F750" s="23"/>
     </row>
     <row r="751" spans="1:6" ht="90" customHeight="1">
-      <c r="A751" s="94"/>
+      <c r="A751" s="97"/>
       <c r="B751" s="5" t="s">
         <v>1612</v>
       </c>
@@ -23908,7 +23908,7 @@
       <c r="F751" s="23"/>
     </row>
     <row r="752" spans="1:6" ht="31">
-      <c r="A752" s="94"/>
+      <c r="A752" s="97"/>
       <c r="B752" s="5" t="s">
         <v>1614</v>
       </c>
@@ -23924,7 +23924,7 @@
       <c r="F752" s="23"/>
     </row>
     <row r="753" spans="1:6" ht="103.5" customHeight="1">
-      <c r="A753" s="94"/>
+      <c r="A753" s="97"/>
       <c r="B753" s="5" t="s">
         <v>1617</v>
       </c>
@@ -23938,7 +23938,7 @@
       <c r="F753" s="23"/>
     </row>
     <row r="754" spans="1:6" ht="124">
-      <c r="A754" s="94"/>
+      <c r="A754" s="97"/>
       <c r="B754" s="5" t="s">
         <v>1619</v>
       </c>
@@ -23952,7 +23952,7 @@
       <c r="F754" s="23"/>
     </row>
     <row r="755" spans="1:6" ht="108.5">
-      <c r="A755" s="94"/>
+      <c r="A755" s="97"/>
       <c r="B755" s="5" t="s">
         <v>1621</v>
       </c>
@@ -23966,7 +23966,7 @@
       <c r="F755" s="23"/>
     </row>
     <row r="756" spans="1:6" ht="62">
-      <c r="A756" s="94"/>
+      <c r="A756" s="97"/>
       <c r="B756" s="5" t="s">
         <v>1623</v>
       </c>
@@ -23980,7 +23980,7 @@
       <c r="F756" s="23"/>
     </row>
     <row r="757" spans="1:6" ht="62">
-      <c r="A757" s="94"/>
+      <c r="A757" s="97"/>
       <c r="B757" s="5" t="s">
         <v>1625</v>
       </c>
@@ -23996,7 +23996,7 @@
       <c r="F757" s="23"/>
     </row>
     <row r="758" spans="1:6" ht="31">
-      <c r="A758" s="94"/>
+      <c r="A758" s="97"/>
       <c r="B758" s="5" t="s">
         <v>1628</v>
       </c>
@@ -24012,7 +24012,7 @@
       <c r="F758" s="23"/>
     </row>
     <row r="759" spans="1:6" ht="46.5">
-      <c r="A759" s="94"/>
+      <c r="A759" s="97"/>
       <c r="B759" s="5" t="s">
         <v>1631</v>
       </c>
@@ -24028,7 +24028,7 @@
       <c r="F759" s="23"/>
     </row>
     <row r="760" spans="1:6" ht="15.5">
-      <c r="A760" s="94"/>
+      <c r="A760" s="97"/>
       <c r="B760" s="5" t="s">
         <v>1634</v>
       </c>
@@ -24042,7 +24042,7 @@
       <c r="F760" s="23"/>
     </row>
     <row r="761" spans="1:6" ht="46.5">
-      <c r="A761" s="94"/>
+      <c r="A761" s="97"/>
       <c r="B761" s="5" t="s">
         <v>1636</v>
       </c>
@@ -24058,7 +24058,7 @@
       <c r="F761" s="23"/>
     </row>
     <row r="762" spans="1:6" ht="15.5">
-      <c r="A762" s="94"/>
+      <c r="A762" s="97"/>
       <c r="B762" s="5" t="s">
         <v>1637</v>
       </c>
@@ -24072,7 +24072,7 @@
       <c r="F762" s="23"/>
     </row>
     <row r="763" spans="1:6" ht="31">
-      <c r="A763" s="94"/>
+      <c r="A763" s="97"/>
       <c r="B763" s="5" t="s">
         <v>1639</v>
       </c>
@@ -24086,7 +24086,7 @@
       <c r="F763" s="23"/>
     </row>
     <row r="764" spans="1:6" ht="31">
-      <c r="A764" s="94"/>
+      <c r="A764" s="97"/>
       <c r="B764" s="5" t="s">
         <v>1641</v>
       </c>
@@ -24100,7 +24100,7 @@
       <c r="F764" s="23"/>
     </row>
     <row r="765" spans="1:6" ht="92.25" customHeight="1">
-      <c r="A765" s="94"/>
+      <c r="A765" s="97"/>
       <c r="B765" s="5" t="s">
         <v>1643</v>
       </c>
@@ -24116,7 +24116,7 @@
       <c r="F765" s="23"/>
     </row>
     <row r="766" spans="1:6" ht="77.5">
-      <c r="A766" s="94"/>
+      <c r="A766" s="97"/>
       <c r="B766" s="5" t="s">
         <v>1645</v>
       </c>
@@ -24130,7 +24130,7 @@
       <c r="F766" s="23"/>
     </row>
     <row r="767" spans="1:6" ht="15.5">
-      <c r="A767" s="94"/>
+      <c r="A767" s="97"/>
       <c r="B767" s="5" t="s">
         <v>1647</v>
       </c>
@@ -24144,7 +24144,7 @@
       <c r="F767" s="23"/>
     </row>
     <row r="768" spans="1:6" ht="77.5">
-      <c r="A768" s="94"/>
+      <c r="A768" s="97"/>
       <c r="B768" s="5" t="s">
         <v>1649</v>
       </c>
@@ -24158,7 +24158,7 @@
       <c r="F768" s="23"/>
     </row>
     <row r="769" spans="1:6" ht="77.5">
-      <c r="A769" s="94"/>
+      <c r="A769" s="97"/>
       <c r="B769" s="5" t="s">
         <v>1652</v>
       </c>
@@ -24172,7 +24172,7 @@
       <c r="F769" s="23"/>
     </row>
     <row r="770" spans="1:6" ht="31">
-      <c r="A770" s="94"/>
+      <c r="A770" s="97"/>
       <c r="B770" s="5" t="s">
         <v>1654</v>
       </c>
@@ -24186,7 +24186,7 @@
       <c r="F770" s="23"/>
     </row>
     <row r="771" spans="1:6" ht="15.5">
-      <c r="A771" s="94"/>
+      <c r="A771" s="97"/>
       <c r="B771" s="5" t="s">
         <v>1656</v>
       </c>
@@ -24200,7 +24200,7 @@
       <c r="F771" s="23"/>
     </row>
     <row r="772" spans="1:6" ht="15.5">
-      <c r="A772" s="94"/>
+      <c r="A772" s="97"/>
       <c r="B772" s="5" t="s">
         <v>1658</v>
       </c>
@@ -24214,7 +24214,7 @@
       <c r="F772" s="23"/>
     </row>
     <row r="773" spans="1:6" ht="78" customHeight="1">
-      <c r="A773" s="94"/>
+      <c r="A773" s="97"/>
       <c r="B773" s="5" t="s">
         <v>1660</v>
       </c>
@@ -24228,7 +24228,7 @@
       <c r="F773" s="23"/>
     </row>
     <row r="774" spans="1:6" ht="31">
-      <c r="A774" s="94"/>
+      <c r="A774" s="97"/>
       <c r="B774" s="5" t="s">
         <v>1663</v>
       </c>
@@ -24242,7 +24242,7 @@
       <c r="F774" s="23"/>
     </row>
     <row r="775" spans="1:6" ht="15.5">
-      <c r="A775" s="94"/>
+      <c r="A775" s="97"/>
       <c r="B775" s="5" t="s">
         <v>1665</v>
       </c>
@@ -24256,7 +24256,7 @@
       <c r="F775" s="23"/>
     </row>
     <row r="776" spans="1:6" ht="31">
-      <c r="A776" s="94"/>
+      <c r="A776" s="97"/>
       <c r="B776" s="5" t="s">
         <v>1667</v>
       </c>
@@ -24270,7 +24270,7 @@
       <c r="F776" s="23"/>
     </row>
     <row r="777" spans="1:6" ht="39.75" customHeight="1">
-      <c r="A777" s="94"/>
+      <c r="A777" s="97"/>
       <c r="B777" s="5" t="s">
         <v>1669</v>
       </c>
@@ -24284,7 +24284,7 @@
       <c r="F777" s="23"/>
     </row>
     <row r="778" spans="1:6" ht="47.25" customHeight="1">
-      <c r="A778" s="99" t="s">
+      <c r="A778" s="104" t="s">
         <v>1672</v>
       </c>
       <c r="B778" s="76" t="s">
@@ -24300,7 +24300,7 @@
       <c r="F778" s="23"/>
     </row>
     <row r="779" spans="1:6" ht="174" customHeight="1">
-      <c r="A779" s="100"/>
+      <c r="A779" s="105"/>
       <c r="B779" s="5" t="s">
         <v>1676</v>
       </c>
@@ -24314,7 +24314,7 @@
       <c r="F779" s="23"/>
     </row>
     <row r="780" spans="1:6" ht="47.25" customHeight="1">
-      <c r="A780" s="100"/>
+      <c r="A780" s="105"/>
       <c r="B780" s="5" t="s">
         <v>1678</v>
       </c>
@@ -24328,7 +24328,7 @@
       <c r="F780" s="23"/>
     </row>
     <row r="781" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A781" s="100"/>
+      <c r="A781" s="105"/>
       <c r="B781" s="5" t="s">
         <v>1679</v>
       </c>
@@ -24342,7 +24342,7 @@
       <c r="F781" s="23"/>
     </row>
     <row r="782" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A782" s="100"/>
+      <c r="A782" s="105"/>
       <c r="B782" s="5" t="s">
         <v>1680</v>
       </c>
@@ -24356,7 +24356,7 @@
       <c r="F782" s="23"/>
     </row>
     <row r="783" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A783" s="100"/>
+      <c r="A783" s="105"/>
       <c r="B783" s="5" t="s">
         <v>1682</v>
       </c>
@@ -24370,7 +24370,7 @@
       <c r="F783" s="23"/>
     </row>
     <row r="784" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A784" s="100"/>
+      <c r="A784" s="105"/>
       <c r="B784" s="5" t="s">
         <v>1684</v>
       </c>
@@ -24384,7 +24384,7 @@
       <c r="F784" s="23"/>
     </row>
     <row r="785" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A785" s="100"/>
+      <c r="A785" s="105"/>
       <c r="B785" s="5" t="s">
         <v>1686</v>
       </c>
@@ -24398,7 +24398,7 @@
       <c r="F785" s="23"/>
     </row>
     <row r="786" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A786" s="100"/>
+      <c r="A786" s="105"/>
       <c r="B786" s="5" t="s">
         <v>1688</v>
       </c>
@@ -24412,7 +24412,7 @@
       <c r="F786" s="23"/>
     </row>
     <row r="787" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A787" s="100"/>
+      <c r="A787" s="105"/>
       <c r="B787" s="5" t="s">
         <v>1689</v>
       </c>
@@ -24426,7 +24426,7 @@
       <c r="F787" s="23"/>
     </row>
     <row r="788" spans="1:6" ht="135" customHeight="1">
-      <c r="A788" s="100"/>
+      <c r="A788" s="105"/>
       <c r="B788" s="5" t="s">
         <v>1691</v>
       </c>
@@ -24440,7 +24440,7 @@
       <c r="F788" s="23"/>
     </row>
     <row r="789" spans="1:6" ht="105" customHeight="1">
-      <c r="A789" s="100"/>
+      <c r="A789" s="105"/>
       <c r="B789" s="5" t="s">
         <v>1693</v>
       </c>
@@ -24454,7 +24454,7 @@
       <c r="F789" s="23"/>
     </row>
     <row r="790" spans="1:6" ht="106.5" customHeight="1">
-      <c r="A790" s="100"/>
+      <c r="A790" s="105"/>
       <c r="B790" s="5" t="s">
         <v>1695</v>
       </c>
@@ -24468,7 +24468,7 @@
       <c r="F790" s="23"/>
     </row>
     <row r="791" spans="1:6" ht="109.5" customHeight="1">
-      <c r="A791" s="100"/>
+      <c r="A791" s="105"/>
       <c r="B791" s="5" t="s">
         <v>1697</v>
       </c>
@@ -24482,7 +24482,7 @@
       <c r="F791" s="23"/>
     </row>
     <row r="792" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A792" s="100"/>
+      <c r="A792" s="105"/>
       <c r="B792" s="5" t="s">
         <v>1699</v>
       </c>
@@ -24496,7 +24496,7 @@
       <c r="F792" s="23"/>
     </row>
     <row r="793" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A793" s="100"/>
+      <c r="A793" s="105"/>
       <c r="B793" s="5" t="s">
         <v>1701</v>
       </c>
@@ -24510,7 +24510,7 @@
       <c r="F793" s="23"/>
     </row>
     <row r="794" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A794" s="100"/>
+      <c r="A794" s="105"/>
       <c r="B794" s="5" t="s">
         <v>1703</v>
       </c>
@@ -24524,7 +24524,7 @@
       <c r="F794" s="23"/>
     </row>
     <row r="795" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A795" s="100"/>
+      <c r="A795" s="105"/>
       <c r="B795" s="5" t="s">
         <v>1705</v>
       </c>
@@ -24538,7 +24538,7 @@
       <c r="F795" s="23"/>
     </row>
     <row r="796" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A796" s="100"/>
+      <c r="A796" s="105"/>
       <c r="B796" s="5" t="s">
         <v>1707</v>
       </c>
@@ -24552,7 +24552,7 @@
       <c r="F796" s="23"/>
     </row>
     <row r="797" spans="1:6" ht="15.5">
-      <c r="A797" s="100"/>
+      <c r="A797" s="105"/>
       <c r="B797" s="5" t="s">
         <v>1709</v>
       </c>
@@ -24566,7 +24566,7 @@
       <c r="F797" s="23"/>
     </row>
     <row r="798" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A798" s="100"/>
+      <c r="A798" s="105"/>
       <c r="B798" s="5" t="s">
         <v>1711</v>
       </c>
@@ -24580,7 +24580,7 @@
       <c r="F798" s="23"/>
     </row>
     <row r="799" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A799" s="100"/>
+      <c r="A799" s="105"/>
       <c r="B799" s="5" t="s">
         <v>1713</v>
       </c>
@@ -24594,7 +24594,7 @@
       <c r="F799" s="23"/>
     </row>
     <row r="800" spans="1:6" ht="39" customHeight="1">
-      <c r="A800" s="100"/>
+      <c r="A800" s="105"/>
       <c r="B800" s="5" t="s">
         <v>1715</v>
       </c>
@@ -24608,7 +24608,7 @@
       <c r="F800" s="23"/>
     </row>
     <row r="801" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A801" s="100"/>
+      <c r="A801" s="105"/>
       <c r="B801" s="5" t="s">
         <v>1717</v>
       </c>
@@ -24622,7 +24622,7 @@
       <c r="F801" s="23"/>
     </row>
     <row r="802" spans="1:6" ht="64.5" customHeight="1">
-      <c r="A802" s="100"/>
+      <c r="A802" s="105"/>
       <c r="B802" s="5" t="s">
         <v>1719</v>
       </c>
@@ -24636,7 +24636,7 @@
       <c r="F802" s="23"/>
     </row>
     <row r="803" spans="1:6" ht="51" customHeight="1">
-      <c r="A803" s="100"/>
+      <c r="A803" s="105"/>
       <c r="B803" s="5" t="s">
         <v>1721</v>
       </c>
@@ -24650,7 +24650,7 @@
       <c r="F803" s="23"/>
     </row>
     <row r="804" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A804" s="100"/>
+      <c r="A804" s="105"/>
       <c r="B804" s="5" t="s">
         <v>1723</v>
       </c>
@@ -24664,7 +24664,7 @@
       <c r="F804" s="23"/>
     </row>
     <row r="805" spans="1:6" ht="69" customHeight="1">
-      <c r="A805" s="100"/>
+      <c r="A805" s="105"/>
       <c r="B805" s="5" t="s">
         <v>1725</v>
       </c>
@@ -24678,7 +24678,7 @@
       <c r="F805" s="23"/>
     </row>
     <row r="806" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A806" s="100"/>
+      <c r="A806" s="105"/>
       <c r="B806" s="5" t="s">
         <v>1727</v>
       </c>
@@ -24692,7 +24692,7 @@
       <c r="F806" s="23"/>
     </row>
     <row r="807" spans="1:6" s="24" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A807" s="100"/>
+      <c r="A807" s="105"/>
       <c r="B807" s="5" t="s">
         <v>1729</v>
       </c>
@@ -24706,7 +24706,7 @@
       <c r="F807" s="23"/>
     </row>
     <row r="808" spans="1:6" ht="138.75" customHeight="1">
-      <c r="A808" s="100"/>
+      <c r="A808" s="105"/>
       <c r="B808" s="5" t="s">
         <v>1731</v>
       </c>
@@ -24720,7 +24720,7 @@
       <c r="F808" s="23"/>
     </row>
     <row r="809" spans="1:6" ht="33" customHeight="1">
-      <c r="A809" s="100"/>
+      <c r="A809" s="105"/>
       <c r="B809" s="5" t="s">
         <v>1733</v>
       </c>
@@ -24734,7 +24734,7 @@
       <c r="F809" s="23"/>
     </row>
     <row r="810" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A810" s="100"/>
+      <c r="A810" s="105"/>
       <c r="B810" s="5" t="s">
         <v>1735</v>
       </c>
@@ -24748,7 +24748,7 @@
       <c r="F810" s="23"/>
     </row>
     <row r="811" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A811" s="100"/>
+      <c r="A811" s="105"/>
       <c r="B811" s="5" t="s">
         <v>1737</v>
       </c>
@@ -24762,7 +24762,7 @@
       <c r="F811" s="23"/>
     </row>
     <row r="812" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A812" s="100"/>
+      <c r="A812" s="105"/>
       <c r="B812" s="5" t="s">
         <v>1739</v>
       </c>
@@ -24776,7 +24776,7 @@
       <c r="F812" s="23"/>
     </row>
     <row r="813" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A813" s="100"/>
+      <c r="A813" s="105"/>
       <c r="B813" s="5" t="s">
         <v>1741</v>
       </c>
@@ -24790,7 +24790,7 @@
       <c r="F813" s="23"/>
     </row>
     <row r="814" spans="1:6" ht="57" customHeight="1">
-      <c r="A814" s="100"/>
+      <c r="A814" s="105"/>
       <c r="B814" s="5" t="s">
         <v>1743</v>
       </c>
@@ -24804,7 +24804,7 @@
       <c r="F814" s="23"/>
     </row>
     <row r="815" spans="1:6" ht="60" customHeight="1">
-      <c r="A815" s="100"/>
+      <c r="A815" s="105"/>
       <c r="B815" s="5" t="s">
         <v>1745</v>
       </c>
@@ -24818,7 +24818,7 @@
       <c r="F815" s="23"/>
     </row>
     <row r="816" spans="1:6" ht="36" customHeight="1">
-      <c r="A816" s="100"/>
+      <c r="A816" s="105"/>
       <c r="B816" s="5" t="s">
         <v>1747</v>
       </c>
@@ -24832,7 +24832,7 @@
       <c r="F816" s="23"/>
     </row>
     <row r="817" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A817" s="100"/>
+      <c r="A817" s="105"/>
       <c r="B817" s="5" t="s">
         <v>1749</v>
       </c>
@@ -24846,7 +24846,7 @@
       <c r="F817" s="23"/>
     </row>
     <row r="818" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A818" s="100"/>
+      <c r="A818" s="105"/>
       <c r="B818" s="27" t="s">
         <v>1751</v>
       </c>
@@ -24860,7 +24860,7 @@
       <c r="F818" s="23"/>
     </row>
     <row r="819" spans="1:6" ht="15.5">
-      <c r="A819" s="100"/>
+      <c r="A819" s="105"/>
       <c r="B819" s="27" t="s">
         <v>1753</v>
       </c>
@@ -24874,7 +24874,7 @@
       <c r="F819" s="23"/>
     </row>
     <row r="820" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A820" s="100"/>
+      <c r="A820" s="105"/>
       <c r="B820" s="5" t="s">
         <v>1755</v>
       </c>
@@ -24888,7 +24888,7 @@
       <c r="F820" s="23"/>
     </row>
     <row r="821" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A821" s="100"/>
+      <c r="A821" s="105"/>
       <c r="B821" s="5" t="s">
         <v>1757</v>
       </c>
@@ -24902,7 +24902,7 @@
       <c r="F821" s="23"/>
     </row>
     <row r="822" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A822" s="100"/>
+      <c r="A822" s="105"/>
       <c r="B822" s="5" t="s">
         <v>1758</v>
       </c>
@@ -24916,7 +24916,7 @@
       <c r="F822" s="23"/>
     </row>
     <row r="823" spans="1:6" ht="42" customHeight="1">
-      <c r="A823" s="100"/>
+      <c r="A823" s="105"/>
       <c r="B823" s="5" t="s">
         <v>1760</v>
       </c>
@@ -24930,7 +24930,7 @@
       <c r="F823" s="23"/>
     </row>
     <row r="824" spans="1:6" ht="69.75" customHeight="1">
-      <c r="A824" s="100"/>
+      <c r="A824" s="105"/>
       <c r="B824" s="5" t="s">
         <v>1762</v>
       </c>
@@ -24944,7 +24944,7 @@
       <c r="F824" s="23"/>
     </row>
     <row r="825" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A825" s="100"/>
+      <c r="A825" s="105"/>
       <c r="B825" s="5" t="s">
         <v>1764</v>
       </c>
@@ -24958,7 +24958,7 @@
       <c r="F825" s="23"/>
     </row>
     <row r="826" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A826" s="100"/>
+      <c r="A826" s="105"/>
       <c r="B826" s="5" t="s">
         <v>1766</v>
       </c>
@@ -24972,7 +24972,7 @@
       <c r="F826" s="23"/>
     </row>
     <row r="827" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A827" s="100"/>
+      <c r="A827" s="105"/>
       <c r="B827" s="5" t="s">
         <v>1768</v>
       </c>
@@ -24986,7 +24986,7 @@
       <c r="F827" s="23"/>
     </row>
     <row r="828" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A828" s="100"/>
+      <c r="A828" s="105"/>
       <c r="B828" s="5" t="s">
         <v>1684</v>
       </c>
@@ -25000,7 +25000,7 @@
       <c r="F828" s="23"/>
     </row>
     <row r="829" spans="1:6" ht="43.5" customHeight="1">
-      <c r="A829" s="100"/>
+      <c r="A829" s="105"/>
       <c r="B829" s="5" t="s">
         <v>1771</v>
       </c>
@@ -25014,7 +25014,7 @@
       <c r="F829" s="23"/>
     </row>
     <row r="830" spans="1:6" ht="84" customHeight="1">
-      <c r="A830" s="100"/>
+      <c r="A830" s="105"/>
       <c r="B830" s="5" t="s">
         <v>1773</v>
       </c>
@@ -25028,7 +25028,7 @@
       <c r="F830" s="23"/>
     </row>
     <row r="831" spans="1:6" ht="39.75" customHeight="1">
-      <c r="A831" s="100"/>
+      <c r="A831" s="105"/>
       <c r="B831" s="5" t="s">
         <v>1775</v>
       </c>
@@ -25042,7 +25042,7 @@
       <c r="F831" s="23"/>
     </row>
     <row r="832" spans="1:6" ht="31">
-      <c r="A832" s="100"/>
+      <c r="A832" s="105"/>
       <c r="B832" s="5" t="s">
         <v>1777</v>
       </c>
@@ -25056,7 +25056,7 @@
       <c r="F832" s="23"/>
     </row>
     <row r="833" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A833" s="100"/>
+      <c r="A833" s="105"/>
       <c r="B833" s="5" t="s">
         <v>1778</v>
       </c>
@@ -25070,7 +25070,7 @@
       <c r="F833" s="23"/>
     </row>
     <row r="834" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A834" s="100"/>
+      <c r="A834" s="105"/>
       <c r="B834" s="27" t="s">
         <v>1780</v>
       </c>
@@ -25084,7 +25084,7 @@
       <c r="F834" s="23"/>
     </row>
     <row r="835" spans="1:6" ht="45" customHeight="1">
-      <c r="A835" s="100"/>
+      <c r="A835" s="105"/>
       <c r="B835" s="27" t="s">
         <v>1782</v>
       </c>
@@ -25098,7 +25098,7 @@
       <c r="F835" s="23"/>
     </row>
     <row r="836" spans="1:6" ht="52.5" customHeight="1">
-      <c r="A836" s="100"/>
+      <c r="A836" s="105"/>
       <c r="B836" s="27" t="s">
         <v>1784</v>
       </c>
@@ -25112,7 +25112,7 @@
       <c r="F836" s="23"/>
     </row>
     <row r="837" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A837" s="100"/>
+      <c r="A837" s="105"/>
       <c r="B837" s="27" t="s">
         <v>1786</v>
       </c>
@@ -25126,7 +25126,7 @@
       <c r="F837" s="23"/>
     </row>
     <row r="838" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A838" s="100"/>
+      <c r="A838" s="105"/>
       <c r="B838" s="5" t="s">
         <v>1682</v>
       </c>
@@ -25140,7 +25140,7 @@
       <c r="F838" s="23"/>
     </row>
     <row r="839" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A839" s="100"/>
+      <c r="A839" s="105"/>
       <c r="B839" s="5" t="s">
         <v>1689</v>
       </c>
@@ -25154,7 +25154,7 @@
       <c r="F839" s="23"/>
     </row>
     <row r="840" spans="1:6" ht="36" customHeight="1">
-      <c r="A840" s="100"/>
+      <c r="A840" s="105"/>
       <c r="B840" s="5" t="s">
         <v>1790</v>
       </c>
@@ -25168,7 +25168,7 @@
       <c r="F840" s="23"/>
     </row>
     <row r="841" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A841" s="100"/>
+      <c r="A841" s="105"/>
       <c r="B841" s="5" t="s">
         <v>1792</v>
       </c>
@@ -25182,7 +25182,7 @@
       <c r="F841" s="23"/>
     </row>
     <row r="842" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A842" s="100"/>
+      <c r="A842" s="105"/>
       <c r="B842" s="5" t="s">
         <v>1794</v>
       </c>
@@ -25196,7 +25196,7 @@
       <c r="F842" s="23"/>
     </row>
     <row r="843" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A843" s="100"/>
+      <c r="A843" s="105"/>
       <c r="B843" s="5" t="s">
         <v>1795</v>
       </c>
@@ -25210,7 +25210,7 @@
       <c r="F843" s="23"/>
     </row>
     <row r="844" spans="1:6" ht="27" customHeight="1">
-      <c r="A844" s="100"/>
+      <c r="A844" s="105"/>
       <c r="B844" s="5" t="s">
         <v>1797</v>
       </c>
@@ -25224,7 +25224,7 @@
       <c r="F844" s="23"/>
     </row>
     <row r="845" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A845" s="100"/>
+      <c r="A845" s="105"/>
       <c r="B845" s="5" t="s">
         <v>1799</v>
       </c>
@@ -25238,7 +25238,7 @@
       <c r="F845" s="23"/>
     </row>
     <row r="846" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A846" s="100"/>
+      <c r="A846" s="105"/>
       <c r="B846" s="5" t="s">
         <v>1801</v>
       </c>
@@ -25252,7 +25252,7 @@
       <c r="F846" s="23"/>
     </row>
     <row r="847" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A847" s="100"/>
+      <c r="A847" s="105"/>
       <c r="B847" s="5" t="s">
         <v>1803</v>
       </c>
@@ -25266,7 +25266,7 @@
       <c r="F847" s="23"/>
     </row>
     <row r="848" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A848" s="100"/>
+      <c r="A848" s="105"/>
       <c r="B848" s="5" t="s">
         <v>1686</v>
       </c>
@@ -25280,7 +25280,7 @@
       <c r="F848" s="23"/>
     </row>
     <row r="849" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A849" s="100"/>
+      <c r="A849" s="105"/>
       <c r="B849" s="5" t="s">
         <v>1806</v>
       </c>
@@ -25294,7 +25294,7 @@
       <c r="F849" s="23"/>
     </row>
     <row r="850" spans="1:6" ht="42.75" customHeight="1">
-      <c r="A850" s="100"/>
+      <c r="A850" s="105"/>
       <c r="B850" s="5" t="s">
         <v>1808</v>
       </c>
@@ -25308,7 +25308,7 @@
       <c r="F850" s="23"/>
     </row>
     <row r="851" spans="1:6" ht="71.25" customHeight="1">
-      <c r="A851" s="100"/>
+      <c r="A851" s="105"/>
       <c r="B851" s="5" t="s">
         <v>1810</v>
       </c>
@@ -25322,7 +25322,7 @@
       <c r="F851" s="23"/>
     </row>
     <row r="852" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A852" s="100"/>
+      <c r="A852" s="105"/>
       <c r="B852" s="5" t="s">
         <v>1812</v>
       </c>
@@ -25336,7 +25336,7 @@
       <c r="F852" s="23"/>
     </row>
     <row r="853" spans="1:6" ht="36" customHeight="1">
-      <c r="A853" s="100"/>
+      <c r="A853" s="105"/>
       <c r="B853" s="5" t="s">
         <v>1814</v>
       </c>
@@ -25350,7 +25350,7 @@
       <c r="F853" s="23"/>
     </row>
     <row r="854" spans="1:6" ht="30" customHeight="1">
-      <c r="A854" s="100"/>
+      <c r="A854" s="105"/>
       <c r="B854" s="5" t="s">
         <v>1815</v>
       </c>
@@ -25364,7 +25364,7 @@
       <c r="F854" s="23"/>
     </row>
     <row r="855" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A855" s="100"/>
+      <c r="A855" s="105"/>
       <c r="B855" s="5" t="s">
         <v>1817</v>
       </c>
@@ -25378,7 +25378,7 @@
       <c r="F855" s="23"/>
     </row>
     <row r="856" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A856" s="100"/>
+      <c r="A856" s="105"/>
       <c r="B856" s="5" t="s">
         <v>1818</v>
       </c>
@@ -25392,7 +25392,7 @@
       <c r="F856" s="23"/>
     </row>
     <row r="857" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A857" s="100"/>
+      <c r="A857" s="105"/>
       <c r="B857" s="5" t="s">
         <v>1820</v>
       </c>
@@ -25406,7 +25406,7 @@
       <c r="F857" s="23"/>
     </row>
     <row r="858" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A858" s="100"/>
+      <c r="A858" s="105"/>
       <c r="B858" s="5" t="s">
         <v>1822</v>
       </c>
@@ -25420,7 +25420,7 @@
       <c r="F858" s="23"/>
     </row>
     <row r="859" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A859" s="100"/>
+      <c r="A859" s="105"/>
       <c r="B859" s="5" t="s">
         <v>1824</v>
       </c>
@@ -25434,7 +25434,7 @@
       <c r="F859" s="23"/>
     </row>
     <row r="860" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A860" s="100"/>
+      <c r="A860" s="105"/>
       <c r="B860" s="5" t="s">
         <v>1826</v>
       </c>
@@ -25448,7 +25448,7 @@
       <c r="F860" s="23"/>
     </row>
     <row r="861" spans="1:6" ht="50.25" customHeight="1">
-      <c r="A861" s="100"/>
+      <c r="A861" s="105"/>
       <c r="B861" s="5" t="s">
         <v>1828</v>
       </c>
@@ -25462,7 +25462,7 @@
       <c r="F861" s="23"/>
     </row>
     <row r="862" spans="1:6" s="24" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A862" s="100"/>
+      <c r="A862" s="105"/>
       <c r="B862" s="5" t="s">
         <v>1830</v>
       </c>
@@ -25476,7 +25476,7 @@
       <c r="F862" s="23"/>
     </row>
     <row r="863" spans="1:6" s="24" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A863" s="100"/>
+      <c r="A863" s="105"/>
       <c r="B863" s="5" t="s">
         <v>1832</v>
       </c>
@@ -25490,7 +25490,7 @@
       <c r="F863" s="23"/>
     </row>
     <row r="864" spans="1:6" s="24" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A864" s="100"/>
+      <c r="A864" s="105"/>
       <c r="B864" s="5" t="s">
         <v>1834</v>
       </c>
@@ -25504,7 +25504,7 @@
       <c r="F864" s="23"/>
     </row>
     <row r="865" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A865" s="100"/>
+      <c r="A865" s="105"/>
       <c r="B865" s="5" t="s">
         <v>1836</v>
       </c>
@@ -25518,7 +25518,7 @@
       <c r="F865" s="23"/>
     </row>
     <row r="866" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A866" s="100"/>
+      <c r="A866" s="105"/>
       <c r="B866" s="5" t="s">
         <v>1838</v>
       </c>
@@ -25532,7 +25532,7 @@
       <c r="F866" s="23"/>
     </row>
     <row r="867" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A867" s="100"/>
+      <c r="A867" s="105"/>
       <c r="B867" s="5" t="s">
         <v>1840</v>
       </c>
@@ -25546,7 +25546,7 @@
       <c r="F867" s="23"/>
     </row>
     <row r="868" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A868" s="100"/>
+      <c r="A868" s="105"/>
       <c r="B868" s="5" t="s">
         <v>1842</v>
       </c>
@@ -25560,7 +25560,7 @@
       <c r="F868" s="23"/>
     </row>
     <row r="869" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A869" s="100"/>
+      <c r="A869" s="105"/>
       <c r="B869" s="5" t="s">
         <v>1844</v>
       </c>
@@ -25574,7 +25574,7 @@
       <c r="F869" s="23"/>
     </row>
     <row r="870" spans="1:6" ht="15.5">
-      <c r="A870" s="100"/>
+      <c r="A870" s="105"/>
       <c r="B870" s="5" t="s">
         <v>1846</v>
       </c>
@@ -25588,7 +25588,7 @@
       <c r="F870" s="23"/>
     </row>
     <row r="871" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A871" s="100"/>
+      <c r="A871" s="105"/>
       <c r="B871" s="5" t="s">
         <v>1848</v>
       </c>
@@ -25602,7 +25602,7 @@
       <c r="F871" s="23"/>
     </row>
     <row r="872" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A872" s="100"/>
+      <c r="A872" s="105"/>
       <c r="B872" s="5" t="s">
         <v>1850</v>
       </c>
@@ -25616,7 +25616,7 @@
       <c r="F872" s="23"/>
     </row>
     <row r="873" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A873" s="100"/>
+      <c r="A873" s="105"/>
       <c r="B873" s="5" t="s">
         <v>1852</v>
       </c>
@@ -25630,7 +25630,7 @@
       <c r="F873" s="23"/>
     </row>
     <row r="874" spans="1:6" ht="27" customHeight="1">
-      <c r="A874" s="100"/>
+      <c r="A874" s="105"/>
       <c r="B874" s="5" t="s">
         <v>1854</v>
       </c>
@@ -25644,7 +25644,7 @@
       <c r="F874" s="23"/>
     </row>
     <row r="875" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A875" s="100"/>
+      <c r="A875" s="105"/>
       <c r="B875" s="5" t="s">
         <v>1856</v>
       </c>
@@ -25658,7 +25658,7 @@
       <c r="F875" s="23"/>
     </row>
     <row r="876" spans="1:6" ht="33" customHeight="1">
-      <c r="A876" s="101" t="s">
+      <c r="A876" s="106" t="s">
         <v>1858</v>
       </c>
       <c r="B876" s="1" t="s">
@@ -25676,7 +25676,7 @@
       <c r="F876" s="23"/>
     </row>
     <row r="877" spans="1:6" ht="70">
-      <c r="A877" s="102"/>
+      <c r="A877" s="107"/>
       <c r="B877" s="5" t="s">
         <v>1862</v>
       </c>
@@ -25692,7 +25692,7 @@
       <c r="F877" s="23"/>
     </row>
     <row r="878" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A878" s="102"/>
+      <c r="A878" s="107"/>
       <c r="B878" s="5" t="s">
         <v>1864</v>
       </c>
@@ -25708,7 +25708,7 @@
       <c r="F878" s="23"/>
     </row>
     <row r="879" spans="1:6" ht="70">
-      <c r="A879" s="102"/>
+      <c r="A879" s="107"/>
       <c r="B879" s="5" t="s">
         <v>1866</v>
       </c>
@@ -25724,7 +25724,7 @@
       <c r="F879" s="23"/>
     </row>
     <row r="880" spans="1:6" ht="70">
-      <c r="A880" s="102"/>
+      <c r="A880" s="107"/>
       <c r="B880" s="5" t="s">
         <v>1868</v>
       </c>
@@ -25740,7 +25740,7 @@
       <c r="F880" s="23"/>
     </row>
     <row r="881" spans="1:6" ht="70">
-      <c r="A881" s="102"/>
+      <c r="A881" s="107"/>
       <c r="B881" s="5" t="s">
         <v>1870</v>
       </c>
@@ -25756,7 +25756,7 @@
       <c r="F881" s="23"/>
     </row>
     <row r="882" spans="1:6" ht="50.25" customHeight="1">
-      <c r="A882" s="102"/>
+      <c r="A882" s="107"/>
       <c r="B882" s="5" t="s">
         <v>1872</v>
       </c>
@@ -25772,7 +25772,7 @@
       <c r="F882" s="23"/>
     </row>
     <row r="883" spans="1:6" ht="70">
-      <c r="A883" s="102"/>
+      <c r="A883" s="107"/>
       <c r="B883" s="5" t="s">
         <v>1874</v>
       </c>
@@ -25788,7 +25788,7 @@
       <c r="F883" s="23"/>
     </row>
     <row r="884" spans="1:6" ht="70">
-      <c r="A884" s="102"/>
+      <c r="A884" s="107"/>
       <c r="B884" s="5" t="s">
         <v>908</v>
       </c>
@@ -25804,7 +25804,7 @@
       <c r="F884" s="23"/>
     </row>
     <row r="885" spans="1:6" ht="28.5">
-      <c r="A885" s="102"/>
+      <c r="A885" s="107"/>
       <c r="B885" s="5" t="s">
         <v>1877</v>
       </c>
@@ -25818,7 +25818,7 @@
       <c r="F885" s="23"/>
     </row>
     <row r="886" spans="1:6" ht="238.5" customHeight="1">
-      <c r="A886" s="102"/>
+      <c r="A886" s="107"/>
       <c r="B886" s="5" t="s">
         <v>1879</v>
       </c>
@@ -25834,7 +25834,7 @@
       <c r="F886" s="23"/>
     </row>
     <row r="887" spans="1:6" ht="70">
-      <c r="A887" s="102"/>
+      <c r="A887" s="107"/>
       <c r="B887" s="5" t="s">
         <v>1881</v>
       </c>
@@ -25850,7 +25850,7 @@
       <c r="F887" s="23"/>
     </row>
     <row r="888" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A888" s="102"/>
+      <c r="A888" s="107"/>
       <c r="B888" s="5" t="s">
         <v>1883</v>
       </c>
@@ -25864,7 +25864,7 @@
       <c r="F888" s="23"/>
     </row>
     <row r="889" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A889" s="102"/>
+      <c r="A889" s="107"/>
       <c r="B889" s="5" t="s">
         <v>1885</v>
       </c>
@@ -25878,7 +25878,7 @@
       <c r="F889" s="23"/>
     </row>
     <row r="890" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A890" s="102"/>
+      <c r="A890" s="107"/>
       <c r="B890" s="5" t="s">
         <v>1887</v>
       </c>
@@ -25892,7 +25892,7 @@
       <c r="F890" s="23"/>
     </row>
     <row r="891" spans="1:6" ht="31">
-      <c r="A891" s="102"/>
+      <c r="A891" s="107"/>
       <c r="B891" s="5" t="s">
         <v>1889</v>
       </c>
@@ -25906,7 +25906,7 @@
       <c r="F891" s="23"/>
     </row>
     <row r="892" spans="1:6" ht="70">
-      <c r="A892" s="102"/>
+      <c r="A892" s="107"/>
       <c r="B892" s="5" t="s">
         <v>1891</v>
       </c>
@@ -25922,7 +25922,7 @@
       <c r="F892" s="23"/>
     </row>
     <row r="893" spans="1:6" ht="31">
-      <c r="A893" s="102"/>
+      <c r="A893" s="107"/>
       <c r="B893" s="5" t="s">
         <v>1893</v>
       </c>
@@ -25936,7 +25936,7 @@
       <c r="F893" s="23"/>
     </row>
     <row r="894" spans="1:6" ht="31">
-      <c r="A894" s="102"/>
+      <c r="A894" s="107"/>
       <c r="B894" s="5" t="s">
         <v>1895</v>
       </c>
@@ -25950,7 +25950,7 @@
       <c r="F894" s="23"/>
     </row>
     <row r="895" spans="1:6" ht="31">
-      <c r="A895" s="102"/>
+      <c r="A895" s="107"/>
       <c r="B895" s="5" t="s">
         <v>1897</v>
       </c>
@@ -25964,7 +25964,7 @@
       <c r="F895" s="23"/>
     </row>
     <row r="896" spans="1:6" ht="190.5" customHeight="1">
-      <c r="A896" s="102"/>
+      <c r="A896" s="107"/>
       <c r="B896" s="5" t="s">
         <v>1899</v>
       </c>
@@ -25980,7 +25980,7 @@
       <c r="F896" s="23"/>
     </row>
     <row r="897" spans="1:6" ht="70">
-      <c r="A897" s="102"/>
+      <c r="A897" s="107"/>
       <c r="B897" s="5" t="s">
         <v>1902</v>
       </c>
@@ -25996,7 +25996,7 @@
       <c r="F897" s="23"/>
     </row>
     <row r="898" spans="1:6" ht="70">
-      <c r="A898" s="102"/>
+      <c r="A898" s="107"/>
       <c r="B898" s="5" t="s">
         <v>1904</v>
       </c>
@@ -26012,7 +26012,7 @@
       <c r="F898" s="23"/>
     </row>
     <row r="899" spans="1:6" ht="70">
-      <c r="A899" s="102"/>
+      <c r="A899" s="107"/>
       <c r="B899" s="5" t="s">
         <v>1906</v>
       </c>
@@ -26028,7 +26028,7 @@
       <c r="F899" s="23"/>
     </row>
     <row r="900" spans="1:6" ht="31">
-      <c r="A900" s="102"/>
+      <c r="A900" s="107"/>
       <c r="B900" s="5" t="s">
         <v>1908</v>
       </c>
@@ -26042,7 +26042,7 @@
       <c r="F900" s="23"/>
     </row>
     <row r="901" spans="1:6" ht="70">
-      <c r="A901" s="102"/>
+      <c r="A901" s="107"/>
       <c r="B901" s="5" t="s">
         <v>1910</v>
       </c>
@@ -26058,7 +26058,7 @@
       <c r="F901" s="23"/>
     </row>
     <row r="902" spans="1:6" ht="28">
-      <c r="A902" s="102"/>
+      <c r="A902" s="107"/>
       <c r="B902" s="5" t="s">
         <v>1912</v>
       </c>
@@ -26072,7 +26072,7 @@
       <c r="F902" s="23"/>
     </row>
     <row r="903" spans="1:6" ht="28">
-      <c r="A903" s="102"/>
+      <c r="A903" s="107"/>
       <c r="B903" s="5" t="s">
         <v>1914</v>
       </c>
@@ -26086,7 +26086,7 @@
       <c r="F903" s="23"/>
     </row>
     <row r="904" spans="1:6" ht="70">
-      <c r="A904" s="102"/>
+      <c r="A904" s="107"/>
       <c r="B904" s="5" t="s">
         <v>1915</v>
       </c>
@@ -26102,7 +26102,7 @@
       <c r="F904" s="23"/>
     </row>
     <row r="905" spans="1:6" ht="70">
-      <c r="A905" s="102"/>
+      <c r="A905" s="107"/>
       <c r="B905" s="5" t="s">
         <v>1917</v>
       </c>
@@ -26118,7 +26118,7 @@
       <c r="F905" s="23"/>
     </row>
     <row r="906" spans="1:6" ht="162.75" customHeight="1">
-      <c r="A906" s="102"/>
+      <c r="A906" s="107"/>
       <c r="B906" s="5" t="s">
         <v>1919</v>
       </c>
@@ -26134,7 +26134,7 @@
       <c r="F906" s="23"/>
     </row>
     <row r="907" spans="1:6" ht="70">
-      <c r="A907" s="102"/>
+      <c r="A907" s="107"/>
       <c r="B907" s="5" t="s">
         <v>1921</v>
       </c>
@@ -26150,7 +26150,7 @@
       <c r="F907" s="23"/>
     </row>
     <row r="908" spans="1:6" ht="58.5" customHeight="1">
-      <c r="A908" s="102"/>
+      <c r="A908" s="107"/>
       <c r="B908" s="5" t="s">
         <v>1923</v>
       </c>
@@ -26164,7 +26164,7 @@
       <c r="F908" s="23"/>
     </row>
     <row r="909" spans="1:6" ht="70">
-      <c r="A909" s="102"/>
+      <c r="A909" s="107"/>
       <c r="B909" s="5" t="s">
         <v>1925</v>
       </c>
@@ -26180,7 +26180,7 @@
       <c r="F909" s="23"/>
     </row>
     <row r="910" spans="1:6" ht="28">
-      <c r="A910" s="102"/>
+      <c r="A910" s="107"/>
       <c r="B910" s="5" t="s">
         <v>1927</v>
       </c>
@@ -26194,7 +26194,7 @@
       <c r="F910" s="23"/>
     </row>
     <row r="911" spans="1:6" ht="31">
-      <c r="A911" s="102"/>
+      <c r="A911" s="107"/>
       <c r="B911" s="5" t="s">
         <v>1929</v>
       </c>
@@ -26208,7 +26208,7 @@
       <c r="F911" s="23"/>
     </row>
     <row r="912" spans="1:6" ht="70">
-      <c r="A912" s="102"/>
+      <c r="A912" s="107"/>
       <c r="B912" s="5" t="s">
         <v>1930</v>
       </c>
@@ -26224,7 +26224,7 @@
       <c r="F912" s="23"/>
     </row>
     <row r="913" spans="1:6" ht="62">
-      <c r="A913" s="102"/>
+      <c r="A913" s="107"/>
       <c r="B913" s="5" t="s">
         <v>1897</v>
       </c>
@@ -26238,7 +26238,7 @@
       <c r="F913" s="23"/>
     </row>
     <row r="914" spans="1:6" ht="77.5">
-      <c r="A914" s="102"/>
+      <c r="A914" s="107"/>
       <c r="B914" s="5" t="s">
         <v>1933</v>
       </c>
@@ -26254,7 +26254,7 @@
       <c r="F914" s="23"/>
     </row>
     <row r="915" spans="1:6" ht="31">
-      <c r="A915" s="102"/>
+      <c r="A915" s="107"/>
       <c r="B915" s="5" t="s">
         <v>1935</v>
       </c>
@@ -26268,7 +26268,7 @@
       <c r="F915" s="23"/>
     </row>
     <row r="916" spans="1:6" ht="70">
-      <c r="A916" s="102"/>
+      <c r="A916" s="107"/>
       <c r="B916" s="5" t="s">
         <v>1937</v>
       </c>
@@ -26284,7 +26284,7 @@
       <c r="F916" s="23"/>
     </row>
     <row r="917" spans="1:6" ht="70">
-      <c r="A917" s="102"/>
+      <c r="A917" s="107"/>
       <c r="B917" s="5" t="s">
         <v>1939</v>
       </c>
@@ -26300,7 +26300,7 @@
       <c r="F917" s="23"/>
     </row>
     <row r="918" spans="1:6" ht="70">
-      <c r="A918" s="102"/>
+      <c r="A918" s="107"/>
       <c r="B918" s="5" t="s">
         <v>1941</v>
       </c>
@@ -26316,7 +26316,7 @@
       <c r="F918" s="23"/>
     </row>
     <row r="919" spans="1:6" ht="31">
-      <c r="A919" s="102"/>
+      <c r="A919" s="107"/>
       <c r="B919" s="5" t="s">
         <v>1943</v>
       </c>
@@ -26330,7 +26330,7 @@
       <c r="F919" s="23"/>
     </row>
     <row r="920" spans="1:6" ht="95.25" customHeight="1">
-      <c r="A920" s="102"/>
+      <c r="A920" s="107"/>
       <c r="B920" s="5" t="s">
         <v>1945</v>
       </c>
@@ -26346,7 +26346,7 @@
       <c r="F920" s="23"/>
     </row>
     <row r="921" spans="1:6" ht="31">
-      <c r="A921" s="102"/>
+      <c r="A921" s="107"/>
       <c r="B921" s="5" t="s">
         <v>1947</v>
       </c>
@@ -26360,7 +26360,7 @@
       <c r="F921" s="23"/>
     </row>
     <row r="922" spans="1:6" ht="31">
-      <c r="A922" s="102"/>
+      <c r="A922" s="107"/>
       <c r="B922" s="5" t="s">
         <v>1949</v>
       </c>
@@ -26374,7 +26374,7 @@
       <c r="F922" s="23"/>
     </row>
     <row r="923" spans="1:6" ht="31">
-      <c r="A923" s="102"/>
+      <c r="A923" s="107"/>
       <c r="B923" s="5" t="s">
         <v>1951</v>
       </c>
@@ -26388,7 +26388,7 @@
       <c r="F923" s="23"/>
     </row>
     <row r="924" spans="1:6" ht="31">
-      <c r="A924" s="102"/>
+      <c r="A924" s="107"/>
       <c r="B924" s="5" t="s">
         <v>1953</v>
       </c>
@@ -26402,7 +26402,7 @@
       <c r="F924" s="23"/>
     </row>
     <row r="925" spans="1:6" ht="31">
-      <c r="A925" s="102"/>
+      <c r="A925" s="107"/>
       <c r="B925" s="5" t="s">
         <v>1955</v>
       </c>
@@ -26416,7 +26416,7 @@
       <c r="F925" s="23"/>
     </row>
     <row r="926" spans="1:6" ht="70">
-      <c r="A926" s="102"/>
+      <c r="A926" s="107"/>
       <c r="B926" s="5" t="s">
         <v>1957</v>
       </c>
@@ -26432,7 +26432,7 @@
       <c r="F926" s="23"/>
     </row>
     <row r="927" spans="1:6" ht="31">
-      <c r="A927" s="102"/>
+      <c r="A927" s="107"/>
       <c r="B927" s="5" t="s">
         <v>1885</v>
       </c>
@@ -26446,7 +26446,7 @@
       <c r="F927" s="23"/>
     </row>
     <row r="928" spans="1:6" ht="62">
-      <c r="A928" s="102"/>
+      <c r="A928" s="107"/>
       <c r="B928" s="5" t="s">
         <v>1960</v>
       </c>
@@ -26460,7 +26460,7 @@
       <c r="F928" s="23"/>
     </row>
     <row r="929" spans="1:6" ht="62">
-      <c r="A929" s="102"/>
+      <c r="A929" s="107"/>
       <c r="B929" s="5" t="s">
         <v>1962</v>
       </c>
@@ -26474,7 +26474,7 @@
       <c r="F929" s="23"/>
     </row>
     <row r="930" spans="1:6" ht="93">
-      <c r="A930" s="102"/>
+      <c r="A930" s="107"/>
       <c r="B930" s="5" t="s">
         <v>1964</v>
       </c>
@@ -26490,7 +26490,7 @@
       <c r="F930" s="23"/>
     </row>
     <row r="931" spans="1:6" ht="70">
-      <c r="A931" s="102"/>
+      <c r="A931" s="107"/>
       <c r="B931" s="5" t="s">
         <v>1966</v>
       </c>
@@ -26506,7 +26506,7 @@
       <c r="F931" s="23"/>
     </row>
     <row r="932" spans="1:6" ht="31">
-      <c r="A932" s="102"/>
+      <c r="A932" s="107"/>
       <c r="B932" s="5" t="s">
         <v>1968</v>
       </c>
@@ -26520,7 +26520,7 @@
       <c r="F932" s="23"/>
     </row>
     <row r="933" spans="1:6" ht="70">
-      <c r="A933" s="102"/>
+      <c r="A933" s="107"/>
       <c r="B933" s="5" t="s">
         <v>1970</v>
       </c>
@@ -26536,7 +26536,7 @@
       <c r="F933" s="23"/>
     </row>
     <row r="934" spans="1:6" ht="28">
-      <c r="A934" s="102"/>
+      <c r="A934" s="107"/>
       <c r="B934" s="5" t="s">
         <v>1972</v>
       </c>
@@ -26550,7 +26550,7 @@
       <c r="F934" s="23"/>
     </row>
     <row r="935" spans="1:6" ht="70">
-      <c r="A935" s="102"/>
+      <c r="A935" s="107"/>
       <c r="B935" s="5" t="s">
         <v>1974</v>
       </c>
@@ -26566,7 +26566,7 @@
       <c r="F935" s="23"/>
     </row>
     <row r="936" spans="1:6" ht="70">
-      <c r="A936" s="102"/>
+      <c r="A936" s="107"/>
       <c r="B936" s="5" t="s">
         <v>1976</v>
       </c>
@@ -26582,7 +26582,7 @@
       <c r="F936" s="23"/>
     </row>
     <row r="937" spans="1:6" ht="28">
-      <c r="A937" s="102"/>
+      <c r="A937" s="107"/>
       <c r="B937" s="5" t="s">
         <v>1978</v>
       </c>
@@ -26596,7 +26596,7 @@
       <c r="F937" s="23"/>
     </row>
     <row r="938" spans="1:6" ht="28">
-      <c r="A938" s="102"/>
+      <c r="A938" s="107"/>
       <c r="B938" s="5" t="s">
         <v>1980</v>
       </c>
@@ -26610,7 +26610,7 @@
       <c r="F938" s="23"/>
     </row>
     <row r="939" spans="1:6" ht="31">
-      <c r="A939" s="102"/>
+      <c r="A939" s="107"/>
       <c r="B939" s="5" t="s">
         <v>1895</v>
       </c>
@@ -26624,7 +26624,7 @@
       <c r="F939" s="23"/>
     </row>
     <row r="940" spans="1:6" ht="28">
-      <c r="A940" s="102"/>
+      <c r="A940" s="107"/>
       <c r="B940" s="5" t="s">
         <v>1983</v>
       </c>
@@ -26638,7 +26638,7 @@
       <c r="F940" s="23"/>
     </row>
     <row r="941" spans="1:6" ht="31">
-      <c r="A941" s="102"/>
+      <c r="A941" s="107"/>
       <c r="B941" s="5" t="s">
         <v>1985</v>
       </c>
@@ -26652,7 +26652,7 @@
       <c r="F941" s="23"/>
     </row>
     <row r="942" spans="1:6" ht="31">
-      <c r="A942" s="102"/>
+      <c r="A942" s="107"/>
       <c r="B942" s="5" t="s">
         <v>1987</v>
       </c>
@@ -26666,7 +26666,7 @@
       <c r="F942" s="23"/>
     </row>
     <row r="943" spans="1:6" ht="31">
-      <c r="A943" s="102"/>
+      <c r="A943" s="107"/>
       <c r="B943" s="5" t="s">
         <v>1989</v>
       </c>
@@ -26680,7 +26680,7 @@
       <c r="F943" s="23"/>
     </row>
     <row r="944" spans="1:6" ht="31">
-      <c r="A944" s="102"/>
+      <c r="A944" s="107"/>
       <c r="B944" s="5" t="s">
         <v>1991</v>
       </c>
@@ -26694,7 +26694,7 @@
       <c r="F944" s="23"/>
     </row>
     <row r="945" spans="1:6" ht="28">
-      <c r="A945" s="102"/>
+      <c r="A945" s="107"/>
       <c r="B945" s="5" t="s">
         <v>1993</v>
       </c>
@@ -26708,7 +26708,7 @@
       <c r="F945" s="23"/>
     </row>
     <row r="946" spans="1:6" ht="31">
-      <c r="A946" s="102"/>
+      <c r="A946" s="107"/>
       <c r="B946" s="5" t="s">
         <v>1889</v>
       </c>
@@ -26722,7 +26722,7 @@
       <c r="F946" s="23"/>
     </row>
     <row r="947" spans="1:6" ht="31">
-      <c r="A947" s="102"/>
+      <c r="A947" s="107"/>
       <c r="B947" s="5" t="s">
         <v>1996</v>
       </c>
@@ -26736,7 +26736,7 @@
       <c r="F947" s="23"/>
     </row>
     <row r="948" spans="1:6" ht="28">
-      <c r="A948" s="102"/>
+      <c r="A948" s="107"/>
       <c r="B948" s="5" t="s">
         <v>1998</v>
       </c>
@@ -26750,7 +26750,7 @@
       <c r="F948" s="23"/>
     </row>
     <row r="949" spans="1:6" ht="31">
-      <c r="A949" s="102"/>
+      <c r="A949" s="107"/>
       <c r="B949" s="5" t="s">
         <v>2000</v>
       </c>
@@ -26764,7 +26764,7 @@
       <c r="F949" s="23"/>
     </row>
     <row r="950" spans="1:6" ht="31">
-      <c r="A950" s="102"/>
+      <c r="A950" s="107"/>
       <c r="B950" s="5" t="s">
         <v>2002</v>
       </c>
@@ -26778,7 +26778,7 @@
       <c r="F950" s="23"/>
     </row>
     <row r="951" spans="1:6" ht="31">
-      <c r="A951" s="102"/>
+      <c r="A951" s="107"/>
       <c r="B951" s="5" t="s">
         <v>2004</v>
       </c>
@@ -26792,7 +26792,7 @@
       <c r="F951" s="23"/>
     </row>
     <row r="952" spans="1:6" ht="31">
-      <c r="A952" s="102"/>
+      <c r="A952" s="107"/>
       <c r="B952" s="5" t="s">
         <v>2006</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="F952" s="23"/>
     </row>
     <row r="953" spans="1:6" ht="31">
-      <c r="A953" s="102"/>
+      <c r="A953" s="107"/>
       <c r="B953" s="5" t="s">
         <v>2008</v>
       </c>
@@ -26820,7 +26820,7 @@
       <c r="F953" s="23"/>
     </row>
     <row r="954" spans="1:6" ht="31">
-      <c r="A954" s="102"/>
+      <c r="A954" s="107"/>
       <c r="B954" s="5" t="s">
         <v>2010</v>
       </c>
@@ -26834,7 +26834,7 @@
       <c r="F954" s="23"/>
     </row>
     <row r="955" spans="1:6" ht="31">
-      <c r="A955" s="102"/>
+      <c r="A955" s="107"/>
       <c r="B955" s="5" t="s">
         <v>2012</v>
       </c>
@@ -26848,7 +26848,7 @@
       <c r="F955" s="23"/>
     </row>
     <row r="956" spans="1:6" ht="31">
-      <c r="A956" s="102"/>
+      <c r="A956" s="107"/>
       <c r="B956" s="5" t="s">
         <v>2014</v>
       </c>
@@ -26862,7 +26862,7 @@
       <c r="F956" s="23"/>
     </row>
     <row r="957" spans="1:6" ht="31">
-      <c r="A957" s="102"/>
+      <c r="A957" s="107"/>
       <c r="B957" s="5" t="s">
         <v>2016</v>
       </c>
@@ -26876,7 +26876,7 @@
       <c r="F957" s="23"/>
     </row>
     <row r="958" spans="1:6" ht="28">
-      <c r="A958" s="102"/>
+      <c r="A958" s="107"/>
       <c r="B958" s="5" t="s">
         <v>2018</v>
       </c>
@@ -26890,7 +26890,7 @@
       <c r="F958" s="23"/>
     </row>
     <row r="959" spans="1:6" ht="31">
-      <c r="A959" s="102"/>
+      <c r="A959" s="107"/>
       <c r="B959" s="5" t="s">
         <v>2020</v>
       </c>
@@ -26904,7 +26904,7 @@
       <c r="F959" s="23"/>
     </row>
     <row r="960" spans="1:6" ht="31">
-      <c r="A960" s="102"/>
+      <c r="A960" s="107"/>
       <c r="B960" s="5" t="s">
         <v>2022</v>
       </c>
@@ -26918,7 +26918,7 @@
       <c r="F960" s="23"/>
     </row>
     <row r="961" spans="1:6" ht="28">
-      <c r="A961" s="102"/>
+      <c r="A961" s="107"/>
       <c r="B961" s="5" t="s">
         <v>2024</v>
       </c>
@@ -26932,7 +26932,7 @@
       <c r="F961" s="23"/>
     </row>
     <row r="962" spans="1:6" ht="28">
-      <c r="A962" s="102"/>
+      <c r="A962" s="107"/>
       <c r="B962" s="5" t="s">
         <v>2026</v>
       </c>
@@ -26946,7 +26946,7 @@
       <c r="F962" s="23"/>
     </row>
     <row r="963" spans="1:6" ht="31">
-      <c r="A963" s="102"/>
+      <c r="A963" s="107"/>
       <c r="B963" s="5" t="s">
         <v>2028</v>
       </c>
@@ -26960,7 +26960,7 @@
       <c r="F963" s="23"/>
     </row>
     <row r="964" spans="1:6" ht="28">
-      <c r="A964" s="102"/>
+      <c r="A964" s="107"/>
       <c r="B964" s="5" t="s">
         <v>2030</v>
       </c>
@@ -26974,7 +26974,7 @@
       <c r="F964" s="23"/>
     </row>
     <row r="965" spans="1:6" ht="70">
-      <c r="A965" s="102"/>
+      <c r="A965" s="107"/>
       <c r="B965" s="5" t="s">
         <v>1904</v>
       </c>
@@ -26990,7 +26990,7 @@
       <c r="F965" s="23"/>
     </row>
     <row r="966" spans="1:6" ht="70">
-      <c r="A966" s="102"/>
+      <c r="A966" s="107"/>
       <c r="B966" s="5" t="s">
         <v>2033</v>
       </c>
@@ -27006,7 +27006,7 @@
       <c r="F966" s="23"/>
     </row>
     <row r="967" spans="1:6" ht="70">
-      <c r="A967" s="102"/>
+      <c r="A967" s="107"/>
       <c r="B967" s="5" t="s">
         <v>2035</v>
       </c>
@@ -27022,7 +27022,7 @@
       <c r="F967" s="23"/>
     </row>
     <row r="968" spans="1:6" ht="70">
-      <c r="A968" s="102"/>
+      <c r="A968" s="107"/>
       <c r="B968" s="5" t="s">
         <v>2037</v>
       </c>
@@ -27038,7 +27038,7 @@
       <c r="F968" s="23"/>
     </row>
     <row r="969" spans="1:6" ht="124">
-      <c r="A969" s="102"/>
+      <c r="A969" s="107"/>
       <c r="B969" s="5" t="s">
         <v>2039</v>
       </c>
@@ -27054,7 +27054,7 @@
       <c r="F969" s="23"/>
     </row>
     <row r="970" spans="1:6" ht="31">
-      <c r="A970" s="102"/>
+      <c r="A970" s="107"/>
       <c r="B970" s="5" t="s">
         <v>2041</v>
       </c>
@@ -27068,7 +27068,7 @@
       <c r="F970" s="23"/>
     </row>
     <row r="971" spans="1:6" ht="62">
-      <c r="A971" s="102"/>
+      <c r="A971" s="107"/>
       <c r="B971" s="5" t="s">
         <v>2043</v>
       </c>
@@ -27082,7 +27082,7 @@
       <c r="F971" s="23"/>
     </row>
     <row r="972" spans="1:6" ht="31">
-      <c r="A972" s="102"/>
+      <c r="A972" s="107"/>
       <c r="B972" s="5" t="s">
         <v>2045</v>
       </c>
@@ -27096,7 +27096,7 @@
       <c r="F972" s="23"/>
     </row>
     <row r="973" spans="1:6" ht="31">
-      <c r="A973" s="102"/>
+      <c r="A973" s="107"/>
       <c r="B973" s="5" t="s">
         <v>2047</v>
       </c>
@@ -27110,7 +27110,7 @@
       <c r="F973" s="23"/>
     </row>
     <row r="974" spans="1:6" ht="70">
-      <c r="A974" s="98"/>
+      <c r="A974" s="103"/>
       <c r="B974" s="5" t="s">
         <v>2049</v>
       </c>
@@ -28486,7 +28486,7 @@
       <c r="F1071" s="23"/>
     </row>
     <row r="1072" spans="1:6" ht="128.25" customHeight="1">
-      <c r="A1072" s="101" t="s">
+      <c r="A1072" s="106" t="s">
         <v>2219</v>
       </c>
       <c r="B1072" s="11" t="s">
@@ -28502,7 +28502,7 @@
       <c r="F1072" s="23"/>
     </row>
     <row r="1073" spans="1:6" ht="121.5" customHeight="1">
-      <c r="A1073" s="102"/>
+      <c r="A1073" s="107"/>
       <c r="B1073" s="5" t="s">
         <v>2222</v>
       </c>
@@ -28518,7 +28518,7 @@
       <c r="F1073" s="23"/>
     </row>
     <row r="1074" spans="1:6" ht="117" customHeight="1">
-      <c r="A1074" s="102"/>
+      <c r="A1074" s="107"/>
       <c r="B1074" s="5" t="s">
         <v>2225</v>
       </c>
@@ -28532,7 +28532,7 @@
       <c r="F1074" s="23"/>
     </row>
     <row r="1075" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A1075" s="102"/>
+      <c r="A1075" s="107"/>
       <c r="B1075" s="5" t="s">
         <v>2228</v>
       </c>
@@ -28546,7 +28546,7 @@
       <c r="F1075" s="23"/>
     </row>
     <row r="1076" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1076" s="102"/>
+      <c r="A1076" s="107"/>
       <c r="B1076" s="5" t="s">
         <v>2231</v>
       </c>
@@ -28560,7 +28560,7 @@
       <c r="F1076" s="23"/>
     </row>
     <row r="1077" spans="1:6" ht="129" customHeight="1">
-      <c r="A1077" s="102"/>
+      <c r="A1077" s="107"/>
       <c r="B1077" s="5" t="s">
         <v>2233</v>
       </c>
@@ -28574,7 +28574,7 @@
       <c r="F1077" s="23"/>
     </row>
     <row r="1078" spans="1:6" ht="73.5" customHeight="1">
-      <c r="A1078" s="102"/>
+      <c r="A1078" s="107"/>
       <c r="B1078" s="5" t="s">
         <v>2235</v>
       </c>
@@ -28588,7 +28588,7 @@
       <c r="F1078" s="23"/>
     </row>
     <row r="1079" spans="1:6" ht="77.25" customHeight="1">
-      <c r="A1079" s="102"/>
+      <c r="A1079" s="107"/>
       <c r="B1079" s="1" t="s">
         <v>2237</v>
       </c>
@@ -28604,7 +28604,7 @@
       <c r="F1079" s="23"/>
     </row>
     <row r="1080" spans="1:6" ht="129" customHeight="1">
-      <c r="A1080" s="102"/>
+      <c r="A1080" s="107"/>
       <c r="B1080" s="5" t="s">
         <v>2239</v>
       </c>
@@ -28618,7 +28618,7 @@
       <c r="F1080" s="23"/>
     </row>
     <row r="1081" spans="1:6" ht="92.25" customHeight="1">
-      <c r="A1081" s="102"/>
+      <c r="A1081" s="107"/>
       <c r="B1081" s="5" t="s">
         <v>2241</v>
       </c>
@@ -28632,7 +28632,7 @@
       <c r="F1081" s="23"/>
     </row>
     <row r="1082" spans="1:6" ht="72.75" customHeight="1">
-      <c r="A1082" s="102"/>
+      <c r="A1082" s="107"/>
       <c r="B1082" s="5" t="s">
         <v>2244</v>
       </c>
@@ -28646,7 +28646,7 @@
       <c r="F1082" s="23"/>
     </row>
     <row r="1083" spans="1:6" ht="87.75" customHeight="1">
-      <c r="A1083" s="102"/>
+      <c r="A1083" s="107"/>
       <c r="B1083" s="5" t="s">
         <v>2246</v>
       </c>
@@ -28660,7 +28660,7 @@
       <c r="F1083" s="23"/>
     </row>
     <row r="1084" spans="1:6" ht="39" customHeight="1">
-      <c r="A1084" s="102"/>
+      <c r="A1084" s="107"/>
       <c r="B1084" s="5" t="s">
         <v>2248</v>
       </c>
@@ -28674,7 +28674,7 @@
       <c r="F1084" s="23"/>
     </row>
     <row r="1085" spans="1:6" ht="94.5" customHeight="1">
-      <c r="A1085" s="102"/>
+      <c r="A1085" s="107"/>
       <c r="B1085" s="5" t="s">
         <v>2250</v>
       </c>
@@ -28688,7 +28688,7 @@
       <c r="F1085" s="23"/>
     </row>
     <row r="1086" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A1086" s="102"/>
+      <c r="A1086" s="107"/>
       <c r="B1086" s="5" t="s">
         <v>2252</v>
       </c>
@@ -28702,7 +28702,7 @@
       <c r="F1086" s="23"/>
     </row>
     <row r="1087" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A1087" s="102"/>
+      <c r="A1087" s="107"/>
       <c r="B1087" s="1" t="s">
         <v>2254</v>
       </c>
@@ -28714,7 +28714,7 @@
       <c r="F1087" s="23"/>
     </row>
     <row r="1088" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1088" s="102"/>
+      <c r="A1088" s="107"/>
       <c r="B1088" s="5" t="s">
         <v>2256</v>
       </c>
@@ -28728,7 +28728,7 @@
       <c r="F1088" s="23"/>
     </row>
     <row r="1089" spans="1:6" ht="85.5" customHeight="1">
-      <c r="A1089" s="102"/>
+      <c r="A1089" s="107"/>
       <c r="B1089" s="5" t="s">
         <v>2258</v>
       </c>
@@ -28742,7 +28742,7 @@
       <c r="F1089" s="23"/>
     </row>
     <row r="1090" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A1090" s="102"/>
+      <c r="A1090" s="107"/>
       <c r="B1090" s="5" t="s">
         <v>2260</v>
       </c>
@@ -28756,7 +28756,7 @@
       <c r="F1090" s="23"/>
     </row>
     <row r="1091" spans="1:6" ht="48" customHeight="1">
-      <c r="A1091" s="102"/>
+      <c r="A1091" s="107"/>
       <c r="B1091" s="1" t="s">
         <v>2262</v>
       </c>
@@ -28770,7 +28770,7 @@
       <c r="F1091" s="23"/>
     </row>
     <row r="1092" spans="1:6" ht="84.75" customHeight="1">
-      <c r="A1092" s="102"/>
+      <c r="A1092" s="107"/>
       <c r="B1092" s="5" t="s">
         <v>2264</v>
       </c>
@@ -28786,7 +28786,7 @@
       <c r="F1092" s="23"/>
     </row>
     <row r="1093" spans="1:6" ht="65.25" customHeight="1">
-      <c r="A1093" s="102"/>
+      <c r="A1093" s="107"/>
       <c r="B1093" s="5" t="s">
         <v>2265</v>
       </c>
@@ -28800,7 +28800,7 @@
       <c r="F1093" s="23"/>
     </row>
     <row r="1094" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1094" s="102"/>
+      <c r="A1094" s="107"/>
       <c r="B1094" s="5" t="s">
         <v>2267</v>
       </c>
@@ -28814,7 +28814,7 @@
       <c r="F1094" s="23"/>
     </row>
     <row r="1095" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1095" s="102"/>
+      <c r="A1095" s="107"/>
       <c r="B1095" s="5" t="s">
         <v>2269</v>
       </c>
@@ -28828,7 +28828,7 @@
       <c r="F1095" s="23"/>
     </row>
     <row r="1096" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A1096" s="102"/>
+      <c r="A1096" s="107"/>
       <c r="B1096" s="6" t="s">
         <v>2271</v>
       </c>
@@ -28838,7 +28838,7 @@
       <c r="F1096" s="23"/>
     </row>
     <row r="1097" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A1097" s="102"/>
+      <c r="A1097" s="107"/>
       <c r="B1097" s="1" t="s">
         <v>2272</v>
       </c>
@@ -28852,7 +28852,7 @@
       <c r="F1097" s="23"/>
     </row>
     <row r="1098" spans="1:6" ht="88.5" customHeight="1">
-      <c r="A1098" s="102"/>
+      <c r="A1098" s="107"/>
       <c r="B1098" s="5" t="s">
         <v>2274</v>
       </c>
@@ -28866,7 +28866,7 @@
       <c r="F1098" s="23"/>
     </row>
     <row r="1099" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1099" s="102"/>
+      <c r="A1099" s="107"/>
       <c r="B1099" s="5" t="s">
         <v>2276</v>
       </c>
@@ -28880,7 +28880,7 @@
       <c r="F1099" s="23"/>
     </row>
     <row r="1100" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1100" s="102"/>
+      <c r="A1100" s="107"/>
       <c r="B1100" s="5" t="s">
         <v>2278</v>
       </c>
@@ -28894,7 +28894,7 @@
       <c r="F1100" s="23"/>
     </row>
     <row r="1101" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1101" s="102"/>
+      <c r="A1101" s="107"/>
       <c r="B1101" s="5" t="s">
         <v>2280</v>
       </c>
@@ -28908,7 +28908,7 @@
       <c r="F1101" s="23"/>
     </row>
     <row r="1102" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1102" s="102"/>
+      <c r="A1102" s="107"/>
       <c r="B1102" s="5" t="s">
         <v>2283</v>
       </c>
@@ -28922,7 +28922,7 @@
       <c r="F1102" s="23"/>
     </row>
     <row r="1103" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1103" s="102"/>
+      <c r="A1103" s="107"/>
       <c r="B1103" s="5" t="s">
         <v>2285</v>
       </c>
@@ -28936,7 +28936,7 @@
       <c r="F1103" s="23"/>
     </row>
     <row r="1104" spans="1:6" ht="39" customHeight="1">
-      <c r="A1104" s="102"/>
+      <c r="A1104" s="107"/>
       <c r="B1104" s="5" t="s">
         <v>2287</v>
       </c>
@@ -28950,7 +28950,7 @@
       <c r="F1104" s="23"/>
     </row>
     <row r="1105" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1105" s="102"/>
+      <c r="A1105" s="107"/>
       <c r="B1105" s="5" t="s">
         <v>2289</v>
       </c>
@@ -28964,7 +28964,7 @@
       <c r="F1105" s="23"/>
     </row>
     <row r="1106" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A1106" s="102"/>
+      <c r="A1106" s="107"/>
       <c r="B1106" s="5" t="s">
         <v>2291</v>
       </c>
@@ -28978,7 +28978,7 @@
       <c r="F1106" s="23"/>
     </row>
     <row r="1107" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A1107" s="102"/>
+      <c r="A1107" s="107"/>
       <c r="B1107" s="5" t="s">
         <v>2292</v>
       </c>
@@ -28992,7 +28992,7 @@
       <c r="F1107" s="23"/>
     </row>
     <row r="1108" spans="1:6" ht="27" customHeight="1">
-      <c r="A1108" s="102"/>
+      <c r="A1108" s="107"/>
       <c r="B1108" s="5" t="s">
         <v>2294</v>
       </c>
@@ -29006,7 +29006,7 @@
       <c r="F1108" s="23"/>
     </row>
     <row r="1109" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1109" s="102"/>
+      <c r="A1109" s="107"/>
       <c r="B1109" s="5" t="s">
         <v>2296</v>
       </c>
@@ -29020,7 +29020,7 @@
       <c r="F1109" s="23"/>
     </row>
     <row r="1110" spans="1:6" ht="81.75" customHeight="1">
-      <c r="A1110" s="102"/>
+      <c r="A1110" s="107"/>
       <c r="B1110" s="5" t="s">
         <v>2298</v>
       </c>
@@ -29036,7 +29036,7 @@
       <c r="F1110" s="23"/>
     </row>
     <row r="1111" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A1111" s="102"/>
+      <c r="A1111" s="107"/>
       <c r="B1111" s="5" t="s">
         <v>2300</v>
       </c>
@@ -29052,7 +29052,7 @@
       <c r="F1111" s="23"/>
     </row>
     <row r="1112" spans="1:6" ht="87.75" customHeight="1">
-      <c r="A1112" s="102"/>
+      <c r="A1112" s="107"/>
       <c r="B1112" s="5" t="s">
         <v>2303</v>
       </c>
@@ -29066,7 +29066,7 @@
       <c r="F1112" s="23"/>
     </row>
     <row r="1113" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1113" s="102"/>
+      <c r="A1113" s="107"/>
       <c r="B1113" s="5" t="s">
         <v>2305</v>
       </c>
@@ -29080,7 +29080,7 @@
       <c r="F1113" s="23"/>
     </row>
     <row r="1114" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A1114" s="102"/>
+      <c r="A1114" s="107"/>
       <c r="B1114" s="5" t="s">
         <v>2307</v>
       </c>
@@ -29094,7 +29094,7 @@
       <c r="F1114" s="23"/>
     </row>
     <row r="1115" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1115" s="102"/>
+      <c r="A1115" s="107"/>
       <c r="B1115" s="5" t="s">
         <v>2309</v>
       </c>
@@ -29108,7 +29108,7 @@
       <c r="F1115" s="23"/>
     </row>
     <row r="1116" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A1116" s="102"/>
+      <c r="A1116" s="107"/>
       <c r="B1116" s="5" t="s">
         <v>2311</v>
       </c>
@@ -29122,7 +29122,7 @@
       <c r="F1116" s="23"/>
     </row>
     <row r="1117" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A1117" s="102"/>
+      <c r="A1117" s="107"/>
       <c r="B1117" s="5" t="s">
         <v>2313</v>
       </c>
@@ -29136,7 +29136,7 @@
       <c r="F1117" s="23"/>
     </row>
     <row r="1118" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1118" s="102"/>
+      <c r="A1118" s="107"/>
       <c r="B1118" s="5" t="s">
         <v>2315</v>
       </c>
@@ -29150,7 +29150,7 @@
       <c r="F1118" s="23"/>
     </row>
     <row r="1119" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1119" s="102"/>
+      <c r="A1119" s="107"/>
       <c r="B1119" s="5" t="s">
         <v>2317</v>
       </c>
@@ -29164,7 +29164,7 @@
       <c r="F1119" s="23"/>
     </row>
     <row r="1120" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A1120" s="102"/>
+      <c r="A1120" s="107"/>
       <c r="B1120" s="5" t="s">
         <v>2319</v>
       </c>
@@ -29178,7 +29178,7 @@
       <c r="F1120" s="23"/>
     </row>
     <row r="1121" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A1121" s="102"/>
+      <c r="A1121" s="107"/>
       <c r="B1121" s="5" t="s">
         <v>2321</v>
       </c>
@@ -29192,7 +29192,7 @@
       <c r="F1121" s="23"/>
     </row>
     <row r="1122" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A1122" s="102"/>
+      <c r="A1122" s="107"/>
       <c r="B1122" s="5" t="s">
         <v>2323</v>
       </c>
@@ -29206,7 +29206,7 @@
       <c r="F1122" s="23"/>
     </row>
     <row r="1123" spans="1:6" ht="36" customHeight="1">
-      <c r="A1123" s="102"/>
+      <c r="A1123" s="107"/>
       <c r="B1123" s="6" t="s">
         <v>2325</v>
       </c>
@@ -29216,7 +29216,7 @@
       <c r="F1123" s="23"/>
     </row>
     <row r="1124" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A1124" s="102"/>
+      <c r="A1124" s="107"/>
       <c r="B1124" s="5" t="s">
         <v>2326</v>
       </c>
@@ -29230,7 +29230,7 @@
       <c r="F1124" s="23"/>
     </row>
     <row r="1125" spans="1:6" ht="45" customHeight="1">
-      <c r="A1125" s="102"/>
+      <c r="A1125" s="107"/>
       <c r="B1125" s="5" t="s">
         <v>2328</v>
       </c>
@@ -29246,7 +29246,7 @@
       <c r="F1125" s="23"/>
     </row>
     <row r="1126" spans="1:6" ht="50.25" customHeight="1">
-      <c r="A1126" s="102"/>
+      <c r="A1126" s="107"/>
       <c r="B1126" s="5" t="s">
         <v>2331</v>
       </c>
@@ -29260,7 +29260,7 @@
       <c r="F1126" s="23"/>
     </row>
     <row r="1127" spans="1:6" ht="82.5" customHeight="1">
-      <c r="A1127" s="102"/>
+      <c r="A1127" s="107"/>
       <c r="B1127" s="5" t="s">
         <v>2333</v>
       </c>
@@ -29276,7 +29276,7 @@
       <c r="F1127" s="23"/>
     </row>
     <row r="1128" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1128" s="102"/>
+      <c r="A1128" s="107"/>
       <c r="B1128" s="5" t="s">
         <v>2335</v>
       </c>
@@ -29290,7 +29290,7 @@
       <c r="F1128" s="23"/>
     </row>
     <row r="1129" spans="1:6" ht="63.75" customHeight="1">
-      <c r="A1129" s="102"/>
+      <c r="A1129" s="107"/>
       <c r="B1129" s="5" t="s">
         <v>2338</v>
       </c>
@@ -29306,7 +29306,7 @@
       <c r="F1129" s="23"/>
     </row>
     <row r="1130" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1130" s="102"/>
+      <c r="A1130" s="107"/>
       <c r="B1130" s="5" t="s">
         <v>2340</v>
       </c>
@@ -29320,7 +29320,7 @@
       <c r="F1130" s="23"/>
     </row>
     <row r="1131" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A1131" s="102"/>
+      <c r="A1131" s="107"/>
       <c r="B1131" s="5" t="s">
         <v>2343</v>
       </c>
@@ -29334,7 +29334,7 @@
       <c r="F1131" s="23"/>
     </row>
     <row r="1132" spans="1:6" ht="135" customHeight="1">
-      <c r="A1132" s="102"/>
+      <c r="A1132" s="107"/>
       <c r="B1132" s="5" t="s">
         <v>2345</v>
       </c>
@@ -29348,7 +29348,7 @@
       <c r="F1132" s="23"/>
     </row>
     <row r="1133" spans="1:6" ht="172.5" customHeight="1">
-      <c r="A1133" s="102"/>
+      <c r="A1133" s="107"/>
       <c r="B1133" s="5" t="s">
         <v>2347</v>
       </c>
@@ -29362,7 +29362,7 @@
       <c r="F1133" s="23"/>
     </row>
     <row r="1134" spans="1:6" ht="105.75" customHeight="1">
-      <c r="A1134" s="102"/>
+      <c r="A1134" s="107"/>
       <c r="B1134" s="5" t="s">
         <v>2349</v>
       </c>
@@ -29376,7 +29376,7 @@
       <c r="F1134" s="23"/>
     </row>
     <row r="1135" spans="1:6" ht="85.5" customHeight="1">
-      <c r="A1135" s="102"/>
+      <c r="A1135" s="107"/>
       <c r="B1135" s="5" t="s">
         <v>2351</v>
       </c>
@@ -29390,7 +29390,7 @@
       <c r="F1135" s="23"/>
     </row>
     <row r="1136" spans="1:6" ht="99" customHeight="1">
-      <c r="A1136" s="102"/>
+      <c r="A1136" s="107"/>
       <c r="B1136" s="1" t="s">
         <v>2354</v>
       </c>
@@ -29404,7 +29404,7 @@
       <c r="F1136" s="23"/>
     </row>
     <row r="1137" spans="1:6" ht="129.75" customHeight="1">
-      <c r="A1137" s="102"/>
+      <c r="A1137" s="107"/>
       <c r="B1137" s="83" t="s">
         <v>2356</v>
       </c>
@@ -29418,7 +29418,7 @@
       <c r="F1137" s="23"/>
     </row>
     <row r="1138" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1138" s="102"/>
+      <c r="A1138" s="107"/>
       <c r="B1138" s="5" t="s">
         <v>2358</v>
       </c>
@@ -29432,7 +29432,7 @@
       <c r="F1138" s="23"/>
     </row>
     <row r="1139" spans="1:6" ht="92.25" customHeight="1">
-      <c r="A1139" s="102"/>
+      <c r="A1139" s="107"/>
       <c r="B1139" s="5" t="s">
         <v>2360</v>
       </c>
@@ -29446,7 +29446,7 @@
       <c r="F1139" s="23"/>
     </row>
     <row r="1140" spans="1:6" ht="58.5" customHeight="1">
-      <c r="A1140" s="102"/>
+      <c r="A1140" s="107"/>
       <c r="B1140" s="5" t="s">
         <v>2362</v>
       </c>
@@ -29460,7 +29460,7 @@
       <c r="F1140" s="23"/>
     </row>
     <row r="1141" spans="1:6" ht="108" customHeight="1">
-      <c r="A1141" s="102"/>
+      <c r="A1141" s="107"/>
       <c r="B1141" s="5" t="s">
         <v>2365</v>
       </c>
@@ -29476,7 +29476,7 @@
       <c r="F1141" s="23"/>
     </row>
     <row r="1142" spans="1:6" ht="72" customHeight="1">
-      <c r="A1142" s="102"/>
+      <c r="A1142" s="107"/>
       <c r="B1142" s="5" t="s">
         <v>2367</v>
       </c>
@@ -29490,7 +29490,7 @@
       <c r="F1142" s="23"/>
     </row>
     <row r="1143" spans="1:6" ht="58.5" customHeight="1">
-      <c r="A1143" s="102"/>
+      <c r="A1143" s="107"/>
       <c r="B1143" s="5" t="s">
         <v>2370</v>
       </c>
@@ -29506,7 +29506,7 @@
       <c r="F1143" s="23"/>
     </row>
     <row r="1144" spans="1:6" ht="27" customHeight="1">
-      <c r="A1144" s="102"/>
+      <c r="A1144" s="107"/>
       <c r="B1144" s="5" t="s">
         <v>2372</v>
       </c>
@@ -29522,7 +29522,7 @@
       <c r="F1144" s="23"/>
     </row>
     <row r="1145" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A1145" s="102"/>
+      <c r="A1145" s="107"/>
       <c r="B1145" s="5" t="s">
         <v>2374</v>
       </c>
@@ -29538,7 +29538,7 @@
       <c r="F1145" s="23"/>
     </row>
     <row r="1146" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A1146" s="102"/>
+      <c r="A1146" s="107"/>
       <c r="B1146" s="5" t="s">
         <v>2376</v>
       </c>
@@ -29552,7 +29552,7 @@
       <c r="F1146" s="23"/>
     </row>
     <row r="1147" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A1147" s="102"/>
+      <c r="A1147" s="107"/>
       <c r="B1147" s="5" t="s">
         <v>2378</v>
       </c>
@@ -29566,7 +29566,7 @@
       <c r="F1147" s="23"/>
     </row>
     <row r="1148" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1148" s="102"/>
+      <c r="A1148" s="107"/>
       <c r="B1148" s="5" t="s">
         <v>2380</v>
       </c>
@@ -29580,7 +29580,7 @@
       <c r="F1148" s="23"/>
     </row>
     <row r="1149" spans="1:6" ht="39" customHeight="1">
-      <c r="A1149" s="102"/>
+      <c r="A1149" s="107"/>
       <c r="B1149" s="5" t="s">
         <v>2382</v>
       </c>
@@ -29594,7 +29594,7 @@
       <c r="F1149" s="23"/>
     </row>
     <row r="1150" spans="1:6" ht="58.5" customHeight="1">
-      <c r="A1150" s="102"/>
+      <c r="A1150" s="107"/>
       <c r="B1150" s="5" t="s">
         <v>2384</v>
       </c>
@@ -29610,7 +29610,7 @@
       <c r="F1150" s="23"/>
     </row>
     <row r="1151" spans="1:6" ht="51" customHeight="1">
-      <c r="A1151" s="102"/>
+      <c r="A1151" s="107"/>
       <c r="B1151" s="5" t="s">
         <v>2387</v>
       </c>
@@ -29624,7 +29624,7 @@
       <c r="F1151" s="23"/>
     </row>
     <row r="1152" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A1152" s="102"/>
+      <c r="A1152" s="107"/>
       <c r="B1152" s="5" t="s">
         <v>2389</v>
       </c>
@@ -29638,7 +29638,7 @@
       <c r="F1152" s="23"/>
     </row>
     <row r="1153" spans="1:6" ht="48.75" customHeight="1">
-      <c r="A1153" s="102"/>
+      <c r="A1153" s="107"/>
       <c r="B1153" s="5" t="s">
         <v>2391</v>
       </c>
@@ -29652,7 +29652,7 @@
       <c r="F1153" s="23"/>
     </row>
     <row r="1154" spans="1:6" ht="48.75" customHeight="1">
-      <c r="A1154" s="102"/>
+      <c r="A1154" s="107"/>
       <c r="B1154" s="5" t="s">
         <v>2393</v>
       </c>
@@ -29666,7 +29666,7 @@
       <c r="F1154" s="23"/>
     </row>
     <row r="1155" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1155" s="102"/>
+      <c r="A1155" s="107"/>
       <c r="B1155" s="5" t="s">
         <v>2395</v>
       </c>
@@ -29680,7 +29680,7 @@
       <c r="F1155" s="23"/>
     </row>
     <row r="1156" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A1156" s="102"/>
+      <c r="A1156" s="107"/>
       <c r="B1156" s="5" t="s">
         <v>2397</v>
       </c>
@@ -29694,7 +29694,7 @@
       <c r="F1156" s="23"/>
     </row>
     <row r="1157" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A1157" s="102"/>
+      <c r="A1157" s="107"/>
       <c r="B1157" s="5" t="s">
         <v>2399</v>
       </c>
@@ -29708,7 +29708,7 @@
       <c r="F1157" s="23"/>
     </row>
     <row r="1158" spans="1:6" ht="42.75" customHeight="1">
-      <c r="A1158" s="102"/>
+      <c r="A1158" s="107"/>
       <c r="B1158" s="5" t="s">
         <v>2401</v>
       </c>
@@ -29724,7 +29724,7 @@
       <c r="F1158" s="23"/>
     </row>
     <row r="1159" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A1159" s="102"/>
+      <c r="A1159" s="107"/>
       <c r="B1159" s="5" t="s">
         <v>2403</v>
       </c>
@@ -29738,7 +29738,7 @@
       <c r="F1159" s="23"/>
     </row>
     <row r="1160" spans="1:6" ht="175.5" customHeight="1">
-      <c r="A1160" s="102"/>
+      <c r="A1160" s="107"/>
       <c r="B1160" s="5" t="s">
         <v>2406</v>
       </c>
@@ -29752,7 +29752,7 @@
       <c r="F1160" s="23"/>
     </row>
     <row r="1161" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1161" s="102"/>
+      <c r="A1161" s="107"/>
       <c r="B1161" s="5" t="s">
         <v>2409</v>
       </c>
@@ -29766,7 +29766,7 @@
       <c r="F1161" s="23"/>
     </row>
     <row r="1162" spans="1:6" ht="89.25" customHeight="1">
-      <c r="A1162" s="102"/>
+      <c r="A1162" s="107"/>
       <c r="B1162" s="5" t="s">
         <v>2411</v>
       </c>
@@ -29780,7 +29780,7 @@
       <c r="F1162" s="23"/>
     </row>
     <row r="1163" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A1163" s="102"/>
+      <c r="A1163" s="107"/>
       <c r="B1163" s="5" t="s">
         <v>2413</v>
       </c>
@@ -29794,7 +29794,7 @@
       <c r="F1163" s="23"/>
     </row>
     <row r="1164" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A1164" s="102"/>
+      <c r="A1164" s="107"/>
       <c r="B1164" s="5" t="s">
         <v>2415</v>
       </c>
@@ -29808,7 +29808,7 @@
       <c r="F1164" s="23"/>
     </row>
     <row r="1165" spans="1:6" ht="195" customHeight="1">
-      <c r="A1165" s="102"/>
+      <c r="A1165" s="107"/>
       <c r="B1165" s="5" t="s">
         <v>2417</v>
       </c>
@@ -29824,7 +29824,7 @@
       <c r="F1165" s="23"/>
     </row>
     <row r="1166" spans="1:6" ht="82.5" customHeight="1">
-      <c r="A1166" s="102"/>
+      <c r="A1166" s="107"/>
       <c r="B1166" s="5" t="s">
         <v>2419</v>
       </c>
@@ -29838,7 +29838,7 @@
       <c r="F1166" s="23"/>
     </row>
     <row r="1167" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A1167" s="102"/>
+      <c r="A1167" s="107"/>
       <c r="B1167" s="1" t="s">
         <v>2421</v>
       </c>
@@ -29852,7 +29852,7 @@
       <c r="F1167" s="23"/>
     </row>
     <row r="1168" spans="1:6" ht="42.75" customHeight="1">
-      <c r="A1168" s="102"/>
+      <c r="A1168" s="107"/>
       <c r="B1168" s="5" t="s">
         <v>2423</v>
       </c>
@@ -29864,7 +29864,7 @@
       <c r="F1168" s="23"/>
     </row>
     <row r="1169" spans="1:6" ht="39.75" customHeight="1">
-      <c r="A1169" s="102"/>
+      <c r="A1169" s="107"/>
       <c r="B1169" s="5" t="s">
         <v>2425</v>
       </c>
@@ -29878,7 +29878,7 @@
       <c r="F1169" s="23"/>
     </row>
     <row r="1170" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1170" s="98"/>
+      <c r="A1170" s="103"/>
       <c r="B1170" s="5" t="s">
         <v>2427</v>
       </c>

--- a/chat_bot/1300_вопросов_от_студентов_для_базы_данных.xlsx
+++ b/chat_bot/1300_вопросов_от_студентов_для_базы_данных.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190"/>
   </bookViews>
   <sheets>
     <sheet name="1300 вопросов" sheetId="2" r:id="rId1"/>
